--- a/files/collected_data_test.xlsx
+++ b/files/collected_data_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF023FA2-2EF7-445D-ACA2-142BB1C09324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED17303F-1107-453D-94BE-F1F5548CC162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="management" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="stations" sheetId="6" r:id="rId3"/>
     <sheet name="usms" sheetId="1" r:id="rId4"/>
     <sheet name="observations" sheetId="9" r:id="rId5"/>
-    <sheet name="options" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="options" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Fertilizer_Application">Table3[Fertilizer Application]</definedName>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="220">
   <si>
     <t>usm_name</t>
   </si>
@@ -544,72 +544,18 @@
     <t>2=Beauce limestone</t>
   </si>
   <si>
-    <t>1=Beauce limestone1</t>
-  </si>
-  <si>
     <t>3=Lutetian limestone</t>
   </si>
   <si>
-    <t>1=at soil surface</t>
-  </si>
-  <si>
-    <t>2=below soil surface</t>
-  </si>
-  <si>
     <t>1=forced Penman</t>
   </si>
   <si>
-    <t>1=ammonium nitrate</t>
-  </si>
-  <si>
-    <t>2=calculated Penman</t>
-  </si>
-  <si>
-    <t>2=UAN solution</t>
-  </si>
-  <si>
     <t>3=Shuttleworth &amp; Wallace</t>
   </si>
   <si>
-    <t>3=urea</t>
-  </si>
-  <si>
     <t>4=Priestley &amp; Taylor</t>
   </si>
   <si>
-    <t>4=anhydrous ammonia</t>
-  </si>
-  <si>
-    <t>5=ammonium sulfate</t>
-  </si>
-  <si>
-    <t>6=ammonium phosphate</t>
-  </si>
-  <si>
-    <t>7=calcium nitrate</t>
-  </si>
-  <si>
-    <t>8=fixed efficiency fertiliser</t>
-  </si>
-  <si>
-    <t>4=Lutetian Brackish marl and limestone</t>
-  </si>
-  <si>
-    <t>5=morainic gravels</t>
-  </si>
-  <si>
-    <t>6=unweathered flint, sandstone or granite</t>
-  </si>
-  <si>
-    <t>7=weathered granite</t>
-  </si>
-  <si>
-    <t>8=Jurassic limestone</t>
-  </si>
-  <si>
-    <t>9=Pebbles from Magneraud</t>
-  </si>
-  <si>
     <t>RG19</t>
   </si>
   <si>
@@ -679,15 +625,6 @@
     <t>Irrigation Location</t>
   </si>
   <si>
-    <t>above foliage</t>
-  </si>
-  <si>
-    <t>under foliage</t>
-  </si>
-  <si>
-    <t>in the soil</t>
-  </si>
-  <si>
     <t>irrigation_depth</t>
   </si>
   <si>
@@ -695,6 +632,84 @@
   </si>
   <si>
     <t>spacing</t>
+  </si>
+  <si>
+    <t>1 = above foliage</t>
+  </si>
+  <si>
+    <t>2 = under foliage</t>
+  </si>
+  <si>
+    <t>3 = in the soil</t>
+  </si>
+  <si>
+    <t>1 = forced Penman</t>
+  </si>
+  <si>
+    <t>1 = ammonium nitrate</t>
+  </si>
+  <si>
+    <t>1 = at soil surface</t>
+  </si>
+  <si>
+    <t>1 = Beauce limestone1</t>
+  </si>
+  <si>
+    <t>2 = calculated Penman</t>
+  </si>
+  <si>
+    <t>2 = UAN solution</t>
+  </si>
+  <si>
+    <t>2 = below soil surface</t>
+  </si>
+  <si>
+    <t>2 = Beauce limestone</t>
+  </si>
+  <si>
+    <t>3 = Shuttleworth &amp; Wallace</t>
+  </si>
+  <si>
+    <t>3 = urea</t>
+  </si>
+  <si>
+    <t>3 = Lutetian limestone</t>
+  </si>
+  <si>
+    <t>4 = Priestley &amp; Taylor</t>
+  </si>
+  <si>
+    <t>4 = anhydrous ammonia</t>
+  </si>
+  <si>
+    <t>4 = Lutetian Brackish marl and limestone</t>
+  </si>
+  <si>
+    <t>5 = ammonium sulfate</t>
+  </si>
+  <si>
+    <t>5 = morainic gravels</t>
+  </si>
+  <si>
+    <t>6 = ammonium phosphate</t>
+  </si>
+  <si>
+    <t>6 = unweathered flint, sandstone or granite</t>
+  </si>
+  <si>
+    <t>7 = calcium nitrate</t>
+  </si>
+  <si>
+    <t>7 = weathered granite</t>
+  </si>
+  <si>
+    <t>8 = fixed efficiency fertiliser</t>
+  </si>
+  <si>
+    <t>8 = Jurassic limestone</t>
+  </si>
+  <si>
+    <t>9 = Pebbles from Magneraud</t>
   </si>
 </sst>
 </file>
@@ -1128,9 +1143,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1146,10 +1159,13 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1164,88 +1180,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="66">
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1429,6 +1368,20 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
@@ -1553,6 +1506,23 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="none">
           <fgColor theme="0" tint="-0.24994659260841701"/>
           <bgColor auto="1"/>
@@ -1590,6 +1560,20 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1789,6 +1773,37 @@
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1817,26 +1832,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AX100" totalsRowShown="0" headerRowDxfId="65" headerRowBorderDxfId="64" tableBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AX100" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A2:AX100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
   <tableColumns count="50">
-    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="58"/>
     <tableColumn id="3" xr3:uid="{416116E5-319A-4096-B7E5-AF8ADEF0E80A}" name="tillage_date"/>
-    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="57"/>
     <tableColumn id="5" xr3:uid="{A768ED69-1CCB-4A41-99C1-D5042177408B}" name="planting_date"/>
     <tableColumn id="6" xr3:uid="{5517C570-4D1C-46EC-9FB0-4FEA929440E1}" name="planting_depth"/>
-    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="56"/>
     <tableColumn id="8" xr3:uid="{7DEB259C-DAE3-4A1E-B476-951FEF30ABD2}" name="emergence"/>
     <tableColumn id="9" xr3:uid="{8590CC43-CF1F-45A9-A612-CE3749B53C84}" name="flowering"/>
-    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="55"/>
     <tableColumn id="11" xr3:uid="{1651DE3B-149A-4121-AFB0-BA33E8308050}" name="application_date"/>
     <tableColumn id="12" xr3:uid="{358B23A5-F859-4B79-9182-F98F3D69F461}" name="kg_N_per_ha"/>
     <tableColumn id="13" xr3:uid="{FEB67719-45D9-4389-A438-548C552EBED6}" name="fert_type"/>
     <tableColumn id="14" xr3:uid="{B9B3005C-6E63-4AA3-BE8E-646D9659B76F}" name="fert_location"/>
-    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="54"/>
     <tableColumn id="47" xr3:uid="{5A7FCCFE-6AE7-4F4A-9144-79DD4C78A77A}" name="harvest_date"/>
-    <tableColumn id="48" xr3:uid="{4F6EC2C1-7F9F-42B7-B004-103B851D9623}" name="latest_harvest_date" dataDxfId="56"/>
+    <tableColumn id="48" xr3:uid="{4F6EC2C1-7F9F-42B7-B004-103B851D9623}" name="latest_harvest_date" dataDxfId="53"/>
     <tableColumn id="49" xr3:uid="{3A282F1C-F9BB-4D9A-A1F3-FE6FAF7FC99B}" name="irrigation_efficiency"/>
     <tableColumn id="50" xr3:uid="{E012D667-4077-4ED4-BA83-E536678E3246}" name="irrigation_location"/>
     <tableColumn id="51" xr3:uid="{AB6C88AB-1F8E-4D7B-8C92-10AA2AB3B1CB}" name="irrigation_depth"/>
@@ -1916,15 +1931,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CH100" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CH100" totalsRowShown="0" headerRowDxfId="52" headerRowBorderDxfId="51" tableBorderDxfId="50">
   <autoFilter ref="A2:CH100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
   <tableColumns count="86">
-    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="52"/>
-    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="49"/>
+    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="48"/>
     <tableColumn id="80" xr3:uid="{0420D7E9-122C-4575-A7AC-7BBC4F58B702}" name="impermeable_lyr"/>
     <tableColumn id="82" xr3:uid="{6B1B49F0-7082-435D-B674-074AD54FF41A}" name="spacing"/>
     <tableColumn id="81" xr3:uid="{D1C9B62E-CB38-44E4-B973-A9B54A950392}" name="hydraulic_conductivity"/>
-    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="50"/>
+    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="47"/>
     <tableColumn id="2" xr3:uid="{72D785FE-A1AF-4E08-AB14-39FAD15DB9BD}" name="thickness_1"/>
     <tableColumn id="3" xr3:uid="{1838D7E8-2B3C-471C-9A0B-D70D91F18417}" name="pH"/>
     <tableColumn id="4" xr3:uid="{22C3A2D3-19B8-4556-9BAC-DEDF286C1C2C}" name="%_sand_1"/>
@@ -1936,88 +1951,88 @@
     <tableColumn id="41" xr3:uid="{F7750E58-5B0E-4494-87AF-B025671824DE}" name="CN_ratio"/>
     <tableColumn id="91" xr3:uid="{4BC0F474-7619-4785-B6E4-D8011A3578A1}" name="carbonate"/>
     <tableColumn id="8" xr3:uid="{0592115C-328E-42C4-B9CB-D43026D4FC27}" name="FC_1"/>
-    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="49"/>
+    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="46"/>
     <tableColumn id="9" xr3:uid="{C1383A59-387E-4667-852A-B0CF467088F3}" name="WP_1"/>
-    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="48"/>
+    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="45"/>
     <tableColumn id="10" xr3:uid="{34D0D911-5DB4-457F-88A7-76A42B57EE1A}" name="initial_NO3_1"/>
-    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="47"/>
+    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="44"/>
     <tableColumn id="53" xr3:uid="{CEF78893-60AA-4A20-A771-E76562B8EBC1}" name="initial_NH4_1"/>
-    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="46"/>
-    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="45"/>
-    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="43"/>
+    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="42"/>
+    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="41"/>
     <tableColumn id="12" xr3:uid="{FD043EB5-2678-4920-8D76-EBE8316E27AA}" name="thickness_2"/>
     <tableColumn id="13" xr3:uid="{F124AE04-B447-4F21-A0E8-7B26199C0F49}" name="%_sand_2"/>
     <tableColumn id="14" xr3:uid="{F119498A-3A35-40E3-A753-7CF13D724118}" name="%_clay_2"/>
     <tableColumn id="15" xr3:uid="{AE51522F-6903-42D4-88CE-A95BCE8C77EF}" name="BD_2"/>
     <tableColumn id="16" xr3:uid="{12076489-6AD7-4297-A729-20EF93AEE58D}" name="SOC_2"/>
     <tableColumn id="17" xr3:uid="{D6D5EFD4-69CC-4AF2-8C6B-0B430468C4C2}" name="FC_2"/>
-    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="44"/>
+    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="40"/>
     <tableColumn id="18" xr3:uid="{BBF6A61D-2092-4DF7-8C38-9024164291AE}" name="WP_2"/>
-    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="43"/>
+    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="39"/>
     <tableColumn id="19" xr3:uid="{BB4B796C-CA3E-424C-87B0-4BF33581B61B}" name="initial_NO3_2"/>
-    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="42"/>
+    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="38"/>
     <tableColumn id="55" xr3:uid="{333E59C3-3A13-4C92-9169-AC90D5E5D3EB}" name="initial_NH4_2"/>
-    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="41"/>
-    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="40"/>
-    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="37"/>
+    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="36"/>
+    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="35"/>
     <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3"/>
     <tableColumn id="22" xr3:uid="{6C917DE4-8D95-496E-A6F1-EAB7450774EE}" name="%_sand_3"/>
     <tableColumn id="23" xr3:uid="{90DE7FE2-3A23-4294-8BD0-2D321FF71179}" name="%_clay_3"/>
     <tableColumn id="24" xr3:uid="{C874CBBB-CB06-4239-AE9B-72564A3EDC14}" name="BD_3"/>
     <tableColumn id="25" xr3:uid="{49CED3FB-E83C-4973-A99D-DAC6B3AFC7B1}" name="SOC_3"/>
     <tableColumn id="26" xr3:uid="{63FB3901-EBED-4379-9E9C-83064A8ADD01}" name="FC_3"/>
-    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="39"/>
+    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="34"/>
     <tableColumn id="27" xr3:uid="{6EEACF0E-3934-49DF-9991-42C2DB718BE0}" name="WP_3"/>
-    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="38"/>
+    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="33"/>
     <tableColumn id="28" xr3:uid="{7AAE3F1E-C60E-4E11-A023-F09548D5AA39}" name="initial_NO3_3"/>
-    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="37"/>
+    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="32"/>
     <tableColumn id="57" xr3:uid="{1D0A3587-38DB-4073-B5D4-36DA82425955}" name="initial_NH4_3"/>
-    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="36"/>
-    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="35"/>
-    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="34"/>
-    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="33"/>
+    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="31"/>
+    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="30"/>
+    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="29"/>
+    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="28"/>
     <tableColumn id="31" xr3:uid="{4C1178FA-055B-4F19-A181-638D37A24EB6}" name="%_sand_4"/>
     <tableColumn id="32" xr3:uid="{7BBFA3FD-BBE5-4B68-A551-EFDEA7062540}" name="%_clay_4"/>
     <tableColumn id="33" xr3:uid="{D0607A27-FB9E-4DA9-A7F3-7A932B2608A4}" name="BD_4"/>
     <tableColumn id="34" xr3:uid="{BD46131F-AB56-411A-8742-B77FBBE1967B}" name="SOC_4"/>
     <tableColumn id="35" xr3:uid="{EC2EEDB8-3CC6-4DEE-9309-DBA3B11A2D16}" name="FC_4"/>
-    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="32"/>
-    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="31"/>
-    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="30"/>
-    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="29"/>
-    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="28"/>
-    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="27"/>
-    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="26"/>
-    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="25"/>
-    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="2"/>
+    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="27"/>
+    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="26"/>
+    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="25"/>
+    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="24"/>
+    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="23"/>
+    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="22"/>
+    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="21"/>
+    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="20"/>
+    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="19"/>
     <tableColumn id="46" xr3:uid="{5545ADBB-3E57-4FCE-9979-330500D810A6}" name="thickness_5"/>
     <tableColumn id="49" xr3:uid="{28F4610E-A232-42D7-866E-B72AB5FC38D8}" name="%_sand_5"/>
     <tableColumn id="60" xr3:uid="{9557F7B0-0944-4CA4-8B86-630B4073480C}" name="%_clay_5"/>
     <tableColumn id="61" xr3:uid="{6977D0A0-E571-46FB-8186-DF22D992C4B6}" name="BD_5"/>
     <tableColumn id="62" xr3:uid="{762BF513-B3A9-4714-B788-A74D32CD414B}" name="SOC_5"/>
     <tableColumn id="63" xr3:uid="{F840DA58-F957-445A-8704-4823DC13AEC7}" name="FC_5"/>
-    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="24"/>
+    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="18"/>
     <tableColumn id="65" xr3:uid="{73133DDD-77CC-4B8F-AF63-0B5537B95DE3}" name="WP_5"/>
-    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="23"/>
+    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="17"/>
     <tableColumn id="67" xr3:uid="{AF697735-FE14-47A1-8029-532D47D2E5C7}" name="initial_NO3_5"/>
-    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="22"/>
-    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="21"/>
-    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="20"/>
-    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="19"/>
-    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="18"/>
+    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="16"/>
+    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="15"/>
+    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="14"/>
+    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="13"/>
+    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="A1:E109" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{25C187AA-B7AD-4009-9499-173271E0B34E}" name="unit"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2025,31 +2040,31 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:I100" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:I100" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A2:I100" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{C58B90D4-B75A-409B-9D58-E09932ABF65C}" name="simulation_start"/>
-    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{C4CB74A7-2660-4D67-9D08-D7802D112D6D}" name="soil_profile_name"/>
     <tableColumn id="6" xr3:uid="{EE8564A9-D685-42B6-914D-B5F77F840B11}" name="weather_station_name"/>
     <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file"/>
     <tableColumn id="9" xr3:uid="{BDB57316-D9C6-4EE3-821F-F5561E0078D9}" name="first_year"/>
-    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="65">
   <autoFilter ref="A1:F30" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="64"/>
     <tableColumn id="2" xr3:uid="{A5156817-2D3F-4E14-AC57-75BA66E12293}" name="year"/>
     <tableColumn id="3" xr3:uid="{173E3383-07EB-425D-884F-01E4ECFF4626}" name="month"/>
-    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="63"/>
     <tableColumn id="6" xr3:uid="{B9B2B184-EF64-48EF-B50B-8E24249DFDCC}" name="lai"/>
     <tableColumn id="7" xr3:uid="{ED0F5D28-DB43-4C9B-ADB2-1706AC6D61F9}" name="pdffruitfrais"/>
   </tableColumns>
@@ -2440,44 +2455,44 @@
       <c r="N1" s="68"/>
       <c r="O1" s="68"/>
       <c r="P1" s="70" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="Q1" s="70"/>
-      <c r="R1" s="65" t="s">
+      <c r="R1" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="65"/>
-      <c r="AB1" s="65"/>
-      <c r="AC1" s="65"/>
-      <c r="AD1" s="65"/>
-      <c r="AE1" s="65"/>
-      <c r="AF1" s="65"/>
-      <c r="AG1" s="65"/>
-      <c r="AH1" s="65"/>
-      <c r="AI1" s="65"/>
-      <c r="AJ1" s="65"/>
-      <c r="AK1" s="65"/>
-      <c r="AL1" s="65"/>
-      <c r="AM1" s="65"/>
-      <c r="AN1" s="65"/>
-      <c r="AO1" s="65"/>
-      <c r="AP1" s="65"/>
-      <c r="AQ1" s="65"/>
-      <c r="AR1" s="65"/>
-      <c r="AS1" s="65"/>
-      <c r="AT1" s="65"/>
-      <c r="AU1" s="65"/>
-      <c r="AV1" s="65"/>
-      <c r="AW1" s="65"/>
-      <c r="AX1" s="65"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="71"/>
+      <c r="AF1" s="71"/>
+      <c r="AG1" s="71"/>
+      <c r="AH1" s="71"/>
+      <c r="AI1" s="71"/>
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="71"/>
+      <c r="AL1" s="71"/>
+      <c r="AM1" s="71"/>
+      <c r="AN1" s="71"/>
+      <c r="AO1" s="71"/>
+      <c r="AP1" s="71"/>
+      <c r="AQ1" s="71"/>
+      <c r="AR1" s="71"/>
+      <c r="AS1" s="71"/>
+      <c r="AT1" s="71"/>
+      <c r="AU1" s="71"/>
+      <c r="AV1" s="71"/>
+      <c r="AW1" s="71"/>
+      <c r="AX1" s="71"/>
     </row>
     <row r="2" spans="1:50" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
@@ -2526,19 +2541,19 @@
         <v>58</v>
       </c>
       <c r="P2" s="62" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="Q2" s="63" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="R2" s="64" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="S2" s="33" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="T2" s="64" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>72</v>
@@ -2633,7 +2648,7 @@
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -2657,10 +2672,10 @@
         <v>120</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="N3" s="34" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="O3" s="6">
         <v>20</v>
@@ -2676,7 +2691,7 @@
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C4" s="59">
         <v>46172</v>
@@ -2709,10 +2724,10 @@
         <v>180</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="P4">
         <v>260</v>
@@ -2724,7 +2739,7 @@
         <v>90</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -2739,7 +2754,7 @@
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="C5">
         <v>106</v>
@@ -2772,10 +2787,10 @@
         <v>200</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="O5" s="6">
         <v>15</v>
@@ -2784,7 +2799,7 @@
         <v>80</v>
       </c>
       <c r="S5" s="34" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="U5">
         <v>146</v>
@@ -3372,12 +3387,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="R1:AX1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:AX1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3511,40 +3526,40 @@
       <c r="BB1" s="66"/>
       <c r="BC1" s="66"/>
       <c r="BD1" s="66"/>
-      <c r="BE1" s="65" t="s">
+      <c r="BE1" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="BF1" s="65"/>
-      <c r="BG1" s="65"/>
-      <c r="BH1" s="65"/>
-      <c r="BI1" s="65"/>
-      <c r="BJ1" s="65"/>
-      <c r="BK1" s="65"/>
-      <c r="BL1" s="65"/>
-      <c r="BM1" s="65"/>
-      <c r="BN1" s="65"/>
-      <c r="BO1" s="65"/>
-      <c r="BP1" s="65"/>
-      <c r="BQ1" s="65"/>
-      <c r="BR1" s="65"/>
-      <c r="BS1" s="65"/>
-      <c r="BT1" s="71" t="s">
+      <c r="BF1" s="71"/>
+      <c r="BG1" s="71"/>
+      <c r="BH1" s="71"/>
+      <c r="BI1" s="71"/>
+      <c r="BJ1" s="71"/>
+      <c r="BK1" s="71"/>
+      <c r="BL1" s="71"/>
+      <c r="BM1" s="71"/>
+      <c r="BN1" s="71"/>
+      <c r="BO1" s="71"/>
+      <c r="BP1" s="71"/>
+      <c r="BQ1" s="71"/>
+      <c r="BR1" s="71"/>
+      <c r="BS1" s="71"/>
+      <c r="BT1" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="BU1" s="71"/>
-      <c r="BV1" s="71"/>
-      <c r="BW1" s="71"/>
-      <c r="BX1" s="71"/>
-      <c r="BY1" s="71"/>
-      <c r="BZ1" s="71"/>
-      <c r="CA1" s="71"/>
-      <c r="CB1" s="71"/>
-      <c r="CC1" s="71"/>
-      <c r="CD1" s="71"/>
-      <c r="CE1" s="71"/>
-      <c r="CF1" s="71"/>
-      <c r="CG1" s="71"/>
-      <c r="CH1" s="71"/>
+      <c r="BU1" s="73"/>
+      <c r="BV1" s="73"/>
+      <c r="BW1" s="73"/>
+      <c r="BX1" s="73"/>
+      <c r="BY1" s="73"/>
+      <c r="BZ1" s="73"/>
+      <c r="CA1" s="73"/>
+      <c r="CB1" s="73"/>
+      <c r="CC1" s="73"/>
+      <c r="CD1" s="73"/>
+      <c r="CE1" s="73"/>
+      <c r="CF1" s="73"/>
+      <c r="CG1" s="73"/>
+      <c r="CH1" s="73"/>
     </row>
     <row r="2" spans="1:86" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
@@ -3557,7 +3572,7 @@
         <v>149</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="E2" s="46" t="s">
         <v>150</v>
@@ -3593,7 +3608,7 @@
         <v>105</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="Q2" s="24" t="s">
         <v>39</v>
@@ -3808,7 +3823,7 @@
     </row>
     <row r="3" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B3" s="48">
         <v>0.25</v>
@@ -3865,7 +3880,7 @@
         <v>20</v>
       </c>
       <c r="Z3" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA3">
         <v>20</v>
@@ -3954,7 +3969,7 @@
       <c r="BC3">
         <v>40</v>
       </c>
-      <c r="BD3" s="77" t="s">
+      <c r="BD3" s="65" t="s">
         <v>163</v>
       </c>
       <c r="BE3">
@@ -4050,7 +4065,7 @@
     </row>
     <row r="4" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B4" s="48">
         <v>0.25</v>
@@ -7029,12 +7044,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="BT1:CH1"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:Z1"/>
     <mergeCell ref="AA1:AO1"/>
     <mergeCell ref="AP1:BD1"/>
     <mergeCell ref="BE1:BS1"/>
-    <mergeCell ref="BT1:CH1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7102,54 +7117,54 @@
         <v>62</v>
       </c>
       <c r="E1" s="61" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B2" s="6">
         <v>24.55</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B3" s="6">
         <v>-48.12</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D3" s="19">
         <v>5</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B4" s="6">
         <v>8.093</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D4" s="19">
         <v>40</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7935,16 +7950,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C1"/>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="73" t="s">
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="74"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
@@ -7977,7 +7992,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B3">
         <v>105</v>
@@ -7986,16 +8001,16 @@
         <v>325</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="H3">
         <v>2019</v>
@@ -8006,7 +8021,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B4" s="59">
         <v>46086</v>
@@ -8015,16 +8030,16 @@
         <v>46118</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="H4">
         <v>2019</v>
@@ -8035,7 +8050,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -8044,16 +8059,16 @@
         <v>236</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G5" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="H5">
         <v>2020</v>
@@ -8064,7 +8079,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B6" s="59">
         <v>46146</v>
@@ -8073,16 +8088,16 @@
         <v>46297</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="H6">
         <v>2004</v>
@@ -8627,15 +8642,15 @@
         <v>142</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B2">
         <v>2019</v>
@@ -8652,7 +8667,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B3">
         <v>2019</v>
@@ -8669,7 +8684,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B4">
         <v>2019</v>
@@ -8686,7 +8701,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B5">
         <v>2019</v>
@@ -8703,7 +8718,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B6">
         <v>2019</v>
@@ -8720,7 +8735,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B7">
         <v>2019</v>
@@ -8737,7 +8752,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B8">
         <v>2019</v>
@@ -8754,7 +8769,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B9">
         <v>2019</v>
@@ -8771,7 +8786,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B10">
         <v>2019</v>
@@ -8788,7 +8803,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B11">
         <v>2004</v>
@@ -8805,7 +8820,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B12">
         <v>2004</v>
@@ -8822,7 +8837,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B13">
         <v>2004</v>
@@ -8839,7 +8854,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B14">
         <v>2004</v>
@@ -8856,7 +8871,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B15">
         <v>2004</v>
@@ -8873,7 +8888,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B16">
         <v>2004</v>
@@ -8890,7 +8905,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B17">
         <v>2004</v>
@@ -8907,7 +8922,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B18">
         <v>2004</v>
@@ -8924,7 +8939,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B19">
         <v>2004</v>
@@ -9013,10 +9028,10 @@
         <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E1" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G1" t="s">
         <v>114</v>
@@ -9025,24 +9040,24 @@
         <v>127</v>
       </c>
       <c r="K1" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="M1" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="O1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="G2" t="s">
         <v>116</v>
@@ -9051,24 +9066,24 @@
         <v>126</v>
       </c>
       <c r="K2" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="M2" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="O2" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="G3" t="s">
         <v>115</v>
@@ -9077,76 +9092,76 @@
         <v>125</v>
       </c>
       <c r="K3" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="M3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="O3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="K4" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="O4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="K5" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="K6" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="K7" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="K8" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="K9" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
       <c r="K10" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/files/collected_data_test.xlsx
+++ b/files/collected_data_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marpo\Documents\Research\STICS\Code\mkSTICSfiles\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED17303F-1107-453D-94BE-F1F5548CC162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BFF4EE-6E94-4373-86F7-74D824C2E62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="management" sheetId="8" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="222">
   <si>
     <t>usm_name</t>
   </si>
@@ -544,9 +544,6 @@
     <t>2=Beauce limestone</t>
   </si>
   <si>
-    <t>3=Lutetian limestone</t>
-  </si>
-  <si>
     <t>1=forced Penman</t>
   </si>
   <si>
@@ -710,6 +707,15 @@
   </si>
   <si>
     <t>9 = Pebbles from Magneraud</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>inorganic_N</t>
+  </si>
+  <si>
+    <t>SOM_2</t>
   </si>
 </sst>
 </file>
@@ -1144,28 +1150,28 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1185,6 +1191,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="66">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1309,6 +1346,110 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1669,141 +1810,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray0625">
-          <fgColor theme="0" tint="-0.24994659260841701"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1832,26 +1838,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AX100" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}" name="Table6" displayName="Table6" ref="A2:AX100" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22">
   <autoFilter ref="A2:AX100" xr:uid="{1AD7F1BC-9C4F-46C6-88D5-D2D5C340F1D9}"/>
   <tableColumns count="50">
-    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{6B129591-A0EC-4CC8-AA8E-70259B5C9131}" name="file_name" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{1FBFF361-0229-404E-A60E-FCEC995B36AD}" name="year" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{416116E5-319A-4096-B7E5-AF8ADEF0E80A}" name="tillage_date"/>
-    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{781FB9F7-258C-4E50-8A90-CAA110FA989E}" name="tillage_depth" dataDxfId="19"/>
     <tableColumn id="5" xr3:uid="{A768ED69-1CCB-4A41-99C1-D5042177408B}" name="planting_date"/>
     <tableColumn id="6" xr3:uid="{5517C570-4D1C-46EC-9FB0-4FEA929440E1}" name="planting_depth"/>
-    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{8F3D9EFB-6197-44D6-9CAB-532096E5D0DE}" name="plants_per_m2" dataDxfId="18"/>
     <tableColumn id="8" xr3:uid="{7DEB259C-DAE3-4A1E-B476-951FEF30ABD2}" name="emergence"/>
     <tableColumn id="9" xr3:uid="{8590CC43-CF1F-45A9-A612-CE3749B53C84}" name="flowering"/>
-    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{DAF1F67C-7CB4-4AD2-B1D4-24884C7C9D57}" name="maturity" dataDxfId="17"/>
     <tableColumn id="11" xr3:uid="{1651DE3B-149A-4121-AFB0-BA33E8308050}" name="application_date"/>
     <tableColumn id="12" xr3:uid="{358B23A5-F859-4B79-9182-F98F3D69F461}" name="kg_N_per_ha"/>
     <tableColumn id="13" xr3:uid="{FEB67719-45D9-4389-A438-548C552EBED6}" name="fert_type"/>
     <tableColumn id="14" xr3:uid="{B9B3005C-6E63-4AA3-BE8E-646D9659B76F}" name="fert_location"/>
-    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="54"/>
+    <tableColumn id="15" xr3:uid="{F5737449-F543-4637-B8F3-6DBD1B98EDA2}" name="fert_depth" dataDxfId="16"/>
     <tableColumn id="47" xr3:uid="{5A7FCCFE-6AE7-4F4A-9144-79DD4C78A77A}" name="harvest_date"/>
-    <tableColumn id="48" xr3:uid="{4F6EC2C1-7F9F-42B7-B004-103B851D9623}" name="latest_harvest_date" dataDxfId="53"/>
+    <tableColumn id="48" xr3:uid="{4F6EC2C1-7F9F-42B7-B004-103B851D9623}" name="latest_harvest_date" dataDxfId="15"/>
     <tableColumn id="49" xr3:uid="{3A282F1C-F9BB-4D9A-A1F3-FE6FAF7FC99B}" name="irrigation_efficiency"/>
     <tableColumn id="50" xr3:uid="{E012D667-4077-4ED4-BA83-E536678E3246}" name="irrigation_location"/>
     <tableColumn id="51" xr3:uid="{AB6C88AB-1F8E-4D7B-8C92-10AA2AB3B1CB}" name="irrigation_depth"/>
@@ -1931,15 +1937,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CH100" totalsRowShown="0" headerRowDxfId="52" headerRowBorderDxfId="51" tableBorderDxfId="50">
-  <autoFilter ref="A2:CH100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
-  <tableColumns count="86">
-    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="49"/>
-    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}" name="Table7" displayName="Table7" ref="A2:CJ100" totalsRowShown="0" headerRowDxfId="65" headerRowBorderDxfId="64" tableBorderDxfId="63">
+  <autoFilter ref="A2:CJ100" xr:uid="{34F446AA-1543-42D0-AA83-3EA91742E62F}"/>
+  <tableColumns count="88">
+    <tableColumn id="1" xr3:uid="{4674EE1C-2CD4-485E-8B27-A14DEFFAAD8A}" name="soil_profile_name" dataDxfId="62"/>
+    <tableColumn id="79" xr3:uid="{5CB48894-415F-45F0-AA28-53288D84720D}" name="albedo" dataDxfId="61"/>
     <tableColumn id="80" xr3:uid="{0420D7E9-122C-4575-A7AC-7BBC4F58B702}" name="impermeable_lyr"/>
     <tableColumn id="82" xr3:uid="{6B1B49F0-7082-435D-B674-074AD54FF41A}" name="spacing"/>
     <tableColumn id="81" xr3:uid="{D1C9B62E-CB38-44E4-B973-A9B54A950392}" name="hydraulic_conductivity"/>
-    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="47"/>
+    <tableColumn id="78" xr3:uid="{E52BCA3D-F2B1-404B-9910-E92D79806338}" name="depth" dataDxfId="60"/>
     <tableColumn id="2" xr3:uid="{72D785FE-A1AF-4E08-AB14-39FAD15DB9BD}" name="thickness_1"/>
     <tableColumn id="3" xr3:uid="{1838D7E8-2B3C-471C-9A0B-D70D91F18417}" name="pH"/>
     <tableColumn id="4" xr3:uid="{22C3A2D3-19B8-4556-9BAC-DEDF286C1C2C}" name="%_sand_1"/>
@@ -1948,91 +1954,93 @@
     <tableColumn id="39" xr3:uid="{E2BB7CB7-ACCE-4FF1-AF91-42C43097A8A0}" name="SOM_1"/>
     <tableColumn id="7" xr3:uid="{20FE986C-6B28-4993-A555-F2428095534E}" name="SOC_1"/>
     <tableColumn id="40" xr3:uid="{EC836542-6DD7-49C9-82D9-B724BCE18341}" name="SON_1"/>
+    <tableColumn id="71" xr3:uid="{B159CEA5-29C9-4E68-B599-3FB15B7BBBAA}" name="inorganic_N"/>
     <tableColumn id="41" xr3:uid="{F7750E58-5B0E-4494-87AF-B025671824DE}" name="CN_ratio"/>
     <tableColumn id="91" xr3:uid="{4BC0F474-7619-4785-B6E4-D8011A3578A1}" name="carbonate"/>
     <tableColumn id="8" xr3:uid="{0592115C-328E-42C4-B9CB-D43026D4FC27}" name="FC_1"/>
-    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="46"/>
+    <tableColumn id="42" xr3:uid="{5C21A417-1737-43F1-BC15-EC087A009A68}" name="FC_1_unit" dataDxfId="59"/>
     <tableColumn id="9" xr3:uid="{C1383A59-387E-4667-852A-B0CF467088F3}" name="WP_1"/>
-    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="45"/>
+    <tableColumn id="43" xr3:uid="{75E60C07-9873-41B6-AB5A-253087B95CFA}" name="WP_1_unit" dataDxfId="58"/>
     <tableColumn id="10" xr3:uid="{34D0D911-5DB4-457F-88A7-76A42B57EE1A}" name="initial_NO3_1"/>
-    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="44"/>
+    <tableColumn id="52" xr3:uid="{630D852C-736F-4D0D-8BB3-6EB32B59A383}" name="initial_NO3_1_units" dataDxfId="57"/>
     <tableColumn id="53" xr3:uid="{CEF78893-60AA-4A20-A771-E76562B8EBC1}" name="initial_NH4_1"/>
-    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="43"/>
-    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="42"/>
-    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{58B6280A-10C4-4120-9FF8-93150CE70C6B}" name="initial_NH4_1_units" dataDxfId="56"/>
+    <tableColumn id="76" xr3:uid="{959F9CFC-A05B-44B3-8BDC-997008E70E75}" name="pebble_content_1" dataDxfId="55"/>
+    <tableColumn id="74" xr3:uid="{1C138026-FB93-4B8F-BA93-A71995053AE9}" name="pebble_type_1" dataDxfId="54"/>
     <tableColumn id="12" xr3:uid="{FD043EB5-2678-4920-8D76-EBE8316E27AA}" name="thickness_2"/>
     <tableColumn id="13" xr3:uid="{F124AE04-B447-4F21-A0E8-7B26199C0F49}" name="%_sand_2"/>
     <tableColumn id="14" xr3:uid="{F119498A-3A35-40E3-A753-7CF13D724118}" name="%_clay_2"/>
     <tableColumn id="15" xr3:uid="{AE51522F-6903-42D4-88CE-A95BCE8C77EF}" name="BD_2"/>
     <tableColumn id="16" xr3:uid="{12076489-6AD7-4297-A729-20EF93AEE58D}" name="SOC_2"/>
+    <tableColumn id="72" xr3:uid="{42D67162-9319-4FDA-88FB-AA422F6D3CCD}" name="SOM_2"/>
     <tableColumn id="17" xr3:uid="{D6D5EFD4-69CC-4AF2-8C6B-0B430468C4C2}" name="FC_2"/>
-    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="40"/>
+    <tableColumn id="44" xr3:uid="{7158FD96-C69C-40D1-A3B8-2D043DF66D42}" name="FC_2_unit" dataDxfId="53"/>
     <tableColumn id="18" xr3:uid="{BBF6A61D-2092-4DF7-8C38-9024164291AE}" name="WP_2"/>
-    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="39"/>
+    <tableColumn id="45" xr3:uid="{2A662E87-2699-41FA-AF9F-C807E1C2112B}" name="WP_2_unit" dataDxfId="52"/>
     <tableColumn id="19" xr3:uid="{BB4B796C-CA3E-424C-87B0-4BF33581B61B}" name="initial_NO3_2"/>
-    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="38"/>
+    <tableColumn id="54" xr3:uid="{13CDB225-A28A-424D-943F-330A6ABE0CF2}" name="initial_NO3_2_unit" dataDxfId="51"/>
     <tableColumn id="55" xr3:uid="{333E59C3-3A13-4C92-9169-AC90D5E5D3EB}" name="initial_NH4_2"/>
-    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="37"/>
-    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="36"/>
-    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="35"/>
+    <tableColumn id="20" xr3:uid="{613F6ECB-AFEC-4E8A-BD78-2579E90B1783}" name="initial_NH4_2_unit" dataDxfId="50"/>
+    <tableColumn id="83" xr3:uid="{B3931D04-574E-4ED5-83CE-57CB3EE9124C}" name="pebble_content_2" dataDxfId="49"/>
+    <tableColumn id="84" xr3:uid="{56BD5168-04EF-4DF7-B946-BD707AA4366B}" name="pebble_type_2" dataDxfId="48"/>
     <tableColumn id="21" xr3:uid="{5D7B3549-7F90-410E-90FF-149F4376EBB7}" name="thickness_3"/>
     <tableColumn id="22" xr3:uid="{6C917DE4-8D95-496E-A6F1-EAB7450774EE}" name="%_sand_3"/>
     <tableColumn id="23" xr3:uid="{90DE7FE2-3A23-4294-8BD0-2D321FF71179}" name="%_clay_3"/>
     <tableColumn id="24" xr3:uid="{C874CBBB-CB06-4239-AE9B-72564A3EDC14}" name="BD_3"/>
     <tableColumn id="25" xr3:uid="{49CED3FB-E83C-4973-A99D-DAC6B3AFC7B1}" name="SOC_3"/>
     <tableColumn id="26" xr3:uid="{63FB3901-EBED-4379-9E9C-83064A8ADD01}" name="FC_3"/>
-    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="34"/>
+    <tableColumn id="47" xr3:uid="{5C201AAC-779E-4362-9603-51762D2AD5CF}" name="FC_3_unit" dataDxfId="47"/>
     <tableColumn id="27" xr3:uid="{6EEACF0E-3934-49DF-9991-42C2DB718BE0}" name="WP_3"/>
-    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="33"/>
+    <tableColumn id="48" xr3:uid="{67EEF171-24DC-4B50-B1F4-746B04E8F368}" name="WP_3_unit" dataDxfId="46"/>
     <tableColumn id="28" xr3:uid="{7AAE3F1E-C60E-4E11-A023-F09548D5AA39}" name="initial_NO3_3"/>
-    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="32"/>
+    <tableColumn id="56" xr3:uid="{2B23B0A6-3617-432B-8EEA-E2AC0892F317}" name="initial_NO3_3_unit" dataDxfId="45"/>
     <tableColumn id="57" xr3:uid="{1D0A3587-38DB-4073-B5D4-36DA82425955}" name="initial_NH4_3"/>
-    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="31"/>
-    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="30"/>
-    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="29"/>
-    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="28"/>
+    <tableColumn id="29" xr3:uid="{4BF74EC8-B9F2-42F0-AA7F-7CF70391A1FD}" name="initial_NH4_3_unit" dataDxfId="44"/>
+    <tableColumn id="85" xr3:uid="{1BBC38F8-EB0B-4F2E-B484-2F9729DE851E}" name="pebble_content_3" dataDxfId="43"/>
+    <tableColumn id="86" xr3:uid="{A9C249B2-4A59-44BD-9F5A-33BF44B91B02}" name="pebble_type_3" dataDxfId="42"/>
+    <tableColumn id="30" xr3:uid="{4F55D6E9-95FD-4FC3-8012-EBB0DDAD9C3D}" name="thickness_4" dataDxfId="41"/>
     <tableColumn id="31" xr3:uid="{4C1178FA-055B-4F19-A181-638D37A24EB6}" name="%_sand_4"/>
     <tableColumn id="32" xr3:uid="{7BBFA3FD-BBE5-4B68-A551-EFDEA7062540}" name="%_clay_4"/>
     <tableColumn id="33" xr3:uid="{D0607A27-FB9E-4DA9-A7F3-7A932B2608A4}" name="BD_4"/>
     <tableColumn id="34" xr3:uid="{BD46131F-AB56-411A-8742-B77FBBE1967B}" name="SOC_4"/>
     <tableColumn id="35" xr3:uid="{EC2EEDB8-3CC6-4DEE-9309-DBA3B11A2D16}" name="FC_4"/>
-    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="27"/>
-    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="26"/>
-    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="25"/>
-    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="24"/>
-    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="23"/>
-    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="22"/>
-    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="21"/>
-    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="20"/>
-    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="19"/>
+    <tableColumn id="50" xr3:uid="{D1D16E63-48A7-4CF1-950A-55FD748CC035}" name="FC_4_unit" dataDxfId="40"/>
+    <tableColumn id="36" xr3:uid="{2FE3E094-F831-4B6A-8F68-958367A1890E}" name="WP_4" dataDxfId="39"/>
+    <tableColumn id="51" xr3:uid="{FDA92DA7-3473-43EC-9CF7-2973FA9CC4D4}" name="WP_4_unit" dataDxfId="38"/>
+    <tableColumn id="58" xr3:uid="{BE460051-3822-4F7B-9128-B9FF3E679D50}" name="initial_NO3_4" dataDxfId="37"/>
+    <tableColumn id="37" xr3:uid="{8064862C-F8DC-4543-B5CF-D282DD564B1D}" name="initial_NO3_4_unit" dataDxfId="36"/>
+    <tableColumn id="59" xr3:uid="{17C5A0C3-B5F4-4AAB-876C-FC876098B9C8}" name="initial_NH4_4" dataDxfId="35"/>
+    <tableColumn id="38" xr3:uid="{251884D5-BA16-4F6E-89D1-06011C0ABD02}" name="initial_NH4_4_unit" dataDxfId="34"/>
+    <tableColumn id="88" xr3:uid="{736E60F4-CF72-45E6-879D-78A8A9925631}" name="pebble_content_4" dataDxfId="33"/>
+    <tableColumn id="87" xr3:uid="{CB23031C-85D6-4671-B76C-C909E04C419F}" name="pebble_type_4" dataDxfId="32"/>
     <tableColumn id="46" xr3:uid="{5545ADBB-3E57-4FCE-9979-330500D810A6}" name="thickness_5"/>
     <tableColumn id="49" xr3:uid="{28F4610E-A232-42D7-866E-B72AB5FC38D8}" name="%_sand_5"/>
     <tableColumn id="60" xr3:uid="{9557F7B0-0944-4CA4-8B86-630B4073480C}" name="%_clay_5"/>
     <tableColumn id="61" xr3:uid="{6977D0A0-E571-46FB-8186-DF22D992C4B6}" name="BD_5"/>
     <tableColumn id="62" xr3:uid="{762BF513-B3A9-4714-B788-A74D32CD414B}" name="SOC_5"/>
     <tableColumn id="63" xr3:uid="{F840DA58-F957-445A-8704-4823DC13AEC7}" name="FC_5"/>
-    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="18"/>
+    <tableColumn id="64" xr3:uid="{47AF2E86-82B6-4018-9B34-1B9AA21CC4AF}" name="FC_5_unit" dataDxfId="31"/>
     <tableColumn id="65" xr3:uid="{73133DDD-77CC-4B8F-AF63-0B5537B95DE3}" name="WP_5"/>
-    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="17"/>
+    <tableColumn id="66" xr3:uid="{7CB1FDF0-326D-4446-9AAC-1DB26A38AAB4}" name="WP_5_unit" dataDxfId="30"/>
     <tableColumn id="67" xr3:uid="{AF697735-FE14-47A1-8029-532D47D2E5C7}" name="initial_NO3_5"/>
-    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="16"/>
-    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="15"/>
-    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="14"/>
-    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="13"/>
-    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="12"/>
+    <tableColumn id="68" xr3:uid="{B9420E91-6BD4-467A-B4C2-A6E2DEAE7AC0}" name="initial_NO3_5_unit" dataDxfId="29"/>
+    <tableColumn id="69" xr3:uid="{FF6305CB-A38F-4242-9850-7966AD42A38B}" name="initial_NH4_5" dataDxfId="28"/>
+    <tableColumn id="70" xr3:uid="{B5EFBF0D-28C6-43EC-8EBE-8FDCF2F3F407}" name="initial_NH4_5_unit" dataDxfId="27"/>
+    <tableColumn id="89" xr3:uid="{B13F724D-C73F-487A-9E3C-B17193C097FC}" name="pebble_content_5" dataDxfId="26"/>
+    <tableColumn id="90" xr3:uid="{252511C5-2E5F-4622-871D-B38CFE14B781}" name="pebble_type_5" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}" name="Table5" displayName="Table5" ref="A1:E109" totalsRowShown="0" headerRowBorderDxfId="14" tableBorderDxfId="13">
   <autoFilter ref="A1:E109" xr:uid="{16C387FE-1D31-45D4-9107-29718893990C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{9BCD565A-9AEA-41E2-A4E9-5770EC475FD6}" name="station_name" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{2FFE488A-7A94-4C6D-BFBF-9D19F7354A7D}" name="latitude" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{7A348C5F-5ECA-4DC4-9498-87CB7828B623}" name="PET_calculation" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{528CFAC7-D6A1-4BF3-A218-92AEE6E73C93}" name="average_windspeed" dataDxfId="9"/>
     <tableColumn id="5" xr3:uid="{25C187AA-B7AD-4009-9499-173271E0B34E}" name="unit"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2040,31 +2048,31 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:I100" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}" name="Table8" displayName="Table8" ref="A2:I100" totalsRowShown="0" headerRowBorderDxfId="8" tableBorderDxfId="7">
   <autoFilter ref="A2:I100" xr:uid="{0F5B8E89-2F05-4CC0-ACA9-79A38A5A9857}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{524AE2E3-B113-41B0-849D-8331462FB910}" name="usm_name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{C58B90D4-B75A-409B-9D58-E09932ABF65C}" name="simulation_start"/>
-    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{DDB99A97-7CAB-4C4A-87B0-F44791A69661}" name="simulation_end" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{CA3AF775-2448-4D7D-9193-B5BBEE39AD09}" name="management_file_name" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{C4CB74A7-2660-4D67-9D08-D7802D112D6D}" name="soil_profile_name"/>
     <tableColumn id="6" xr3:uid="{EE8564A9-D685-42B6-914D-B5F77F840B11}" name="weather_station_name"/>
     <tableColumn id="7" xr3:uid="{DF70C6E4-2795-4D3D-B86B-8B48BE8FB3E1}" name="plant_file"/>
     <tableColumn id="9" xr3:uid="{BDB57316-D9C6-4EE3-821F-F5561E0078D9}" name="first_year"/>
-    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{733885B2-6768-4BD5-9F65-4E7F4F6262F5}" name="last_year" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}" name="Table10" displayName="Table10" ref="A1:F30" totalsRowShown="0" headerRowBorderDxfId="2">
   <autoFilter ref="A1:F30" xr:uid="{16A01ECA-7371-41CC-818F-9452134FC132}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{F945B708-1D60-4D2B-99F2-60E35ECBDB15}" name="usm_name" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{A5156817-2D3F-4E14-AC57-75BA66E12293}" name="year"/>
     <tableColumn id="3" xr3:uid="{173E3383-07EB-425D-884F-01E4ECFF4626}" name="month"/>
-    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{786A5374-97E3-4942-B27A-E7E524EC0BA1}" name="day" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{B9B2B184-EF64-48EF-B50B-8E24249DFDCC}" name="lai"/>
     <tableColumn id="7" xr3:uid="{ED0F5D28-DB43-4C9B-ADB2-1706AC6D61F9}" name="pdffruitfrais"/>
   </tableColumns>
@@ -2433,31 +2441,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67" t="s">
+      <c r="D1" s="70"/>
+      <c r="E1" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="69" t="s">
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="68" t="s">
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q1" s="70"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q1" s="67"/>
       <c r="R1" s="71" t="s">
         <v>102</v>
       </c>
@@ -2541,19 +2549,19 @@
         <v>58</v>
       </c>
       <c r="P2" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q2" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="Q2" s="63" t="s">
+      <c r="R2" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="R2" s="64" t="s">
+      <c r="S2" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="S2" s="33" t="s">
-        <v>186</v>
-      </c>
       <c r="T2" s="64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U2" s="11" t="s">
         <v>72</v>
@@ -2648,7 +2656,7 @@
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -2672,10 +2680,10 @@
         <v>120</v>
       </c>
       <c r="M3" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N3" s="34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6">
         <v>20</v>
@@ -2691,7 +2699,7 @@
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C4" s="59">
         <v>46172</v>
@@ -2724,10 +2732,10 @@
         <v>180</v>
       </c>
       <c r="M4" s="34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P4">
         <v>260</v>
@@ -2739,7 +2747,7 @@
         <v>90</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -2754,7 +2762,7 @@
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>106</v>
@@ -2787,10 +2795,10 @@
         <v>200</v>
       </c>
       <c r="M5" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N5" s="34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O5" s="6">
         <v>15</v>
@@ -2799,7 +2807,7 @@
         <v>80</v>
       </c>
       <c r="S5" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U5">
         <v>146</v>
@@ -3431,7 +3439,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:CH100"/>
+  <dimension ref="A1:CJ100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" style="5" customWidth="1"/>
@@ -3463,69 +3471,69 @@
     <col min="76" max="76" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="C1" s="70" t="s">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="C1" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="72" t="s">
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="68" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="67" t="s">
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="68"/>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="67"/>
-      <c r="AG1" s="67"/>
-      <c r="AH1" s="67"/>
-      <c r="AI1" s="67"/>
-      <c r="AJ1" s="67"/>
-      <c r="AK1" s="67"/>
-      <c r="AL1" s="67"/>
-      <c r="AM1" s="67"/>
-      <c r="AN1" s="67"/>
-      <c r="AO1" s="67"/>
-      <c r="AP1" s="66" t="s">
+      <c r="AB1" s="69"/>
+      <c r="AC1" s="69"/>
+      <c r="AD1" s="69"/>
+      <c r="AE1" s="69"/>
+      <c r="AF1" s="69"/>
+      <c r="AG1" s="69"/>
+      <c r="AH1" s="69"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AM1" s="69"/>
+      <c r="AN1" s="69"/>
+      <c r="AO1" s="69"/>
+      <c r="AP1" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="AQ1" s="66"/>
-      <c r="AR1" s="66"/>
-      <c r="AS1" s="66"/>
-      <c r="AT1" s="66"/>
-      <c r="AU1" s="66"/>
-      <c r="AV1" s="66"/>
-      <c r="AW1" s="66"/>
-      <c r="AX1" s="66"/>
-      <c r="AY1" s="66"/>
-      <c r="AZ1" s="66"/>
-      <c r="BA1" s="66"/>
-      <c r="BB1" s="66"/>
-      <c r="BC1" s="66"/>
-      <c r="BD1" s="66"/>
+      <c r="AQ1" s="70"/>
+      <c r="AR1" s="70"/>
+      <c r="AS1" s="70"/>
+      <c r="AT1" s="70"/>
+      <c r="AU1" s="70"/>
+      <c r="AV1" s="70"/>
+      <c r="AW1" s="70"/>
+      <c r="AX1" s="70"/>
+      <c r="AY1" s="70"/>
+      <c r="AZ1" s="70"/>
+      <c r="BA1" s="70"/>
+      <c r="BB1" s="70"/>
+      <c r="BC1" s="70"/>
+      <c r="BD1" s="70"/>
       <c r="BE1" s="71" t="s">
         <v>147</v>
       </c>
@@ -3543,25 +3551,25 @@
       <c r="BQ1" s="71"/>
       <c r="BR1" s="71"/>
       <c r="BS1" s="71"/>
-      <c r="BT1" s="73" t="s">
+      <c r="BT1" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="BU1" s="73"/>
-      <c r="BV1" s="73"/>
-      <c r="BW1" s="73"/>
-      <c r="BX1" s="73"/>
-      <c r="BY1" s="73"/>
-      <c r="BZ1" s="73"/>
-      <c r="CA1" s="73"/>
-      <c r="CB1" s="73"/>
-      <c r="CC1" s="73"/>
-      <c r="CD1" s="73"/>
-      <c r="CE1" s="73"/>
-      <c r="CF1" s="73"/>
-      <c r="CG1" s="73"/>
-      <c r="CH1" s="73"/>
-    </row>
-    <row r="2" spans="1:86" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="BU1" s="66"/>
+      <c r="BV1" s="66"/>
+      <c r="BW1" s="66"/>
+      <c r="BX1" s="66"/>
+      <c r="BY1" s="66"/>
+      <c r="BZ1" s="66"/>
+      <c r="CA1" s="66"/>
+      <c r="CB1" s="66"/>
+      <c r="CC1" s="66"/>
+      <c r="CD1" s="66"/>
+      <c r="CE1" s="66"/>
+      <c r="CF1" s="66"/>
+      <c r="CG1" s="66"/>
+      <c r="CH1" s="66"/>
+    </row>
+    <row r="2" spans="1:88" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
@@ -3572,7 +3580,7 @@
         <v>149</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E2" s="46" t="s">
         <v>150</v>
@@ -3605,225 +3613,231 @@
         <v>104</v>
       </c>
       <c r="O2" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="P2" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="P2" s="24" t="s">
-        <v>192</v>
-      </c>
       <c r="Q2" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="R2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="S2" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="T2" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="U2" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="U2" s="24" t="s">
+      <c r="V2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="W2" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="X2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="Y2" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Y2" s="26" t="s">
+      <c r="Z2" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="AA2" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="27" t="s">
+      <c r="AD2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AE2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AF2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AG2" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="AH2" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="AG2" s="22" t="s">
+      <c r="AI2" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="AH2" s="27" t="s">
+      <c r="AJ2" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="AI2" s="22" t="s">
+      <c r="AK2" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="AJ2" s="27" t="s">
+      <c r="AL2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AK2" s="22" t="s">
+      <c r="AM2" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="AL2" s="27" t="s">
+      <c r="AN2" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="AM2" s="53" t="s">
+      <c r="AO2" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="AN2" s="58" t="s">
+      <c r="AP2" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="AO2" s="57" t="s">
+      <c r="AQ2" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="AP2" s="28" t="s">
+      <c r="AR2" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="AQ2" s="28" t="s">
+      <c r="AS2" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="AR2" s="28" t="s">
+      <c r="AT2" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="AS2" s="28" t="s">
+      <c r="AU2" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="AT2" s="28" t="s">
+      <c r="AV2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="AU2" s="28" t="s">
+      <c r="AW2" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="AV2" s="30" t="s">
+      <c r="AX2" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AW2" s="28" t="s">
+      <c r="AY2" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="AX2" s="30" t="s">
+      <c r="AZ2" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="28" t="s">
+      <c r="BA2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BB2" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="BA2" s="28" t="s">
+      <c r="BC2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="BB2" s="52" t="s">
+      <c r="BD2" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="BC2" s="29" t="s">
+      <c r="BE2" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="BD2" s="31" t="s">
+      <c r="BF2" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="BE2" s="32" t="s">
+      <c r="BG2" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="BF2" s="32" t="s">
+      <c r="BH2" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BI2" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="BH2" s="32" t="s">
+      <c r="BJ2" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="BI2" s="32" t="s">
+      <c r="BK2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="BJ2" s="32" t="s">
+      <c r="BL2" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="BK2" s="33" t="s">
+      <c r="BM2" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="BL2" s="32" t="s">
+      <c r="BN2" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="BM2" s="33" t="s">
+      <c r="BO2" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="BN2" s="32" t="s">
+      <c r="BP2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="BO2" s="33" t="s">
+      <c r="BQ2" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="BP2" s="32" t="s">
+      <c r="BR2" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="BQ2" s="50" t="s">
+      <c r="BS2" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="BR2" s="54" t="s">
+      <c r="BT2" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="BS2" s="55" t="s">
+      <c r="BU2" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="BT2" s="38" t="s">
+      <c r="BV2" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="BU2" s="39" t="s">
+      <c r="BW2" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="BV2" s="39" t="s">
+      <c r="BX2" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="BW2" s="39" t="s">
+      <c r="BY2" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="BX2" s="39" t="s">
+      <c r="BZ2" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="BY2" s="39" t="s">
+      <c r="CA2" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="BZ2" s="40" t="s">
+      <c r="CB2" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="CA2" s="39" t="s">
+      <c r="CC2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="CB2" s="40" t="s">
+      <c r="CD2" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="CC2" s="39" t="s">
+      <c r="CE2" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="CD2" s="40" t="s">
+      <c r="CF2" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="CE2" s="39" t="s">
+      <c r="CG2" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="CF2" s="51" t="s">
+      <c r="CH2" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="CG2" s="39" t="s">
+      <c r="CI2" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="CH2" s="56" t="s">
+      <c r="CJ2" s="56" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3" s="48">
         <v>0.25</v>
@@ -3852,220 +3866,224 @@
       <c r="N3">
         <v>10</v>
       </c>
-      <c r="Q3">
+      <c r="O3">
+        <v>14</v>
+      </c>
+      <c r="R3">
         <v>30</v>
       </c>
-      <c r="R3" s="34" t="s">
+      <c r="S3" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>15</v>
       </c>
-      <c r="T3" s="34" t="s">
+      <c r="U3" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>1.8</v>
       </c>
-      <c r="V3" s="34" t="s">
+      <c r="W3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>0</v>
       </c>
-      <c r="X3" s="34" t="s">
+      <c r="Y3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>20</v>
       </c>
-      <c r="Z3" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA3">
+      <c r="AA3" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB3">
         <v>20</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>40</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>50</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>1.08</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>30</v>
       </c>
-      <c r="AF3">
+      <c r="AG3"/>
+      <c r="AH3">
         <v>18</v>
-      </c>
-      <c r="AG3" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="AH3">
-        <v>15</v>
       </c>
       <c r="AI3" s="34" t="s">
         <v>116</v>
       </c>
       <c r="AJ3">
+        <v>15</v>
+      </c>
+      <c r="AK3" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL3">
         <v>0.5</v>
       </c>
-      <c r="AK3" s="34" t="s">
+      <c r="AM3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="AL3">
+      <c r="AN3">
         <v>0</v>
       </c>
-      <c r="AM3" s="34" t="s">
+      <c r="AO3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="AN3">
+      <c r="AP3">
         <v>40</v>
       </c>
-      <c r="AO3" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="AP3">
+      <c r="AQ3" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AR3">
         <v>20</v>
       </c>
-      <c r="AQ3">
+      <c r="AS3">
         <v>40</v>
       </c>
-      <c r="AR3">
+      <c r="AT3">
         <v>50</v>
       </c>
-      <c r="AS3">
+      <c r="AU3">
         <v>1.08</v>
       </c>
-      <c r="AT3">
+      <c r="AV3">
         <v>30</v>
       </c>
-      <c r="AU3">
+      <c r="AW3">
         <v>18</v>
-      </c>
-      <c r="AV3" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="AW3">
-        <v>15</v>
       </c>
       <c r="AX3" s="34" t="s">
         <v>116</v>
       </c>
       <c r="AY3">
+        <v>15</v>
+      </c>
+      <c r="AZ3" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA3">
         <v>0.5</v>
       </c>
-      <c r="AZ3" s="34" t="s">
+      <c r="BB3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BA3">
+      <c r="BC3">
         <v>0</v>
       </c>
-      <c r="BB3" s="34" t="s">
+      <c r="BD3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="BC3">
+      <c r="BE3">
         <v>40</v>
       </c>
-      <c r="BD3" s="65" t="s">
+      <c r="BF3" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="BE3">
+      <c r="BG3">
         <v>20</v>
       </c>
-      <c r="BF3">
+      <c r="BH3">
         <v>40</v>
       </c>
-      <c r="BG3">
+      <c r="BI3">
         <v>50</v>
       </c>
-      <c r="BH3">
+      <c r="BJ3">
         <v>1.08</v>
       </c>
-      <c r="BI3">
+      <c r="BK3">
         <v>30</v>
       </c>
-      <c r="BJ3">
+      <c r="BL3">
         <v>18</v>
-      </c>
-      <c r="BK3" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="BL3">
-        <v>15</v>
       </c>
       <c r="BM3" s="34" t="s">
         <v>116</v>
       </c>
       <c r="BN3">
+        <v>15</v>
+      </c>
+      <c r="BO3" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="BP3">
         <v>0.5</v>
       </c>
-      <c r="BO3" s="34" t="s">
+      <c r="BQ3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BP3">
+      <c r="BR3">
         <v>0</v>
       </c>
-      <c r="BQ3" s="34" t="s">
+      <c r="BS3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="BR3">
+      <c r="BT3">
         <v>40</v>
       </c>
-      <c r="BS3" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="BT3">
+      <c r="BU3" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="BV3">
         <v>20</v>
       </c>
-      <c r="BU3">
+      <c r="BW3">
         <v>40</v>
       </c>
-      <c r="BV3">
+      <c r="BX3">
         <v>50</v>
       </c>
-      <c r="BW3">
+      <c r="BY3">
         <v>1.08</v>
       </c>
-      <c r="BX3">
+      <c r="BZ3">
         <v>30</v>
       </c>
-      <c r="BY3">
+      <c r="CA3">
         <v>18</v>
-      </c>
-      <c r="BZ3" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="CA3">
-        <v>15</v>
       </c>
       <c r="CB3" s="34" t="s">
         <v>116</v>
       </c>
       <c r="CC3">
+        <v>15</v>
+      </c>
+      <c r="CD3" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="CE3">
         <v>0.5</v>
       </c>
-      <c r="CD3" s="34" t="s">
+      <c r="CF3" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="CE3">
+      <c r="CG3">
         <v>0</v>
       </c>
-      <c r="CF3" s="34" t="s">
+      <c r="CH3" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="CG3">
+      <c r="CI3">
         <v>40</v>
       </c>
-      <c r="CH3" s="34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.3">
+      <c r="CJ3" s="34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:88" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="48">
         <v>0.25</v>
@@ -4103,2944 +4121,3354 @@
       <c r="N4">
         <v>0.5</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>11.25</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>20</v>
       </c>
-      <c r="R4" s="34" t="s">
+      <c r="S4" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>10</v>
       </c>
-      <c r="T4" s="34" t="s">
+      <c r="U4" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>9</v>
       </c>
-      <c r="V4" s="34" t="s">
+      <c r="W4" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>8</v>
       </c>
-      <c r="X4" s="34" t="s">
+      <c r="Y4" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="Z4" s="37"/>
-      <c r="AA4">
+      <c r="Z4"/>
+      <c r="AA4" s="37"/>
+      <c r="AB4">
         <v>30</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>70</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>5</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>0.95</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>10</v>
       </c>
-      <c r="AF4">
+      <c r="AG4"/>
+      <c r="AH4">
         <v>20</v>
-      </c>
-      <c r="AG4" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="AH4">
-        <v>9</v>
       </c>
       <c r="AI4" s="34" t="s">
         <v>115</v>
       </c>
       <c r="AJ4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AK4" s="34" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="AL4">
         <v>2</v>
       </c>
       <c r="AM4" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN4">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="AO4" s="37"/>
-      <c r="AP4">
+      <c r="AQ4" s="37"/>
+      <c r="AR4">
         <v>30</v>
       </c>
-      <c r="AQ4">
+      <c r="AS4">
         <v>70</v>
       </c>
-      <c r="AR4">
+      <c r="AT4">
         <v>5</v>
       </c>
-      <c r="AS4">
+      <c r="AU4">
         <v>0.95</v>
       </c>
-      <c r="AT4">
+      <c r="AV4">
         <v>10</v>
       </c>
-      <c r="AU4">
+      <c r="AW4">
         <v>20</v>
-      </c>
-      <c r="AV4" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW4">
-        <v>9</v>
       </c>
       <c r="AX4" s="34" t="s">
         <v>115</v>
       </c>
       <c r="AY4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AZ4" s="34" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="BA4">
         <v>2</v>
       </c>
       <c r="BB4" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="BC4">
+        <v>2</v>
+      </c>
+      <c r="BD4" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BD4" s="37"/>
-      <c r="BE4">
+      <c r="BF4" s="37"/>
+      <c r="BG4">
         <v>30</v>
       </c>
-      <c r="BF4">
+      <c r="BH4">
         <v>70</v>
       </c>
-      <c r="BG4">
+      <c r="BI4">
         <v>5</v>
       </c>
-      <c r="BH4">
+      <c r="BJ4">
         <v>0.95</v>
       </c>
-      <c r="BI4">
+      <c r="BK4">
         <v>10</v>
       </c>
-      <c r="BJ4">
+      <c r="BL4">
         <v>20</v>
-      </c>
-      <c r="BK4" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="BL4">
-        <v>9</v>
       </c>
       <c r="BM4" s="34" t="s">
         <v>115</v>
       </c>
       <c r="BN4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BO4" s="34" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="BP4">
         <v>2</v>
       </c>
       <c r="BQ4" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR4">
+        <v>2</v>
+      </c>
+      <c r="BS4" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="BS4" s="37"/>
+      <c r="BU4" s="37"/>
       <c r="BX4"/>
-      <c r="BZ4" s="34"/>
       <c r="CB4" s="34"/>
       <c r="CD4" s="34"/>
       <c r="CF4" s="34"/>
       <c r="CH4" s="34"/>
-    </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="V5" s="34"/>
-      <c r="X5" s="34"/>
-      <c r="Z5" s="37"/>
-      <c r="AG5" s="34"/>
+      <c r="CJ4" s="34"/>
+    </row>
+    <row r="5" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="48">
+        <v>0.25</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>5.6</v>
+      </c>
+      <c r="I5">
+        <v>38</v>
+      </c>
+      <c r="J5">
+        <v>24</v>
+      </c>
+      <c r="M5">
+        <v>50</v>
+      </c>
+      <c r="O5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5"/>
+      <c r="AA5" s="37"/>
+      <c r="AG5"/>
       <c r="AI5" s="34"/>
       <c r="AK5" s="34"/>
       <c r="AM5" s="34"/>
-      <c r="AO5" s="37"/>
-      <c r="AV5" s="34"/>
+      <c r="AO5" s="34"/>
+      <c r="AQ5" s="37"/>
+      <c r="AV5"/>
       <c r="AX5" s="34"/>
       <c r="AZ5" s="34"/>
       <c r="BB5" s="34"/>
       <c r="BD5" s="34"/>
-      <c r="BE5" s="19"/>
-      <c r="BK5" s="34"/>
+      <c r="BF5" s="34"/>
+      <c r="BG5" s="19"/>
+      <c r="BK5"/>
       <c r="BM5" s="34"/>
       <c r="BO5" s="34"/>
       <c r="BQ5" s="34"/>
-      <c r="BS5" s="37"/>
+      <c r="BS5" s="34"/>
+      <c r="BU5" s="37"/>
       <c r="BX5"/>
-      <c r="BZ5" s="34"/>
       <c r="CB5" s="34"/>
       <c r="CD5" s="34"/>
       <c r="CF5" s="34"/>
       <c r="CH5" s="34"/>
-    </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="X6" s="34"/>
-      <c r="Z6" s="37"/>
-      <c r="AG6" s="34"/>
+      <c r="CJ5" s="34"/>
+    </row>
+    <row r="6" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6"/>
+      <c r="AA6" s="37"/>
+      <c r="AG6"/>
       <c r="AI6" s="34"/>
       <c r="AK6" s="34"/>
       <c r="AM6" s="34"/>
-      <c r="AO6" s="37"/>
-      <c r="AV6" s="34"/>
+      <c r="AO6" s="34"/>
+      <c r="AQ6" s="37"/>
+      <c r="AV6"/>
       <c r="AX6" s="34"/>
       <c r="AZ6" s="34"/>
       <c r="BB6" s="34"/>
       <c r="BD6" s="34"/>
-      <c r="BE6" s="19"/>
-      <c r="BK6" s="34"/>
+      <c r="BF6" s="34"/>
+      <c r="BG6" s="19"/>
+      <c r="BK6"/>
       <c r="BM6" s="34"/>
       <c r="BO6" s="34"/>
       <c r="BQ6" s="34"/>
-      <c r="BS6" s="37"/>
+      <c r="BS6" s="34"/>
+      <c r="BU6" s="37"/>
       <c r="BX6"/>
-      <c r="BZ6" s="34"/>
       <c r="CB6" s="34"/>
       <c r="CD6" s="34"/>
       <c r="CF6" s="34"/>
       <c r="CH6" s="34"/>
-    </row>
-    <row r="7" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Z7" s="37"/>
-      <c r="AG7" s="34"/>
+      <c r="CJ6" s="34"/>
+    </row>
+    <row r="7" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="W7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7"/>
+      <c r="AA7" s="37"/>
+      <c r="AG7"/>
       <c r="AI7" s="34"/>
       <c r="AK7" s="34"/>
       <c r="AM7" s="34"/>
-      <c r="AO7" s="37"/>
-      <c r="AV7" s="34"/>
+      <c r="AO7" s="34"/>
+      <c r="AQ7" s="37"/>
+      <c r="AV7"/>
       <c r="AX7" s="34"/>
       <c r="AZ7" s="34"/>
       <c r="BB7" s="34"/>
       <c r="BD7" s="34"/>
-      <c r="BE7" s="19"/>
-      <c r="BK7" s="34"/>
+      <c r="BF7" s="34"/>
+      <c r="BG7" s="19"/>
+      <c r="BK7"/>
       <c r="BM7" s="34"/>
       <c r="BO7" s="34"/>
       <c r="BQ7" s="34"/>
-      <c r="BS7" s="37"/>
+      <c r="BS7" s="34"/>
+      <c r="BU7" s="37"/>
       <c r="BX7"/>
-      <c r="BZ7" s="34"/>
       <c r="CB7" s="34"/>
       <c r="CD7" s="34"/>
       <c r="CF7" s="34"/>
       <c r="CH7" s="34"/>
-    </row>
-    <row r="8" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="X8" s="34"/>
-      <c r="Z8" s="37"/>
-      <c r="AG8" s="34"/>
+      <c r="CJ7" s="34"/>
+    </row>
+    <row r="8" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8"/>
+      <c r="AA8" s="37"/>
+      <c r="AG8"/>
       <c r="AI8" s="34"/>
       <c r="AK8" s="34"/>
       <c r="AM8" s="34"/>
-      <c r="AO8" s="37"/>
-      <c r="AV8" s="34"/>
+      <c r="AO8" s="34"/>
+      <c r="AQ8" s="37"/>
+      <c r="AV8"/>
       <c r="AX8" s="34"/>
       <c r="AZ8" s="34"/>
       <c r="BB8" s="34"/>
       <c r="BD8" s="34"/>
-      <c r="BE8" s="19"/>
-      <c r="BK8" s="34"/>
+      <c r="BF8" s="34"/>
+      <c r="BG8" s="19"/>
+      <c r="BK8"/>
       <c r="BM8" s="34"/>
       <c r="BO8" s="34"/>
       <c r="BQ8" s="34"/>
-      <c r="BS8" s="37"/>
+      <c r="BS8" s="34"/>
+      <c r="BU8" s="37"/>
       <c r="BX8"/>
-      <c r="BZ8" s="34"/>
       <c r="CB8" s="34"/>
       <c r="CD8" s="34"/>
       <c r="CF8" s="34"/>
       <c r="CH8" s="34"/>
-    </row>
-    <row r="9" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Z9" s="37"/>
-      <c r="AG9" s="34"/>
+      <c r="CJ8" s="34"/>
+    </row>
+    <row r="9" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9"/>
+      <c r="AA9" s="37"/>
+      <c r="AG9"/>
       <c r="AI9" s="34"/>
       <c r="AK9" s="34"/>
       <c r="AM9" s="34"/>
-      <c r="AO9" s="37"/>
-      <c r="AV9" s="34"/>
+      <c r="AO9" s="34"/>
+      <c r="AQ9" s="37"/>
+      <c r="AV9"/>
       <c r="AX9" s="34"/>
       <c r="AZ9" s="34"/>
       <c r="BB9" s="34"/>
       <c r="BD9" s="34"/>
-      <c r="BE9" s="19"/>
-      <c r="BK9" s="34"/>
+      <c r="BF9" s="34"/>
+      <c r="BG9" s="19"/>
+      <c r="BK9"/>
       <c r="BM9" s="34"/>
       <c r="BO9" s="34"/>
       <c r="BQ9" s="34"/>
-      <c r="BS9" s="37"/>
+      <c r="BS9" s="34"/>
+      <c r="BU9" s="37"/>
       <c r="BX9"/>
-      <c r="BZ9" s="34"/>
       <c r="CB9" s="34"/>
       <c r="CD9" s="34"/>
       <c r="CF9" s="34"/>
       <c r="CH9" s="34"/>
-    </row>
-    <row r="10" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="X10" s="34"/>
-      <c r="Z10" s="37"/>
-      <c r="AG10" s="34"/>
+      <c r="CJ9" s="34"/>
+    </row>
+    <row r="10" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S10" s="34"/>
+      <c r="U10" s="34"/>
+      <c r="W10" s="34"/>
+      <c r="Y10" s="34"/>
+      <c r="Z10"/>
+      <c r="AA10" s="37"/>
+      <c r="AG10"/>
       <c r="AI10" s="34"/>
       <c r="AK10" s="34"/>
       <c r="AM10" s="34"/>
-      <c r="AO10" s="37"/>
-      <c r="AV10" s="34"/>
+      <c r="AO10" s="34"/>
+      <c r="AQ10" s="37"/>
+      <c r="AV10"/>
       <c r="AX10" s="34"/>
       <c r="AZ10" s="34"/>
       <c r="BB10" s="34"/>
       <c r="BD10" s="34"/>
-      <c r="BE10" s="19"/>
-      <c r="BK10" s="34"/>
+      <c r="BF10" s="34"/>
+      <c r="BG10" s="19"/>
+      <c r="BK10"/>
       <c r="BM10" s="34"/>
       <c r="BO10" s="34"/>
       <c r="BQ10" s="34"/>
-      <c r="BS10" s="37"/>
+      <c r="BS10" s="34"/>
+      <c r="BU10" s="37"/>
       <c r="BX10"/>
-      <c r="BZ10" s="34"/>
       <c r="CB10" s="34"/>
       <c r="CD10" s="34"/>
       <c r="CF10" s="34"/>
       <c r="CH10" s="34"/>
-    </row>
-    <row r="11" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Z11" s="37"/>
-      <c r="AG11" s="34"/>
+      <c r="CJ10" s="34"/>
+    </row>
+    <row r="11" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S11" s="34"/>
+      <c r="U11" s="34"/>
+      <c r="W11" s="34"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11"/>
+      <c r="AA11" s="37"/>
+      <c r="AG11"/>
       <c r="AI11" s="34"/>
       <c r="AK11" s="34"/>
       <c r="AM11" s="34"/>
-      <c r="AO11" s="37"/>
-      <c r="AV11" s="34"/>
+      <c r="AO11" s="34"/>
+      <c r="AQ11" s="37"/>
+      <c r="AV11"/>
       <c r="AX11" s="34"/>
       <c r="AZ11" s="34"/>
       <c r="BB11" s="34"/>
       <c r="BD11" s="34"/>
-      <c r="BE11" s="19"/>
-      <c r="BK11" s="34"/>
+      <c r="BF11" s="34"/>
+      <c r="BG11" s="19"/>
+      <c r="BK11"/>
       <c r="BM11" s="34"/>
       <c r="BO11" s="34"/>
       <c r="BQ11" s="34"/>
-      <c r="BS11" s="37"/>
+      <c r="BS11" s="34"/>
+      <c r="BU11" s="37"/>
       <c r="BX11"/>
-      <c r="BZ11" s="34"/>
       <c r="CB11" s="34"/>
       <c r="CD11" s="34"/>
       <c r="CF11" s="34"/>
       <c r="CH11" s="34"/>
-    </row>
-    <row r="12" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="X12" s="34"/>
-      <c r="Z12" s="37"/>
-      <c r="AG12" s="34"/>
+      <c r="CJ11" s="34"/>
+    </row>
+    <row r="12" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="W12" s="34"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12"/>
+      <c r="AA12" s="37"/>
+      <c r="AG12"/>
       <c r="AI12" s="34"/>
       <c r="AK12" s="34"/>
       <c r="AM12" s="34"/>
-      <c r="AO12" s="37"/>
-      <c r="AV12" s="34"/>
+      <c r="AO12" s="34"/>
+      <c r="AQ12" s="37"/>
+      <c r="AV12"/>
       <c r="AX12" s="34"/>
       <c r="AZ12" s="34"/>
       <c r="BB12" s="34"/>
       <c r="BD12" s="34"/>
-      <c r="BE12" s="19"/>
-      <c r="BK12" s="34"/>
+      <c r="BF12" s="34"/>
+      <c r="BG12" s="19"/>
+      <c r="BK12"/>
       <c r="BM12" s="34"/>
       <c r="BO12" s="34"/>
       <c r="BQ12" s="34"/>
-      <c r="BS12" s="37"/>
+      <c r="BS12" s="34"/>
+      <c r="BU12" s="37"/>
       <c r="BX12"/>
-      <c r="BZ12" s="34"/>
       <c r="CB12" s="34"/>
       <c r="CD12" s="34"/>
       <c r="CF12" s="34"/>
       <c r="CH12" s="34"/>
-    </row>
-    <row r="13" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="X13" s="34"/>
-      <c r="Z13" s="37"/>
-      <c r="AG13" s="34"/>
+      <c r="CJ12" s="34"/>
+    </row>
+    <row r="13" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S13" s="34"/>
+      <c r="U13" s="34"/>
+      <c r="W13" s="34"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13"/>
+      <c r="AA13" s="37"/>
+      <c r="AG13"/>
       <c r="AI13" s="34"/>
       <c r="AK13" s="34"/>
       <c r="AM13" s="34"/>
-      <c r="AO13" s="37"/>
-      <c r="AV13" s="34"/>
+      <c r="AO13" s="34"/>
+      <c r="AQ13" s="37"/>
+      <c r="AV13"/>
       <c r="AX13" s="34"/>
       <c r="AZ13" s="34"/>
       <c r="BB13" s="34"/>
       <c r="BD13" s="34"/>
-      <c r="BE13" s="19"/>
-      <c r="BK13" s="34"/>
+      <c r="BF13" s="34"/>
+      <c r="BG13" s="19"/>
+      <c r="BK13"/>
       <c r="BM13" s="34"/>
       <c r="BO13" s="34"/>
       <c r="BQ13" s="34"/>
-      <c r="BS13" s="37"/>
+      <c r="BS13" s="34"/>
+      <c r="BU13" s="37"/>
       <c r="BX13"/>
-      <c r="BZ13" s="34"/>
       <c r="CB13" s="34"/>
       <c r="CD13" s="34"/>
       <c r="CF13" s="34"/>
       <c r="CH13" s="34"/>
-    </row>
-    <row r="14" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="X14" s="34"/>
-      <c r="Z14" s="37"/>
-      <c r="AG14" s="34"/>
+      <c r="CJ13" s="34"/>
+    </row>
+    <row r="14" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S14" s="34"/>
+      <c r="U14" s="34"/>
+      <c r="W14" s="34"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14"/>
+      <c r="AA14" s="37"/>
+      <c r="AG14"/>
       <c r="AI14" s="34"/>
       <c r="AK14" s="34"/>
       <c r="AM14" s="34"/>
-      <c r="AO14" s="37"/>
-      <c r="AV14" s="34"/>
+      <c r="AO14" s="34"/>
+      <c r="AQ14" s="37"/>
+      <c r="AV14"/>
       <c r="AX14" s="34"/>
       <c r="AZ14" s="34"/>
       <c r="BB14" s="34"/>
       <c r="BD14" s="34"/>
-      <c r="BE14" s="19"/>
-      <c r="BK14" s="34"/>
+      <c r="BF14" s="34"/>
+      <c r="BG14" s="19"/>
+      <c r="BK14"/>
       <c r="BM14" s="34"/>
       <c r="BO14" s="34"/>
       <c r="BQ14" s="34"/>
-      <c r="BS14" s="37"/>
+      <c r="BS14" s="34"/>
+      <c r="BU14" s="37"/>
       <c r="BX14"/>
-      <c r="BZ14" s="34"/>
       <c r="CB14" s="34"/>
       <c r="CD14" s="34"/>
       <c r="CF14" s="34"/>
       <c r="CH14" s="34"/>
-    </row>
-    <row r="15" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="X15" s="34"/>
-      <c r="Z15" s="37"/>
-      <c r="AG15" s="34"/>
+      <c r="CJ14" s="34"/>
+    </row>
+    <row r="15" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="W15" s="34"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15"/>
+      <c r="AA15" s="37"/>
+      <c r="AG15"/>
       <c r="AI15" s="34"/>
       <c r="AK15" s="34"/>
       <c r="AM15" s="34"/>
-      <c r="AO15" s="37"/>
-      <c r="AV15" s="34"/>
+      <c r="AO15" s="34"/>
+      <c r="AQ15" s="37"/>
+      <c r="AV15"/>
       <c r="AX15" s="34"/>
       <c r="AZ15" s="34"/>
       <c r="BB15" s="34"/>
       <c r="BD15" s="34"/>
-      <c r="BE15" s="19"/>
-      <c r="BK15" s="34"/>
+      <c r="BF15" s="34"/>
+      <c r="BG15" s="19"/>
+      <c r="BK15"/>
       <c r="BM15" s="34"/>
       <c r="BO15" s="34"/>
       <c r="BQ15" s="34"/>
-      <c r="BS15" s="37"/>
+      <c r="BS15" s="34"/>
+      <c r="BU15" s="37"/>
       <c r="BX15"/>
-      <c r="BZ15" s="34"/>
       <c r="CB15" s="34"/>
       <c r="CD15" s="34"/>
       <c r="CF15" s="34"/>
       <c r="CH15" s="34"/>
-    </row>
-    <row r="16" spans="1:86" x14ac:dyDescent="0.3">
-      <c r="R16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Z16" s="37"/>
-      <c r="AG16" s="34"/>
+      <c r="CJ15" s="34"/>
+    </row>
+    <row r="16" spans="1:88" x14ac:dyDescent="0.3">
+      <c r="S16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16"/>
+      <c r="AA16" s="37"/>
+      <c r="AG16"/>
       <c r="AI16" s="34"/>
       <c r="AK16" s="34"/>
       <c r="AM16" s="34"/>
-      <c r="AO16" s="37"/>
-      <c r="AV16" s="34"/>
+      <c r="AO16" s="34"/>
+      <c r="AQ16" s="37"/>
+      <c r="AV16"/>
       <c r="AX16" s="34"/>
       <c r="AZ16" s="34"/>
       <c r="BB16" s="34"/>
       <c r="BD16" s="34"/>
-      <c r="BE16" s="19"/>
-      <c r="BK16" s="34"/>
+      <c r="BF16" s="34"/>
+      <c r="BG16" s="19"/>
+      <c r="BK16"/>
       <c r="BM16" s="34"/>
       <c r="BO16" s="34"/>
       <c r="BQ16" s="34"/>
-      <c r="BS16" s="37"/>
+      <c r="BS16" s="34"/>
+      <c r="BU16" s="37"/>
       <c r="BX16"/>
-      <c r="BZ16" s="34"/>
       <c r="CB16" s="34"/>
       <c r="CD16" s="34"/>
       <c r="CF16" s="34"/>
       <c r="CH16" s="34"/>
-    </row>
-    <row r="17" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Z17" s="37"/>
-      <c r="AG17" s="34"/>
+      <c r="CJ16" s="34"/>
+    </row>
+    <row r="17" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="W17" s="34"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17"/>
+      <c r="AA17" s="37"/>
+      <c r="AG17"/>
       <c r="AI17" s="34"/>
       <c r="AK17" s="34"/>
       <c r="AM17" s="34"/>
-      <c r="AO17" s="37"/>
-      <c r="AV17" s="34"/>
+      <c r="AO17" s="34"/>
+      <c r="AQ17" s="37"/>
+      <c r="AV17"/>
       <c r="AX17" s="34"/>
       <c r="AZ17" s="34"/>
       <c r="BB17" s="34"/>
       <c r="BD17" s="34"/>
-      <c r="BE17" s="19"/>
-      <c r="BK17" s="34"/>
+      <c r="BF17" s="34"/>
+      <c r="BG17" s="19"/>
+      <c r="BK17"/>
       <c r="BM17" s="34"/>
       <c r="BO17" s="34"/>
       <c r="BQ17" s="34"/>
-      <c r="BS17" s="37"/>
+      <c r="BS17" s="34"/>
+      <c r="BU17" s="37"/>
       <c r="BX17"/>
-      <c r="BZ17" s="34"/>
       <c r="CB17" s="34"/>
       <c r="CD17" s="34"/>
       <c r="CF17" s="34"/>
       <c r="CH17" s="34"/>
-    </row>
-    <row r="18" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Z18" s="37"/>
-      <c r="AG18" s="34"/>
+      <c r="CJ17" s="34"/>
+    </row>
+    <row r="18" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="W18" s="34"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18"/>
+      <c r="AA18" s="37"/>
+      <c r="AG18"/>
       <c r="AI18" s="34"/>
       <c r="AK18" s="34"/>
       <c r="AM18" s="34"/>
-      <c r="AO18" s="37"/>
-      <c r="AV18" s="34"/>
+      <c r="AO18" s="34"/>
+      <c r="AQ18" s="37"/>
+      <c r="AV18"/>
       <c r="AX18" s="34"/>
       <c r="AZ18" s="34"/>
       <c r="BB18" s="34"/>
       <c r="BD18" s="34"/>
-      <c r="BE18" s="19"/>
-      <c r="BK18" s="34"/>
+      <c r="BF18" s="34"/>
+      <c r="BG18" s="19"/>
+      <c r="BK18"/>
       <c r="BM18" s="34"/>
       <c r="BO18" s="34"/>
       <c r="BQ18" s="34"/>
-      <c r="BS18" s="37"/>
+      <c r="BS18" s="34"/>
+      <c r="BU18" s="37"/>
       <c r="BX18"/>
-      <c r="BZ18" s="34"/>
       <c r="CB18" s="34"/>
       <c r="CD18" s="34"/>
       <c r="CF18" s="34"/>
       <c r="CH18" s="34"/>
-    </row>
-    <row r="19" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Z19" s="37"/>
-      <c r="AG19" s="34"/>
+      <c r="CJ18" s="34"/>
+    </row>
+    <row r="19" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="W19" s="34"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19"/>
+      <c r="AA19" s="37"/>
+      <c r="AG19"/>
       <c r="AI19" s="34"/>
       <c r="AK19" s="34"/>
       <c r="AM19" s="34"/>
-      <c r="AO19" s="37"/>
-      <c r="AV19" s="34"/>
+      <c r="AO19" s="34"/>
+      <c r="AQ19" s="37"/>
+      <c r="AV19"/>
       <c r="AX19" s="34"/>
       <c r="AZ19" s="34"/>
       <c r="BB19" s="34"/>
       <c r="BD19" s="34"/>
-      <c r="BE19" s="19"/>
-      <c r="BK19" s="34"/>
+      <c r="BF19" s="34"/>
+      <c r="BG19" s="19"/>
+      <c r="BK19"/>
       <c r="BM19" s="34"/>
       <c r="BO19" s="34"/>
       <c r="BQ19" s="34"/>
-      <c r="BS19" s="37"/>
+      <c r="BS19" s="34"/>
+      <c r="BU19" s="37"/>
       <c r="BX19"/>
-      <c r="BZ19" s="34"/>
       <c r="CB19" s="34"/>
       <c r="CD19" s="34"/>
       <c r="CF19" s="34"/>
       <c r="CH19" s="34"/>
-    </row>
-    <row r="20" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Z20" s="37"/>
-      <c r="AG20" s="34"/>
+      <c r="CJ19" s="34"/>
+    </row>
+    <row r="20" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20"/>
+      <c r="AA20" s="37"/>
+      <c r="AG20"/>
       <c r="AI20" s="34"/>
       <c r="AK20" s="34"/>
       <c r="AM20" s="34"/>
-      <c r="AO20" s="37"/>
-      <c r="AV20" s="34"/>
+      <c r="AO20" s="34"/>
+      <c r="AQ20" s="37"/>
+      <c r="AV20"/>
       <c r="AX20" s="34"/>
       <c r="AZ20" s="34"/>
       <c r="BB20" s="34"/>
       <c r="BD20" s="34"/>
-      <c r="BE20" s="19"/>
-      <c r="BK20" s="34"/>
+      <c r="BF20" s="34"/>
+      <c r="BG20" s="19"/>
+      <c r="BK20"/>
       <c r="BM20" s="34"/>
       <c r="BO20" s="34"/>
       <c r="BQ20" s="34"/>
-      <c r="BS20" s="37"/>
+      <c r="BS20" s="34"/>
+      <c r="BU20" s="37"/>
       <c r="BX20"/>
-      <c r="BZ20" s="34"/>
       <c r="CB20" s="34"/>
       <c r="CD20" s="34"/>
       <c r="CF20" s="34"/>
       <c r="CH20" s="34"/>
-    </row>
-    <row r="21" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Z21" s="37"/>
-      <c r="AG21" s="34"/>
+      <c r="CJ20" s="34"/>
+    </row>
+    <row r="21" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="W21" s="34"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21"/>
+      <c r="AA21" s="37"/>
+      <c r="AG21"/>
       <c r="AI21" s="34"/>
       <c r="AK21" s="34"/>
       <c r="AM21" s="34"/>
-      <c r="AO21" s="37"/>
-      <c r="AV21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AQ21" s="37"/>
+      <c r="AV21"/>
       <c r="AX21" s="34"/>
       <c r="AZ21" s="34"/>
       <c r="BB21" s="34"/>
       <c r="BD21" s="34"/>
-      <c r="BE21" s="19"/>
-      <c r="BK21" s="34"/>
+      <c r="BF21" s="34"/>
+      <c r="BG21" s="19"/>
+      <c r="BK21"/>
       <c r="BM21" s="34"/>
       <c r="BO21" s="34"/>
       <c r="BQ21" s="34"/>
-      <c r="BS21" s="37"/>
+      <c r="BS21" s="34"/>
+      <c r="BU21" s="37"/>
       <c r="BX21"/>
-      <c r="BZ21" s="34"/>
       <c r="CB21" s="34"/>
       <c r="CD21" s="34"/>
       <c r="CF21" s="34"/>
       <c r="CH21" s="34"/>
-    </row>
-    <row r="22" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Z22" s="37"/>
-      <c r="AG22" s="34"/>
+      <c r="CJ21" s="34"/>
+    </row>
+    <row r="22" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22"/>
+      <c r="AA22" s="37"/>
+      <c r="AG22"/>
       <c r="AI22" s="34"/>
       <c r="AK22" s="34"/>
       <c r="AM22" s="34"/>
-      <c r="AO22" s="37"/>
-      <c r="AV22" s="34"/>
+      <c r="AO22" s="34"/>
+      <c r="AQ22" s="37"/>
+      <c r="AV22"/>
       <c r="AX22" s="34"/>
       <c r="AZ22" s="34"/>
       <c r="BB22" s="34"/>
       <c r="BD22" s="34"/>
-      <c r="BE22" s="19"/>
-      <c r="BK22" s="34"/>
+      <c r="BF22" s="34"/>
+      <c r="BG22" s="19"/>
+      <c r="BK22"/>
       <c r="BM22" s="34"/>
       <c r="BO22" s="34"/>
       <c r="BQ22" s="34"/>
-      <c r="BS22" s="37"/>
+      <c r="BS22" s="34"/>
+      <c r="BU22" s="37"/>
       <c r="BX22"/>
-      <c r="BZ22" s="34"/>
       <c r="CB22" s="34"/>
       <c r="CD22" s="34"/>
       <c r="CF22" s="34"/>
       <c r="CH22" s="34"/>
-    </row>
-    <row r="23" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Z23" s="37"/>
-      <c r="AG23" s="34"/>
+      <c r="CJ22" s="34"/>
+    </row>
+    <row r="23" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23"/>
+      <c r="AA23" s="37"/>
+      <c r="AG23"/>
       <c r="AI23" s="34"/>
       <c r="AK23" s="34"/>
       <c r="AM23" s="34"/>
-      <c r="AO23" s="37"/>
-      <c r="AV23" s="34"/>
+      <c r="AO23" s="34"/>
+      <c r="AQ23" s="37"/>
+      <c r="AV23"/>
       <c r="AX23" s="34"/>
       <c r="AZ23" s="34"/>
       <c r="BB23" s="34"/>
       <c r="BD23" s="34"/>
-      <c r="BE23" s="19"/>
-      <c r="BK23" s="34"/>
+      <c r="BF23" s="34"/>
+      <c r="BG23" s="19"/>
+      <c r="BK23"/>
       <c r="BM23" s="34"/>
       <c r="BO23" s="34"/>
       <c r="BQ23" s="34"/>
-      <c r="BS23" s="37"/>
+      <c r="BS23" s="34"/>
+      <c r="BU23" s="37"/>
       <c r="BX23"/>
-      <c r="BZ23" s="34"/>
       <c r="CB23" s="34"/>
       <c r="CD23" s="34"/>
       <c r="CF23" s="34"/>
       <c r="CH23" s="34"/>
-    </row>
-    <row r="24" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Z24" s="37"/>
-      <c r="AG24" s="34"/>
+      <c r="CJ23" s="34"/>
+    </row>
+    <row r="24" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="Y24" s="34"/>
+      <c r="Z24"/>
+      <c r="AA24" s="37"/>
+      <c r="AG24"/>
       <c r="AI24" s="34"/>
       <c r="AK24" s="34"/>
       <c r="AM24" s="34"/>
-      <c r="AO24" s="37"/>
-      <c r="AV24" s="34"/>
+      <c r="AO24" s="34"/>
+      <c r="AQ24" s="37"/>
+      <c r="AV24"/>
       <c r="AX24" s="34"/>
       <c r="AZ24" s="34"/>
       <c r="BB24" s="34"/>
       <c r="BD24" s="34"/>
-      <c r="BE24" s="19"/>
-      <c r="BK24" s="34"/>
+      <c r="BF24" s="34"/>
+      <c r="BG24" s="19"/>
+      <c r="BK24"/>
       <c r="BM24" s="34"/>
       <c r="BO24" s="34"/>
       <c r="BQ24" s="34"/>
-      <c r="BS24" s="37"/>
+      <c r="BS24" s="34"/>
+      <c r="BU24" s="37"/>
       <c r="BX24"/>
-      <c r="BZ24" s="34"/>
       <c r="CB24" s="34"/>
       <c r="CD24" s="34"/>
       <c r="CF24" s="34"/>
       <c r="CH24" s="34"/>
-    </row>
-    <row r="25" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Z25" s="37"/>
-      <c r="AG25" s="34"/>
+      <c r="CJ24" s="34"/>
+    </row>
+    <row r="25" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25"/>
+      <c r="AA25" s="37"/>
+      <c r="AG25"/>
       <c r="AI25" s="34"/>
       <c r="AK25" s="34"/>
       <c r="AM25" s="34"/>
-      <c r="AO25" s="37"/>
-      <c r="AV25" s="34"/>
+      <c r="AO25" s="34"/>
+      <c r="AQ25" s="37"/>
+      <c r="AV25"/>
       <c r="AX25" s="34"/>
       <c r="AZ25" s="34"/>
       <c r="BB25" s="34"/>
       <c r="BD25" s="34"/>
-      <c r="BE25" s="19"/>
-      <c r="BK25" s="34"/>
+      <c r="BF25" s="34"/>
+      <c r="BG25" s="19"/>
+      <c r="BK25"/>
       <c r="BM25" s="34"/>
       <c r="BO25" s="34"/>
       <c r="BQ25" s="34"/>
-      <c r="BS25" s="37"/>
+      <c r="BS25" s="34"/>
+      <c r="BU25" s="37"/>
       <c r="BX25"/>
-      <c r="BZ25" s="34"/>
       <c r="CB25" s="34"/>
       <c r="CD25" s="34"/>
       <c r="CF25" s="34"/>
       <c r="CH25" s="34"/>
-    </row>
-    <row r="26" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Z26" s="37"/>
-      <c r="AG26" s="34"/>
+      <c r="CJ25" s="34"/>
+    </row>
+    <row r="26" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="Y26" s="34"/>
+      <c r="Z26"/>
+      <c r="AA26" s="37"/>
+      <c r="AG26"/>
       <c r="AI26" s="34"/>
       <c r="AK26" s="34"/>
       <c r="AM26" s="34"/>
-      <c r="AO26" s="37"/>
-      <c r="AV26" s="34"/>
+      <c r="AO26" s="34"/>
+      <c r="AQ26" s="37"/>
+      <c r="AV26"/>
       <c r="AX26" s="34"/>
       <c r="AZ26" s="34"/>
       <c r="BB26" s="34"/>
       <c r="BD26" s="34"/>
-      <c r="BE26" s="19"/>
-      <c r="BK26" s="34"/>
+      <c r="BF26" s="34"/>
+      <c r="BG26" s="19"/>
+      <c r="BK26"/>
       <c r="BM26" s="34"/>
       <c r="BO26" s="34"/>
       <c r="BQ26" s="34"/>
-      <c r="BS26" s="37"/>
+      <c r="BS26" s="34"/>
+      <c r="BU26" s="37"/>
       <c r="BX26"/>
-      <c r="BZ26" s="34"/>
       <c r="CB26" s="34"/>
       <c r="CD26" s="34"/>
       <c r="CF26" s="34"/>
       <c r="CH26" s="34"/>
-    </row>
-    <row r="27" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Z27" s="37"/>
-      <c r="AG27" s="34"/>
+      <c r="CJ26" s="34"/>
+    </row>
+    <row r="27" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27"/>
+      <c r="AA27" s="37"/>
+      <c r="AG27"/>
       <c r="AI27" s="34"/>
       <c r="AK27" s="34"/>
       <c r="AM27" s="34"/>
-      <c r="AO27" s="37"/>
-      <c r="AV27" s="34"/>
+      <c r="AO27" s="34"/>
+      <c r="AQ27" s="37"/>
+      <c r="AV27"/>
       <c r="AX27" s="34"/>
       <c r="AZ27" s="34"/>
       <c r="BB27" s="34"/>
       <c r="BD27" s="34"/>
-      <c r="BE27" s="19"/>
-      <c r="BK27" s="34"/>
+      <c r="BF27" s="34"/>
+      <c r="BG27" s="19"/>
+      <c r="BK27"/>
       <c r="BM27" s="34"/>
       <c r="BO27" s="34"/>
       <c r="BQ27" s="34"/>
-      <c r="BS27" s="37"/>
+      <c r="BS27" s="34"/>
+      <c r="BU27" s="37"/>
       <c r="BX27"/>
-      <c r="BZ27" s="34"/>
       <c r="CB27" s="34"/>
       <c r="CD27" s="34"/>
       <c r="CF27" s="34"/>
       <c r="CH27" s="34"/>
-    </row>
-    <row r="28" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Z28" s="37"/>
-      <c r="AG28" s="34"/>
+      <c r="CJ27" s="34"/>
+    </row>
+    <row r="28" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28"/>
+      <c r="AA28" s="37"/>
+      <c r="AG28"/>
       <c r="AI28" s="34"/>
       <c r="AK28" s="34"/>
       <c r="AM28" s="34"/>
-      <c r="AO28" s="37"/>
-      <c r="AV28" s="34"/>
+      <c r="AO28" s="34"/>
+      <c r="AQ28" s="37"/>
+      <c r="AV28"/>
       <c r="AX28" s="34"/>
       <c r="AZ28" s="34"/>
       <c r="BB28" s="34"/>
       <c r="BD28" s="34"/>
-      <c r="BE28" s="19"/>
-      <c r="BK28" s="34"/>
+      <c r="BF28" s="34"/>
+      <c r="BG28" s="19"/>
+      <c r="BK28"/>
       <c r="BM28" s="34"/>
       <c r="BO28" s="34"/>
       <c r="BQ28" s="34"/>
-      <c r="BS28" s="37"/>
+      <c r="BS28" s="34"/>
+      <c r="BU28" s="37"/>
       <c r="BX28"/>
-      <c r="BZ28" s="34"/>
       <c r="CB28" s="34"/>
       <c r="CD28" s="34"/>
       <c r="CF28" s="34"/>
       <c r="CH28" s="34"/>
-    </row>
-    <row r="29" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Z29" s="37"/>
-      <c r="AG29" s="34"/>
+      <c r="CJ28" s="34"/>
+    </row>
+    <row r="29" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29"/>
+      <c r="AA29" s="37"/>
+      <c r="AG29"/>
       <c r="AI29" s="34"/>
       <c r="AK29" s="34"/>
       <c r="AM29" s="34"/>
-      <c r="AO29" s="37"/>
-      <c r="AV29" s="34"/>
+      <c r="AO29" s="34"/>
+      <c r="AQ29" s="37"/>
+      <c r="AV29"/>
       <c r="AX29" s="34"/>
       <c r="AZ29" s="34"/>
       <c r="BB29" s="34"/>
       <c r="BD29" s="34"/>
-      <c r="BE29" s="19"/>
-      <c r="BK29" s="34"/>
+      <c r="BF29" s="34"/>
+      <c r="BG29" s="19"/>
+      <c r="BK29"/>
       <c r="BM29" s="34"/>
       <c r="BO29" s="34"/>
       <c r="BQ29" s="34"/>
-      <c r="BS29" s="37"/>
+      <c r="BS29" s="34"/>
+      <c r="BU29" s="37"/>
       <c r="BX29"/>
-      <c r="BZ29" s="34"/>
       <c r="CB29" s="34"/>
       <c r="CD29" s="34"/>
       <c r="CF29" s="34"/>
       <c r="CH29" s="34"/>
-    </row>
-    <row r="30" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Z30" s="37"/>
-      <c r="AG30" s="34"/>
+      <c r="CJ29" s="34"/>
+    </row>
+    <row r="30" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30"/>
+      <c r="AA30" s="37"/>
+      <c r="AG30"/>
       <c r="AI30" s="34"/>
       <c r="AK30" s="34"/>
       <c r="AM30" s="34"/>
-      <c r="AO30" s="37"/>
-      <c r="AV30" s="34"/>
+      <c r="AO30" s="34"/>
+      <c r="AQ30" s="37"/>
+      <c r="AV30"/>
       <c r="AX30" s="34"/>
       <c r="AZ30" s="34"/>
       <c r="BB30" s="34"/>
       <c r="BD30" s="34"/>
-      <c r="BE30" s="19"/>
-      <c r="BK30" s="34"/>
+      <c r="BF30" s="34"/>
+      <c r="BG30" s="19"/>
+      <c r="BK30"/>
       <c r="BM30" s="34"/>
       <c r="BO30" s="34"/>
       <c r="BQ30" s="34"/>
-      <c r="BS30" s="37"/>
+      <c r="BS30" s="34"/>
+      <c r="BU30" s="37"/>
       <c r="BX30"/>
-      <c r="BZ30" s="34"/>
       <c r="CB30" s="34"/>
       <c r="CD30" s="34"/>
       <c r="CF30" s="34"/>
       <c r="CH30" s="34"/>
-    </row>
-    <row r="31" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Z31" s="37"/>
-      <c r="AG31" s="34"/>
+      <c r="CJ30" s="34"/>
+    </row>
+    <row r="31" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31"/>
+      <c r="AA31" s="37"/>
+      <c r="AG31"/>
       <c r="AI31" s="34"/>
       <c r="AK31" s="34"/>
       <c r="AM31" s="34"/>
-      <c r="AO31" s="37"/>
-      <c r="AV31" s="34"/>
+      <c r="AO31" s="34"/>
+      <c r="AQ31" s="37"/>
+      <c r="AV31"/>
       <c r="AX31" s="34"/>
       <c r="AZ31" s="34"/>
       <c r="BB31" s="34"/>
       <c r="BD31" s="34"/>
-      <c r="BE31" s="19"/>
-      <c r="BK31" s="34"/>
+      <c r="BF31" s="34"/>
+      <c r="BG31" s="19"/>
+      <c r="BK31"/>
       <c r="BM31" s="34"/>
       <c r="BO31" s="34"/>
       <c r="BQ31" s="34"/>
-      <c r="BS31" s="37"/>
+      <c r="BS31" s="34"/>
+      <c r="BU31" s="37"/>
       <c r="BX31"/>
-      <c r="BZ31" s="34"/>
       <c r="CB31" s="34"/>
       <c r="CD31" s="34"/>
       <c r="CF31" s="34"/>
       <c r="CH31" s="34"/>
-    </row>
-    <row r="32" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Z32" s="37"/>
-      <c r="AG32" s="34"/>
+      <c r="CJ31" s="34"/>
+    </row>
+    <row r="32" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="Y32" s="34"/>
+      <c r="Z32"/>
+      <c r="AA32" s="37"/>
+      <c r="AG32"/>
       <c r="AI32" s="34"/>
       <c r="AK32" s="34"/>
       <c r="AM32" s="34"/>
-      <c r="AO32" s="37"/>
-      <c r="AV32" s="34"/>
+      <c r="AO32" s="34"/>
+      <c r="AQ32" s="37"/>
+      <c r="AV32"/>
       <c r="AX32" s="34"/>
       <c r="AZ32" s="34"/>
       <c r="BB32" s="34"/>
       <c r="BD32" s="34"/>
-      <c r="BE32" s="19"/>
-      <c r="BK32" s="34"/>
+      <c r="BF32" s="34"/>
+      <c r="BG32" s="19"/>
+      <c r="BK32"/>
       <c r="BM32" s="34"/>
       <c r="BO32" s="34"/>
       <c r="BQ32" s="34"/>
-      <c r="BS32" s="37"/>
+      <c r="BS32" s="34"/>
+      <c r="BU32" s="37"/>
       <c r="BX32"/>
-      <c r="BZ32" s="34"/>
       <c r="CB32" s="34"/>
       <c r="CD32" s="34"/>
       <c r="CF32" s="34"/>
       <c r="CH32" s="34"/>
-    </row>
-    <row r="33" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="X33" s="34"/>
-      <c r="Z33" s="37"/>
-      <c r="AG33" s="34"/>
+      <c r="CJ32" s="34"/>
+    </row>
+    <row r="33" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S33" s="34"/>
+      <c r="U33" s="34"/>
+      <c r="W33" s="34"/>
+      <c r="Y33" s="34"/>
+      <c r="Z33"/>
+      <c r="AA33" s="37"/>
+      <c r="AG33"/>
       <c r="AI33" s="34"/>
       <c r="AK33" s="34"/>
       <c r="AM33" s="34"/>
-      <c r="AO33" s="37"/>
-      <c r="AV33" s="34"/>
+      <c r="AO33" s="34"/>
+      <c r="AQ33" s="37"/>
+      <c r="AV33"/>
       <c r="AX33" s="34"/>
       <c r="AZ33" s="34"/>
       <c r="BB33" s="34"/>
       <c r="BD33" s="34"/>
-      <c r="BE33" s="19"/>
-      <c r="BK33" s="34"/>
+      <c r="BF33" s="34"/>
+      <c r="BG33" s="19"/>
+      <c r="BK33"/>
       <c r="BM33" s="34"/>
       <c r="BO33" s="34"/>
       <c r="BQ33" s="34"/>
-      <c r="BS33" s="37"/>
+      <c r="BS33" s="34"/>
+      <c r="BU33" s="37"/>
       <c r="BX33"/>
-      <c r="BZ33" s="34"/>
       <c r="CB33" s="34"/>
       <c r="CD33" s="34"/>
       <c r="CF33" s="34"/>
       <c r="CH33" s="34"/>
-    </row>
-    <row r="34" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Z34" s="37"/>
-      <c r="AG34" s="34"/>
+      <c r="CJ33" s="34"/>
+    </row>
+    <row r="34" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="W34" s="34"/>
+      <c r="Y34" s="34"/>
+      <c r="Z34"/>
+      <c r="AA34" s="37"/>
+      <c r="AG34"/>
       <c r="AI34" s="34"/>
       <c r="AK34" s="34"/>
       <c r="AM34" s="34"/>
-      <c r="AO34" s="37"/>
-      <c r="AV34" s="34"/>
+      <c r="AO34" s="34"/>
+      <c r="AQ34" s="37"/>
+      <c r="AV34"/>
       <c r="AX34" s="34"/>
       <c r="AZ34" s="34"/>
       <c r="BB34" s="34"/>
       <c r="BD34" s="34"/>
-      <c r="BE34" s="19"/>
-      <c r="BK34" s="34"/>
+      <c r="BF34" s="34"/>
+      <c r="BG34" s="19"/>
+      <c r="BK34"/>
       <c r="BM34" s="34"/>
       <c r="BO34" s="34"/>
       <c r="BQ34" s="34"/>
-      <c r="BS34" s="37"/>
+      <c r="BS34" s="34"/>
+      <c r="BU34" s="37"/>
       <c r="BX34"/>
-      <c r="BZ34" s="34"/>
       <c r="CB34" s="34"/>
       <c r="CD34" s="34"/>
       <c r="CF34" s="34"/>
       <c r="CH34" s="34"/>
-    </row>
-    <row r="35" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Z35" s="37"/>
-      <c r="AG35" s="34"/>
+      <c r="CJ34" s="34"/>
+    </row>
+    <row r="35" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S35" s="34"/>
+      <c r="U35" s="34"/>
+      <c r="W35" s="34"/>
+      <c r="Y35" s="34"/>
+      <c r="Z35"/>
+      <c r="AA35" s="37"/>
+      <c r="AG35"/>
       <c r="AI35" s="34"/>
       <c r="AK35" s="34"/>
       <c r="AM35" s="34"/>
-      <c r="AO35" s="37"/>
-      <c r="AV35" s="34"/>
+      <c r="AO35" s="34"/>
+      <c r="AQ35" s="37"/>
+      <c r="AV35"/>
       <c r="AX35" s="34"/>
       <c r="AZ35" s="34"/>
       <c r="BB35" s="34"/>
       <c r="BD35" s="34"/>
-      <c r="BE35" s="19"/>
-      <c r="BK35" s="34"/>
+      <c r="BF35" s="34"/>
+      <c r="BG35" s="19"/>
+      <c r="BK35"/>
       <c r="BM35" s="34"/>
       <c r="BO35" s="34"/>
       <c r="BQ35" s="34"/>
-      <c r="BS35" s="37"/>
+      <c r="BS35" s="34"/>
+      <c r="BU35" s="37"/>
       <c r="BX35"/>
-      <c r="BZ35" s="34"/>
       <c r="CB35" s="34"/>
       <c r="CD35" s="34"/>
       <c r="CF35" s="34"/>
       <c r="CH35" s="34"/>
-    </row>
-    <row r="36" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Z36" s="37"/>
-      <c r="AG36" s="34"/>
+      <c r="CJ35" s="34"/>
+    </row>
+    <row r="36" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="W36" s="34"/>
+      <c r="Y36" s="34"/>
+      <c r="Z36"/>
+      <c r="AA36" s="37"/>
+      <c r="AG36"/>
       <c r="AI36" s="34"/>
       <c r="AK36" s="34"/>
       <c r="AM36" s="34"/>
-      <c r="AO36" s="37"/>
-      <c r="AV36" s="34"/>
+      <c r="AO36" s="34"/>
+      <c r="AQ36" s="37"/>
+      <c r="AV36"/>
       <c r="AX36" s="34"/>
       <c r="AZ36" s="34"/>
       <c r="BB36" s="34"/>
       <c r="BD36" s="34"/>
-      <c r="BE36" s="19"/>
-      <c r="BK36" s="34"/>
+      <c r="BF36" s="34"/>
+      <c r="BG36" s="19"/>
+      <c r="BK36"/>
       <c r="BM36" s="34"/>
       <c r="BO36" s="34"/>
       <c r="BQ36" s="34"/>
-      <c r="BS36" s="37"/>
+      <c r="BS36" s="34"/>
+      <c r="BU36" s="37"/>
       <c r="BX36"/>
-      <c r="BZ36" s="34"/>
       <c r="CB36" s="34"/>
       <c r="CD36" s="34"/>
       <c r="CF36" s="34"/>
       <c r="CH36" s="34"/>
-    </row>
-    <row r="37" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="X37" s="34"/>
-      <c r="Z37" s="37"/>
-      <c r="AG37" s="34"/>
+      <c r="CJ36" s="34"/>
+    </row>
+    <row r="37" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S37" s="34"/>
+      <c r="U37" s="34"/>
+      <c r="W37" s="34"/>
+      <c r="Y37" s="34"/>
+      <c r="Z37"/>
+      <c r="AA37" s="37"/>
+      <c r="AG37"/>
       <c r="AI37" s="34"/>
       <c r="AK37" s="34"/>
       <c r="AM37" s="34"/>
-      <c r="AO37" s="37"/>
-      <c r="AV37" s="34"/>
+      <c r="AO37" s="34"/>
+      <c r="AQ37" s="37"/>
+      <c r="AV37"/>
       <c r="AX37" s="34"/>
       <c r="AZ37" s="34"/>
       <c r="BB37" s="34"/>
       <c r="BD37" s="34"/>
-      <c r="BE37" s="19"/>
-      <c r="BK37" s="34"/>
+      <c r="BF37" s="34"/>
+      <c r="BG37" s="19"/>
+      <c r="BK37"/>
       <c r="BM37" s="34"/>
       <c r="BO37" s="34"/>
       <c r="BQ37" s="34"/>
-      <c r="BS37" s="37"/>
+      <c r="BS37" s="34"/>
+      <c r="BU37" s="37"/>
       <c r="BX37"/>
-      <c r="BZ37" s="34"/>
       <c r="CB37" s="34"/>
       <c r="CD37" s="34"/>
       <c r="CF37" s="34"/>
       <c r="CH37" s="34"/>
-    </row>
-    <row r="38" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="X38" s="34"/>
-      <c r="Z38" s="37"/>
-      <c r="AG38" s="34"/>
+      <c r="CJ37" s="34"/>
+    </row>
+    <row r="38" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S38" s="34"/>
+      <c r="U38" s="34"/>
+      <c r="W38" s="34"/>
+      <c r="Y38" s="34"/>
+      <c r="Z38"/>
+      <c r="AA38" s="37"/>
+      <c r="AG38"/>
       <c r="AI38" s="34"/>
       <c r="AK38" s="34"/>
       <c r="AM38" s="34"/>
-      <c r="AO38" s="37"/>
-      <c r="AV38" s="34"/>
+      <c r="AO38" s="34"/>
+      <c r="AQ38" s="37"/>
+      <c r="AV38"/>
       <c r="AX38" s="34"/>
       <c r="AZ38" s="34"/>
       <c r="BB38" s="34"/>
       <c r="BD38" s="34"/>
-      <c r="BE38" s="19"/>
-      <c r="BK38" s="34"/>
+      <c r="BF38" s="34"/>
+      <c r="BG38" s="19"/>
+      <c r="BK38"/>
       <c r="BM38" s="34"/>
       <c r="BO38" s="34"/>
       <c r="BQ38" s="34"/>
-      <c r="BS38" s="37"/>
+      <c r="BS38" s="34"/>
+      <c r="BU38" s="37"/>
       <c r="BX38"/>
-      <c r="BZ38" s="34"/>
       <c r="CB38" s="34"/>
       <c r="CD38" s="34"/>
       <c r="CF38" s="34"/>
       <c r="CH38" s="34"/>
-    </row>
-    <row r="39" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Z39" s="37"/>
-      <c r="AG39" s="34"/>
+      <c r="CJ38" s="34"/>
+    </row>
+    <row r="39" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S39" s="34"/>
+      <c r="U39" s="34"/>
+      <c r="W39" s="34"/>
+      <c r="Y39" s="34"/>
+      <c r="Z39"/>
+      <c r="AA39" s="37"/>
+      <c r="AG39"/>
       <c r="AI39" s="34"/>
       <c r="AK39" s="34"/>
       <c r="AM39" s="34"/>
-      <c r="AO39" s="37"/>
-      <c r="AV39" s="34"/>
+      <c r="AO39" s="34"/>
+      <c r="AQ39" s="37"/>
+      <c r="AV39"/>
       <c r="AX39" s="34"/>
       <c r="AZ39" s="34"/>
       <c r="BB39" s="34"/>
       <c r="BD39" s="34"/>
-      <c r="BE39" s="19"/>
-      <c r="BK39" s="34"/>
+      <c r="BF39" s="34"/>
+      <c r="BG39" s="19"/>
+      <c r="BK39"/>
       <c r="BM39" s="34"/>
       <c r="BO39" s="34"/>
       <c r="BQ39" s="34"/>
-      <c r="BS39" s="37"/>
+      <c r="BS39" s="34"/>
+      <c r="BU39" s="37"/>
       <c r="BX39"/>
-      <c r="BZ39" s="34"/>
       <c r="CB39" s="34"/>
       <c r="CD39" s="34"/>
       <c r="CF39" s="34"/>
       <c r="CH39" s="34"/>
-    </row>
-    <row r="40" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="V40" s="34"/>
-      <c r="X40" s="34"/>
-      <c r="Z40" s="37"/>
-      <c r="AG40" s="34"/>
+      <c r="CJ39" s="34"/>
+    </row>
+    <row r="40" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S40" s="34"/>
+      <c r="U40" s="34"/>
+      <c r="W40" s="34"/>
+      <c r="Y40" s="34"/>
+      <c r="Z40"/>
+      <c r="AA40" s="37"/>
+      <c r="AG40"/>
       <c r="AI40" s="34"/>
       <c r="AK40" s="34"/>
       <c r="AM40" s="34"/>
-      <c r="AO40" s="37"/>
-      <c r="AV40" s="34"/>
+      <c r="AO40" s="34"/>
+      <c r="AQ40" s="37"/>
+      <c r="AV40"/>
       <c r="AX40" s="34"/>
       <c r="AZ40" s="34"/>
       <c r="BB40" s="34"/>
       <c r="BD40" s="34"/>
-      <c r="BE40" s="19"/>
-      <c r="BK40" s="34"/>
+      <c r="BF40" s="34"/>
+      <c r="BG40" s="19"/>
+      <c r="BK40"/>
       <c r="BM40" s="34"/>
       <c r="BO40" s="34"/>
       <c r="BQ40" s="34"/>
-      <c r="BS40" s="37"/>
+      <c r="BS40" s="34"/>
+      <c r="BU40" s="37"/>
       <c r="BX40"/>
-      <c r="BZ40" s="34"/>
       <c r="CB40" s="34"/>
       <c r="CD40" s="34"/>
       <c r="CF40" s="34"/>
       <c r="CH40" s="34"/>
-    </row>
-    <row r="41" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="V41" s="34"/>
-      <c r="X41" s="34"/>
-      <c r="Z41" s="37"/>
-      <c r="AG41" s="34"/>
+      <c r="CJ40" s="34"/>
+    </row>
+    <row r="41" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S41" s="34"/>
+      <c r="U41" s="34"/>
+      <c r="W41" s="34"/>
+      <c r="Y41" s="34"/>
+      <c r="Z41"/>
+      <c r="AA41" s="37"/>
+      <c r="AG41"/>
       <c r="AI41" s="34"/>
       <c r="AK41" s="34"/>
       <c r="AM41" s="34"/>
-      <c r="AO41" s="37"/>
-      <c r="AV41" s="34"/>
+      <c r="AO41" s="34"/>
+      <c r="AQ41" s="37"/>
+      <c r="AV41"/>
       <c r="AX41" s="34"/>
       <c r="AZ41" s="34"/>
       <c r="BB41" s="34"/>
       <c r="BD41" s="34"/>
-      <c r="BE41" s="19"/>
-      <c r="BK41" s="34"/>
+      <c r="BF41" s="34"/>
+      <c r="BG41" s="19"/>
+      <c r="BK41"/>
       <c r="BM41" s="34"/>
       <c r="BO41" s="34"/>
       <c r="BQ41" s="34"/>
-      <c r="BS41" s="37"/>
+      <c r="BS41" s="34"/>
+      <c r="BU41" s="37"/>
       <c r="BX41"/>
-      <c r="BZ41" s="34"/>
       <c r="CB41" s="34"/>
       <c r="CD41" s="34"/>
       <c r="CF41" s="34"/>
       <c r="CH41" s="34"/>
-    </row>
-    <row r="42" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="X42" s="34"/>
-      <c r="Z42" s="37"/>
-      <c r="AG42" s="34"/>
+      <c r="CJ41" s="34"/>
+    </row>
+    <row r="42" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="W42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42"/>
+      <c r="AA42" s="37"/>
+      <c r="AG42"/>
       <c r="AI42" s="34"/>
       <c r="AK42" s="34"/>
       <c r="AM42" s="34"/>
-      <c r="AO42" s="37"/>
-      <c r="AV42" s="34"/>
+      <c r="AO42" s="34"/>
+      <c r="AQ42" s="37"/>
+      <c r="AV42"/>
       <c r="AX42" s="34"/>
       <c r="AZ42" s="34"/>
       <c r="BB42" s="34"/>
       <c r="BD42" s="34"/>
-      <c r="BE42" s="19"/>
-      <c r="BK42" s="34"/>
+      <c r="BF42" s="34"/>
+      <c r="BG42" s="19"/>
+      <c r="BK42"/>
       <c r="BM42" s="34"/>
       <c r="BO42" s="34"/>
       <c r="BQ42" s="34"/>
-      <c r="BS42" s="37"/>
+      <c r="BS42" s="34"/>
+      <c r="BU42" s="37"/>
       <c r="BX42"/>
-      <c r="BZ42" s="34"/>
       <c r="CB42" s="34"/>
       <c r="CD42" s="34"/>
       <c r="CF42" s="34"/>
       <c r="CH42" s="34"/>
-    </row>
-    <row r="43" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="V43" s="34"/>
-      <c r="X43" s="34"/>
-      <c r="Z43" s="37"/>
-      <c r="AG43" s="34"/>
+      <c r="CJ42" s="34"/>
+    </row>
+    <row r="43" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S43" s="34"/>
+      <c r="U43" s="34"/>
+      <c r="W43" s="34"/>
+      <c r="Y43" s="34"/>
+      <c r="Z43"/>
+      <c r="AA43" s="37"/>
+      <c r="AG43"/>
       <c r="AI43" s="34"/>
       <c r="AK43" s="34"/>
       <c r="AM43" s="34"/>
-      <c r="AO43" s="37"/>
-      <c r="AV43" s="34"/>
+      <c r="AO43" s="34"/>
+      <c r="AQ43" s="37"/>
+      <c r="AV43"/>
       <c r="AX43" s="34"/>
       <c r="AZ43" s="34"/>
       <c r="BB43" s="34"/>
       <c r="BD43" s="34"/>
-      <c r="BE43" s="19"/>
-      <c r="BK43" s="34"/>
+      <c r="BF43" s="34"/>
+      <c r="BG43" s="19"/>
+      <c r="BK43"/>
       <c r="BM43" s="34"/>
       <c r="BO43" s="34"/>
       <c r="BQ43" s="34"/>
-      <c r="BS43" s="37"/>
+      <c r="BS43" s="34"/>
+      <c r="BU43" s="37"/>
       <c r="BX43"/>
-      <c r="BZ43" s="34"/>
       <c r="CB43" s="34"/>
       <c r="CD43" s="34"/>
       <c r="CF43" s="34"/>
       <c r="CH43" s="34"/>
-    </row>
-    <row r="44" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="X44" s="34"/>
-      <c r="Z44" s="37"/>
-      <c r="AG44" s="34"/>
+      <c r="CJ43" s="34"/>
+    </row>
+    <row r="44" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="W44" s="34"/>
+      <c r="Y44" s="34"/>
+      <c r="Z44"/>
+      <c r="AA44" s="37"/>
+      <c r="AG44"/>
       <c r="AI44" s="34"/>
       <c r="AK44" s="34"/>
       <c r="AM44" s="34"/>
-      <c r="AO44" s="37"/>
-      <c r="AV44" s="34"/>
+      <c r="AO44" s="34"/>
+      <c r="AQ44" s="37"/>
+      <c r="AV44"/>
       <c r="AX44" s="34"/>
       <c r="AZ44" s="34"/>
       <c r="BB44" s="34"/>
       <c r="BD44" s="34"/>
-      <c r="BE44" s="19"/>
-      <c r="BK44" s="34"/>
+      <c r="BF44" s="34"/>
+      <c r="BG44" s="19"/>
+      <c r="BK44"/>
       <c r="BM44" s="34"/>
       <c r="BO44" s="34"/>
       <c r="BQ44" s="34"/>
-      <c r="BS44" s="37"/>
+      <c r="BS44" s="34"/>
+      <c r="BU44" s="37"/>
       <c r="BX44"/>
-      <c r="BZ44" s="34"/>
       <c r="CB44" s="34"/>
       <c r="CD44" s="34"/>
       <c r="CF44" s="34"/>
       <c r="CH44" s="34"/>
-    </row>
-    <row r="45" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R45" s="34"/>
-      <c r="T45" s="34"/>
-      <c r="V45" s="34"/>
-      <c r="X45" s="34"/>
-      <c r="Z45" s="37"/>
-      <c r="AG45" s="34"/>
+      <c r="CJ44" s="34"/>
+    </row>
+    <row r="45" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S45" s="34"/>
+      <c r="U45" s="34"/>
+      <c r="W45" s="34"/>
+      <c r="Y45" s="34"/>
+      <c r="Z45"/>
+      <c r="AA45" s="37"/>
+      <c r="AG45"/>
       <c r="AI45" s="34"/>
       <c r="AK45" s="34"/>
       <c r="AM45" s="34"/>
-      <c r="AO45" s="37"/>
-      <c r="AV45" s="34"/>
+      <c r="AO45" s="34"/>
+      <c r="AQ45" s="37"/>
+      <c r="AV45"/>
       <c r="AX45" s="34"/>
       <c r="AZ45" s="34"/>
       <c r="BB45" s="34"/>
       <c r="BD45" s="34"/>
-      <c r="BE45" s="19"/>
-      <c r="BK45" s="34"/>
+      <c r="BF45" s="34"/>
+      <c r="BG45" s="19"/>
+      <c r="BK45"/>
       <c r="BM45" s="34"/>
       <c r="BO45" s="34"/>
       <c r="BQ45" s="34"/>
-      <c r="BS45" s="37"/>
+      <c r="BS45" s="34"/>
+      <c r="BU45" s="37"/>
       <c r="BX45"/>
-      <c r="BZ45" s="34"/>
       <c r="CB45" s="34"/>
       <c r="CD45" s="34"/>
       <c r="CF45" s="34"/>
       <c r="CH45" s="34"/>
-    </row>
-    <row r="46" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R46" s="34"/>
-      <c r="T46" s="34"/>
-      <c r="V46" s="34"/>
-      <c r="X46" s="34"/>
-      <c r="Z46" s="37"/>
-      <c r="AG46" s="34"/>
+      <c r="CJ45" s="34"/>
+    </row>
+    <row r="46" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S46" s="34"/>
+      <c r="U46" s="34"/>
+      <c r="W46" s="34"/>
+      <c r="Y46" s="34"/>
+      <c r="Z46"/>
+      <c r="AA46" s="37"/>
+      <c r="AG46"/>
       <c r="AI46" s="34"/>
       <c r="AK46" s="34"/>
       <c r="AM46" s="34"/>
-      <c r="AO46" s="37"/>
-      <c r="AV46" s="34"/>
+      <c r="AO46" s="34"/>
+      <c r="AQ46" s="37"/>
+      <c r="AV46"/>
       <c r="AX46" s="34"/>
       <c r="AZ46" s="34"/>
       <c r="BB46" s="34"/>
       <c r="BD46" s="34"/>
-      <c r="BE46" s="19"/>
-      <c r="BK46" s="34"/>
+      <c r="BF46" s="34"/>
+      <c r="BG46" s="19"/>
+      <c r="BK46"/>
       <c r="BM46" s="34"/>
       <c r="BO46" s="34"/>
       <c r="BQ46" s="34"/>
-      <c r="BS46" s="37"/>
+      <c r="BS46" s="34"/>
+      <c r="BU46" s="37"/>
       <c r="BX46"/>
-      <c r="BZ46" s="34"/>
       <c r="CB46" s="34"/>
       <c r="CD46" s="34"/>
       <c r="CF46" s="34"/>
       <c r="CH46" s="34"/>
-    </row>
-    <row r="47" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R47" s="34"/>
-      <c r="T47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="X47" s="34"/>
-      <c r="Z47" s="37"/>
-      <c r="AG47" s="34"/>
+      <c r="CJ46" s="34"/>
+    </row>
+    <row r="47" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S47" s="34"/>
+      <c r="U47" s="34"/>
+      <c r="W47" s="34"/>
+      <c r="Y47" s="34"/>
+      <c r="Z47"/>
+      <c r="AA47" s="37"/>
+      <c r="AG47"/>
       <c r="AI47" s="34"/>
       <c r="AK47" s="34"/>
       <c r="AM47" s="34"/>
-      <c r="AO47" s="37"/>
-      <c r="AV47" s="34"/>
+      <c r="AO47" s="34"/>
+      <c r="AQ47" s="37"/>
+      <c r="AV47"/>
       <c r="AX47" s="34"/>
       <c r="AZ47" s="34"/>
       <c r="BB47" s="34"/>
       <c r="BD47" s="34"/>
-      <c r="BE47" s="19"/>
-      <c r="BK47" s="34"/>
+      <c r="BF47" s="34"/>
+      <c r="BG47" s="19"/>
+      <c r="BK47"/>
       <c r="BM47" s="34"/>
       <c r="BO47" s="34"/>
       <c r="BQ47" s="34"/>
-      <c r="BS47" s="37"/>
+      <c r="BS47" s="34"/>
+      <c r="BU47" s="37"/>
       <c r="BX47"/>
-      <c r="BZ47" s="34"/>
       <c r="CB47" s="34"/>
       <c r="CD47" s="34"/>
       <c r="CF47" s="34"/>
       <c r="CH47" s="34"/>
-    </row>
-    <row r="48" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R48" s="34"/>
-      <c r="T48" s="34"/>
-      <c r="V48" s="34"/>
-      <c r="X48" s="34"/>
-      <c r="Z48" s="37"/>
-      <c r="AG48" s="34"/>
+      <c r="CJ47" s="34"/>
+    </row>
+    <row r="48" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S48" s="34"/>
+      <c r="U48" s="34"/>
+      <c r="W48" s="34"/>
+      <c r="Y48" s="34"/>
+      <c r="Z48"/>
+      <c r="AA48" s="37"/>
+      <c r="AG48"/>
       <c r="AI48" s="34"/>
       <c r="AK48" s="34"/>
       <c r="AM48" s="34"/>
-      <c r="AO48" s="37"/>
-      <c r="AV48" s="34"/>
+      <c r="AO48" s="34"/>
+      <c r="AQ48" s="37"/>
+      <c r="AV48"/>
       <c r="AX48" s="34"/>
       <c r="AZ48" s="34"/>
       <c r="BB48" s="34"/>
       <c r="BD48" s="34"/>
-      <c r="BE48" s="19"/>
-      <c r="BK48" s="34"/>
+      <c r="BF48" s="34"/>
+      <c r="BG48" s="19"/>
+      <c r="BK48"/>
       <c r="BM48" s="34"/>
       <c r="BO48" s="34"/>
       <c r="BQ48" s="34"/>
-      <c r="BS48" s="37"/>
+      <c r="BS48" s="34"/>
+      <c r="BU48" s="37"/>
       <c r="BX48"/>
-      <c r="BZ48" s="34"/>
       <c r="CB48" s="34"/>
       <c r="CD48" s="34"/>
       <c r="CF48" s="34"/>
       <c r="CH48" s="34"/>
-    </row>
-    <row r="49" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="X49" s="34"/>
-      <c r="Z49" s="37"/>
-      <c r="AG49" s="34"/>
+      <c r="CJ48" s="34"/>
+    </row>
+    <row r="49" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S49" s="34"/>
+      <c r="U49" s="34"/>
+      <c r="W49" s="34"/>
+      <c r="Y49" s="34"/>
+      <c r="Z49"/>
+      <c r="AA49" s="37"/>
+      <c r="AG49"/>
       <c r="AI49" s="34"/>
       <c r="AK49" s="34"/>
       <c r="AM49" s="34"/>
-      <c r="AO49" s="37"/>
-      <c r="AV49" s="34"/>
+      <c r="AO49" s="34"/>
+      <c r="AQ49" s="37"/>
+      <c r="AV49"/>
       <c r="AX49" s="34"/>
       <c r="AZ49" s="34"/>
       <c r="BB49" s="34"/>
       <c r="BD49" s="34"/>
-      <c r="BE49" s="19"/>
-      <c r="BK49" s="34"/>
+      <c r="BF49" s="34"/>
+      <c r="BG49" s="19"/>
+      <c r="BK49"/>
       <c r="BM49" s="34"/>
       <c r="BO49" s="34"/>
       <c r="BQ49" s="34"/>
-      <c r="BS49" s="37"/>
+      <c r="BS49" s="34"/>
+      <c r="BU49" s="37"/>
       <c r="BX49"/>
-      <c r="BZ49" s="34"/>
       <c r="CB49" s="34"/>
       <c r="CD49" s="34"/>
       <c r="CF49" s="34"/>
       <c r="CH49" s="34"/>
-    </row>
-    <row r="50" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="X50" s="34"/>
-      <c r="Z50" s="37"/>
-      <c r="AG50" s="34"/>
+      <c r="CJ49" s="34"/>
+    </row>
+    <row r="50" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S50" s="34"/>
+      <c r="U50" s="34"/>
+      <c r="W50" s="34"/>
+      <c r="Y50" s="34"/>
+      <c r="Z50"/>
+      <c r="AA50" s="37"/>
+      <c r="AG50"/>
       <c r="AI50" s="34"/>
       <c r="AK50" s="34"/>
       <c r="AM50" s="34"/>
-      <c r="AO50" s="37"/>
-      <c r="AV50" s="34"/>
+      <c r="AO50" s="34"/>
+      <c r="AQ50" s="37"/>
+      <c r="AV50"/>
       <c r="AX50" s="34"/>
       <c r="AZ50" s="34"/>
       <c r="BB50" s="34"/>
       <c r="BD50" s="34"/>
-      <c r="BE50" s="19"/>
-      <c r="BK50" s="34"/>
+      <c r="BF50" s="34"/>
+      <c r="BG50" s="19"/>
+      <c r="BK50"/>
       <c r="BM50" s="34"/>
       <c r="BO50" s="34"/>
       <c r="BQ50" s="34"/>
-      <c r="BS50" s="37"/>
+      <c r="BS50" s="34"/>
+      <c r="BU50" s="37"/>
       <c r="BX50"/>
-      <c r="BZ50" s="34"/>
       <c r="CB50" s="34"/>
       <c r="CD50" s="34"/>
       <c r="CF50" s="34"/>
       <c r="CH50" s="34"/>
-    </row>
-    <row r="51" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R51" s="34"/>
-      <c r="T51" s="34"/>
-      <c r="V51" s="34"/>
-      <c r="X51" s="34"/>
-      <c r="Z51" s="37"/>
-      <c r="AG51" s="34"/>
+      <c r="CJ50" s="34"/>
+    </row>
+    <row r="51" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S51" s="34"/>
+      <c r="U51" s="34"/>
+      <c r="W51" s="34"/>
+      <c r="Y51" s="34"/>
+      <c r="Z51"/>
+      <c r="AA51" s="37"/>
+      <c r="AG51"/>
       <c r="AI51" s="34"/>
       <c r="AK51" s="34"/>
       <c r="AM51" s="34"/>
-      <c r="AO51" s="37"/>
-      <c r="AV51" s="34"/>
+      <c r="AO51" s="34"/>
+      <c r="AQ51" s="37"/>
+      <c r="AV51"/>
       <c r="AX51" s="34"/>
       <c r="AZ51" s="34"/>
       <c r="BB51" s="34"/>
       <c r="BD51" s="34"/>
-      <c r="BE51" s="19"/>
-      <c r="BK51" s="34"/>
+      <c r="BF51" s="34"/>
+      <c r="BG51" s="19"/>
+      <c r="BK51"/>
       <c r="BM51" s="34"/>
       <c r="BO51" s="34"/>
       <c r="BQ51" s="34"/>
-      <c r="BS51" s="37"/>
+      <c r="BS51" s="34"/>
+      <c r="BU51" s="37"/>
       <c r="BX51"/>
-      <c r="BZ51" s="34"/>
       <c r="CB51" s="34"/>
       <c r="CD51" s="34"/>
       <c r="CF51" s="34"/>
       <c r="CH51" s="34"/>
-    </row>
-    <row r="52" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R52" s="34"/>
-      <c r="T52" s="34"/>
-      <c r="V52" s="34"/>
-      <c r="X52" s="34"/>
-      <c r="Z52" s="37"/>
-      <c r="AG52" s="34"/>
+      <c r="CJ51" s="34"/>
+    </row>
+    <row r="52" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S52" s="34"/>
+      <c r="U52" s="34"/>
+      <c r="W52" s="34"/>
+      <c r="Y52" s="34"/>
+      <c r="Z52"/>
+      <c r="AA52" s="37"/>
+      <c r="AG52"/>
       <c r="AI52" s="34"/>
       <c r="AK52" s="34"/>
       <c r="AM52" s="34"/>
-      <c r="AO52" s="37"/>
-      <c r="AV52" s="34"/>
+      <c r="AO52" s="34"/>
+      <c r="AQ52" s="37"/>
+      <c r="AV52"/>
       <c r="AX52" s="34"/>
       <c r="AZ52" s="34"/>
       <c r="BB52" s="34"/>
       <c r="BD52" s="34"/>
-      <c r="BE52" s="19"/>
-      <c r="BK52" s="34"/>
+      <c r="BF52" s="34"/>
+      <c r="BG52" s="19"/>
+      <c r="BK52"/>
       <c r="BM52" s="34"/>
       <c r="BO52" s="34"/>
       <c r="BQ52" s="34"/>
-      <c r="BS52" s="37"/>
+      <c r="BS52" s="34"/>
+      <c r="BU52" s="37"/>
       <c r="BX52"/>
-      <c r="BZ52" s="34"/>
       <c r="CB52" s="34"/>
       <c r="CD52" s="34"/>
       <c r="CF52" s="34"/>
       <c r="CH52" s="34"/>
-    </row>
-    <row r="53" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R53" s="34"/>
-      <c r="T53" s="34"/>
-      <c r="V53" s="34"/>
-      <c r="X53" s="34"/>
-      <c r="Z53" s="37"/>
-      <c r="AG53" s="34"/>
+      <c r="CJ52" s="34"/>
+    </row>
+    <row r="53" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S53" s="34"/>
+      <c r="U53" s="34"/>
+      <c r="W53" s="34"/>
+      <c r="Y53" s="34"/>
+      <c r="Z53"/>
+      <c r="AA53" s="37"/>
+      <c r="AG53"/>
       <c r="AI53" s="34"/>
       <c r="AK53" s="34"/>
       <c r="AM53" s="34"/>
-      <c r="AO53" s="37"/>
-      <c r="AV53" s="34"/>
+      <c r="AO53" s="34"/>
+      <c r="AQ53" s="37"/>
+      <c r="AV53"/>
       <c r="AX53" s="34"/>
       <c r="AZ53" s="34"/>
       <c r="BB53" s="34"/>
       <c r="BD53" s="34"/>
-      <c r="BE53" s="19"/>
-      <c r="BK53" s="34"/>
+      <c r="BF53" s="34"/>
+      <c r="BG53" s="19"/>
+      <c r="BK53"/>
       <c r="BM53" s="34"/>
       <c r="BO53" s="34"/>
       <c r="BQ53" s="34"/>
-      <c r="BS53" s="37"/>
+      <c r="BS53" s="34"/>
+      <c r="BU53" s="37"/>
       <c r="BX53"/>
-      <c r="BZ53" s="34"/>
       <c r="CB53" s="34"/>
       <c r="CD53" s="34"/>
       <c r="CF53" s="34"/>
       <c r="CH53" s="34"/>
-    </row>
-    <row r="54" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R54" s="34"/>
-      <c r="T54" s="34"/>
-      <c r="V54" s="34"/>
-      <c r="X54" s="34"/>
-      <c r="Z54" s="37"/>
-      <c r="AG54" s="34"/>
+      <c r="CJ53" s="34"/>
+    </row>
+    <row r="54" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S54" s="34"/>
+      <c r="U54" s="34"/>
+      <c r="W54" s="34"/>
+      <c r="Y54" s="34"/>
+      <c r="Z54"/>
+      <c r="AA54" s="37"/>
+      <c r="AG54"/>
       <c r="AI54" s="34"/>
       <c r="AK54" s="34"/>
       <c r="AM54" s="34"/>
-      <c r="AO54" s="37"/>
-      <c r="AV54" s="34"/>
+      <c r="AO54" s="34"/>
+      <c r="AQ54" s="37"/>
+      <c r="AV54"/>
       <c r="AX54" s="34"/>
       <c r="AZ54" s="34"/>
       <c r="BB54" s="34"/>
       <c r="BD54" s="34"/>
-      <c r="BE54" s="19"/>
-      <c r="BK54" s="34"/>
+      <c r="BF54" s="34"/>
+      <c r="BG54" s="19"/>
+      <c r="BK54"/>
       <c r="BM54" s="34"/>
       <c r="BO54" s="34"/>
       <c r="BQ54" s="34"/>
-      <c r="BS54" s="37"/>
+      <c r="BS54" s="34"/>
+      <c r="BU54" s="37"/>
       <c r="BX54"/>
-      <c r="BZ54" s="34"/>
       <c r="CB54" s="34"/>
       <c r="CD54" s="34"/>
       <c r="CF54" s="34"/>
       <c r="CH54" s="34"/>
-    </row>
-    <row r="55" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R55" s="34"/>
-      <c r="T55" s="34"/>
-      <c r="V55" s="34"/>
-      <c r="X55" s="34"/>
-      <c r="Z55" s="37"/>
-      <c r="AG55" s="34"/>
+      <c r="CJ54" s="34"/>
+    </row>
+    <row r="55" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S55" s="34"/>
+      <c r="U55" s="34"/>
+      <c r="W55" s="34"/>
+      <c r="Y55" s="34"/>
+      <c r="Z55"/>
+      <c r="AA55" s="37"/>
+      <c r="AG55"/>
       <c r="AI55" s="34"/>
       <c r="AK55" s="34"/>
       <c r="AM55" s="34"/>
-      <c r="AO55" s="37"/>
-      <c r="AV55" s="34"/>
+      <c r="AO55" s="34"/>
+      <c r="AQ55" s="37"/>
+      <c r="AV55"/>
       <c r="AX55" s="34"/>
       <c r="AZ55" s="34"/>
       <c r="BB55" s="34"/>
       <c r="BD55" s="34"/>
-      <c r="BE55" s="19"/>
-      <c r="BK55" s="34"/>
+      <c r="BF55" s="34"/>
+      <c r="BG55" s="19"/>
+      <c r="BK55"/>
       <c r="BM55" s="34"/>
       <c r="BO55" s="34"/>
       <c r="BQ55" s="34"/>
-      <c r="BS55" s="37"/>
+      <c r="BS55" s="34"/>
+      <c r="BU55" s="37"/>
       <c r="BX55"/>
-      <c r="BZ55" s="34"/>
       <c r="CB55" s="34"/>
       <c r="CD55" s="34"/>
       <c r="CF55" s="34"/>
       <c r="CH55" s="34"/>
-    </row>
-    <row r="56" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R56" s="34"/>
-      <c r="T56" s="34"/>
-      <c r="V56" s="34"/>
-      <c r="X56" s="34"/>
-      <c r="Z56" s="37"/>
-      <c r="AG56" s="34"/>
+      <c r="CJ55" s="34"/>
+    </row>
+    <row r="56" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S56" s="34"/>
+      <c r="U56" s="34"/>
+      <c r="W56" s="34"/>
+      <c r="Y56" s="34"/>
+      <c r="Z56"/>
+      <c r="AA56" s="37"/>
+      <c r="AG56"/>
       <c r="AI56" s="34"/>
       <c r="AK56" s="34"/>
       <c r="AM56" s="34"/>
-      <c r="AO56" s="37"/>
-      <c r="AV56" s="34"/>
+      <c r="AO56" s="34"/>
+      <c r="AQ56" s="37"/>
+      <c r="AV56"/>
       <c r="AX56" s="34"/>
       <c r="AZ56" s="34"/>
       <c r="BB56" s="34"/>
       <c r="BD56" s="34"/>
-      <c r="BE56" s="19"/>
-      <c r="BK56" s="34"/>
+      <c r="BF56" s="34"/>
+      <c r="BG56" s="19"/>
+      <c r="BK56"/>
       <c r="BM56" s="34"/>
       <c r="BO56" s="34"/>
       <c r="BQ56" s="34"/>
-      <c r="BS56" s="37"/>
+      <c r="BS56" s="34"/>
+      <c r="BU56" s="37"/>
       <c r="BX56"/>
-      <c r="BZ56" s="34"/>
       <c r="CB56" s="34"/>
       <c r="CD56" s="34"/>
       <c r="CF56" s="34"/>
       <c r="CH56" s="34"/>
-    </row>
-    <row r="57" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R57" s="34"/>
-      <c r="T57" s="34"/>
-      <c r="V57" s="34"/>
-      <c r="X57" s="34"/>
-      <c r="Z57" s="37"/>
-      <c r="AG57" s="34"/>
+      <c r="CJ56" s="34"/>
+    </row>
+    <row r="57" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S57" s="34"/>
+      <c r="U57" s="34"/>
+      <c r="W57" s="34"/>
+      <c r="Y57" s="34"/>
+      <c r="Z57"/>
+      <c r="AA57" s="37"/>
+      <c r="AG57"/>
       <c r="AI57" s="34"/>
       <c r="AK57" s="34"/>
       <c r="AM57" s="34"/>
-      <c r="AO57" s="37"/>
-      <c r="AV57" s="34"/>
+      <c r="AO57" s="34"/>
+      <c r="AQ57" s="37"/>
+      <c r="AV57"/>
       <c r="AX57" s="34"/>
       <c r="AZ57" s="34"/>
       <c r="BB57" s="34"/>
       <c r="BD57" s="34"/>
-      <c r="BE57" s="19"/>
-      <c r="BK57" s="34"/>
+      <c r="BF57" s="34"/>
+      <c r="BG57" s="19"/>
+      <c r="BK57"/>
       <c r="BM57" s="34"/>
       <c r="BO57" s="34"/>
       <c r="BQ57" s="34"/>
-      <c r="BS57" s="37"/>
+      <c r="BS57" s="34"/>
+      <c r="BU57" s="37"/>
       <c r="BX57"/>
-      <c r="BZ57" s="34"/>
       <c r="CB57" s="34"/>
       <c r="CD57" s="34"/>
       <c r="CF57" s="34"/>
       <c r="CH57" s="34"/>
-    </row>
-    <row r="58" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R58" s="34"/>
-      <c r="T58" s="34"/>
-      <c r="V58" s="34"/>
-      <c r="X58" s="34"/>
-      <c r="Z58" s="37"/>
-      <c r="AG58" s="34"/>
+      <c r="CJ57" s="34"/>
+    </row>
+    <row r="58" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S58" s="34"/>
+      <c r="U58" s="34"/>
+      <c r="W58" s="34"/>
+      <c r="Y58" s="34"/>
+      <c r="Z58"/>
+      <c r="AA58" s="37"/>
+      <c r="AG58"/>
       <c r="AI58" s="34"/>
       <c r="AK58" s="34"/>
       <c r="AM58" s="34"/>
-      <c r="AO58" s="37"/>
-      <c r="AV58" s="34"/>
+      <c r="AO58" s="34"/>
+      <c r="AQ58" s="37"/>
+      <c r="AV58"/>
       <c r="AX58" s="34"/>
       <c r="AZ58" s="34"/>
       <c r="BB58" s="34"/>
       <c r="BD58" s="34"/>
-      <c r="BE58" s="19"/>
-      <c r="BK58" s="34"/>
+      <c r="BF58" s="34"/>
+      <c r="BG58" s="19"/>
+      <c r="BK58"/>
       <c r="BM58" s="34"/>
       <c r="BO58" s="34"/>
       <c r="BQ58" s="34"/>
-      <c r="BS58" s="37"/>
+      <c r="BS58" s="34"/>
+      <c r="BU58" s="37"/>
       <c r="BX58"/>
-      <c r="BZ58" s="34"/>
       <c r="CB58" s="34"/>
       <c r="CD58" s="34"/>
       <c r="CF58" s="34"/>
       <c r="CH58" s="34"/>
-    </row>
-    <row r="59" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R59" s="34"/>
-      <c r="T59" s="34"/>
-      <c r="V59" s="34"/>
-      <c r="X59" s="34"/>
-      <c r="Z59" s="37"/>
-      <c r="AG59" s="34"/>
+      <c r="CJ58" s="34"/>
+    </row>
+    <row r="59" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S59" s="34"/>
+      <c r="U59" s="34"/>
+      <c r="W59" s="34"/>
+      <c r="Y59" s="34"/>
+      <c r="Z59"/>
+      <c r="AA59" s="37"/>
+      <c r="AG59"/>
       <c r="AI59" s="34"/>
       <c r="AK59" s="34"/>
       <c r="AM59" s="34"/>
-      <c r="AO59" s="37"/>
-      <c r="AV59" s="34"/>
+      <c r="AO59" s="34"/>
+      <c r="AQ59" s="37"/>
+      <c r="AV59"/>
       <c r="AX59" s="34"/>
       <c r="AZ59" s="34"/>
       <c r="BB59" s="34"/>
       <c r="BD59" s="34"/>
-      <c r="BE59" s="19"/>
-      <c r="BK59" s="34"/>
+      <c r="BF59" s="34"/>
+      <c r="BG59" s="19"/>
+      <c r="BK59"/>
       <c r="BM59" s="34"/>
       <c r="BO59" s="34"/>
       <c r="BQ59" s="34"/>
-      <c r="BS59" s="37"/>
+      <c r="BS59" s="34"/>
+      <c r="BU59" s="37"/>
       <c r="BX59"/>
-      <c r="BZ59" s="34"/>
       <c r="CB59" s="34"/>
       <c r="CD59" s="34"/>
       <c r="CF59" s="34"/>
       <c r="CH59" s="34"/>
-    </row>
-    <row r="60" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="V60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Z60" s="37"/>
-      <c r="AG60" s="34"/>
+      <c r="CJ59" s="34"/>
+    </row>
+    <row r="60" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S60" s="34"/>
+      <c r="U60" s="34"/>
+      <c r="W60" s="34"/>
+      <c r="Y60" s="34"/>
+      <c r="Z60"/>
+      <c r="AA60" s="37"/>
+      <c r="AG60"/>
       <c r="AI60" s="34"/>
       <c r="AK60" s="34"/>
       <c r="AM60" s="34"/>
-      <c r="AO60" s="37"/>
-      <c r="AV60" s="34"/>
+      <c r="AO60" s="34"/>
+      <c r="AQ60" s="37"/>
+      <c r="AV60"/>
       <c r="AX60" s="34"/>
       <c r="AZ60" s="34"/>
       <c r="BB60" s="34"/>
       <c r="BD60" s="34"/>
-      <c r="BE60" s="19"/>
-      <c r="BK60" s="34"/>
+      <c r="BF60" s="34"/>
+      <c r="BG60" s="19"/>
+      <c r="BK60"/>
       <c r="BM60" s="34"/>
       <c r="BO60" s="34"/>
       <c r="BQ60" s="34"/>
-      <c r="BS60" s="37"/>
+      <c r="BS60" s="34"/>
+      <c r="BU60" s="37"/>
       <c r="BX60"/>
-      <c r="BZ60" s="34"/>
       <c r="CB60" s="34"/>
       <c r="CD60" s="34"/>
       <c r="CF60" s="34"/>
       <c r="CH60" s="34"/>
-    </row>
-    <row r="61" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R61" s="34"/>
-      <c r="T61" s="34"/>
-      <c r="V61" s="34"/>
-      <c r="X61" s="34"/>
-      <c r="Z61" s="37"/>
-      <c r="AG61" s="34"/>
+      <c r="CJ60" s="34"/>
+    </row>
+    <row r="61" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S61" s="34"/>
+      <c r="U61" s="34"/>
+      <c r="W61" s="34"/>
+      <c r="Y61" s="34"/>
+      <c r="Z61"/>
+      <c r="AA61" s="37"/>
+      <c r="AG61"/>
       <c r="AI61" s="34"/>
       <c r="AK61" s="34"/>
       <c r="AM61" s="34"/>
-      <c r="AO61" s="37"/>
-      <c r="AV61" s="34"/>
+      <c r="AO61" s="34"/>
+      <c r="AQ61" s="37"/>
+      <c r="AV61"/>
       <c r="AX61" s="34"/>
       <c r="AZ61" s="34"/>
       <c r="BB61" s="34"/>
       <c r="BD61" s="34"/>
-      <c r="BE61" s="19"/>
-      <c r="BK61" s="34"/>
+      <c r="BF61" s="34"/>
+      <c r="BG61" s="19"/>
+      <c r="BK61"/>
       <c r="BM61" s="34"/>
       <c r="BO61" s="34"/>
       <c r="BQ61" s="34"/>
-      <c r="BS61" s="37"/>
+      <c r="BS61" s="34"/>
+      <c r="BU61" s="37"/>
       <c r="BX61"/>
-      <c r="BZ61" s="34"/>
       <c r="CB61" s="34"/>
       <c r="CD61" s="34"/>
       <c r="CF61" s="34"/>
       <c r="CH61" s="34"/>
-    </row>
-    <row r="62" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R62" s="34"/>
-      <c r="T62" s="34"/>
-      <c r="V62" s="34"/>
-      <c r="X62" s="34"/>
-      <c r="Z62" s="37"/>
-      <c r="AG62" s="34"/>
+      <c r="CJ61" s="34"/>
+    </row>
+    <row r="62" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S62" s="34"/>
+      <c r="U62" s="34"/>
+      <c r="W62" s="34"/>
+      <c r="Y62" s="34"/>
+      <c r="Z62"/>
+      <c r="AA62" s="37"/>
+      <c r="AG62"/>
       <c r="AI62" s="34"/>
       <c r="AK62" s="34"/>
       <c r="AM62" s="34"/>
-      <c r="AO62" s="37"/>
-      <c r="AV62" s="34"/>
+      <c r="AO62" s="34"/>
+      <c r="AQ62" s="37"/>
+      <c r="AV62"/>
       <c r="AX62" s="34"/>
       <c r="AZ62" s="34"/>
       <c r="BB62" s="34"/>
       <c r="BD62" s="34"/>
-      <c r="BE62" s="19"/>
-      <c r="BK62" s="34"/>
+      <c r="BF62" s="34"/>
+      <c r="BG62" s="19"/>
+      <c r="BK62"/>
       <c r="BM62" s="34"/>
       <c r="BO62" s="34"/>
       <c r="BQ62" s="34"/>
-      <c r="BS62" s="37"/>
+      <c r="BS62" s="34"/>
+      <c r="BU62" s="37"/>
       <c r="BX62"/>
-      <c r="BZ62" s="34"/>
       <c r="CB62" s="34"/>
       <c r="CD62" s="34"/>
       <c r="CF62" s="34"/>
       <c r="CH62" s="34"/>
-    </row>
-    <row r="63" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R63" s="34"/>
-      <c r="T63" s="34"/>
-      <c r="V63" s="34"/>
-      <c r="X63" s="34"/>
-      <c r="Z63" s="37"/>
-      <c r="AG63" s="34"/>
+      <c r="CJ62" s="34"/>
+    </row>
+    <row r="63" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S63" s="34"/>
+      <c r="U63" s="34"/>
+      <c r="W63" s="34"/>
+      <c r="Y63" s="34"/>
+      <c r="Z63"/>
+      <c r="AA63" s="37"/>
+      <c r="AG63"/>
       <c r="AI63" s="34"/>
       <c r="AK63" s="34"/>
       <c r="AM63" s="34"/>
-      <c r="AO63" s="37"/>
-      <c r="AV63" s="34"/>
+      <c r="AO63" s="34"/>
+      <c r="AQ63" s="37"/>
+      <c r="AV63"/>
       <c r="AX63" s="34"/>
       <c r="AZ63" s="34"/>
       <c r="BB63" s="34"/>
       <c r="BD63" s="34"/>
-      <c r="BE63" s="19"/>
-      <c r="BK63" s="34"/>
+      <c r="BF63" s="34"/>
+      <c r="BG63" s="19"/>
+      <c r="BK63"/>
       <c r="BM63" s="34"/>
       <c r="BO63" s="34"/>
       <c r="BQ63" s="34"/>
-      <c r="BS63" s="37"/>
+      <c r="BS63" s="34"/>
+      <c r="BU63" s="37"/>
       <c r="BX63"/>
-      <c r="BZ63" s="34"/>
       <c r="CB63" s="34"/>
       <c r="CD63" s="34"/>
       <c r="CF63" s="34"/>
       <c r="CH63" s="34"/>
-    </row>
-    <row r="64" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R64" s="34"/>
-      <c r="T64" s="34"/>
-      <c r="V64" s="34"/>
-      <c r="X64" s="34"/>
-      <c r="Z64" s="37"/>
-      <c r="AG64" s="34"/>
+      <c r="CJ63" s="34"/>
+    </row>
+    <row r="64" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S64" s="34"/>
+      <c r="U64" s="34"/>
+      <c r="W64" s="34"/>
+      <c r="Y64" s="34"/>
+      <c r="Z64"/>
+      <c r="AA64" s="37"/>
+      <c r="AG64"/>
       <c r="AI64" s="34"/>
       <c r="AK64" s="34"/>
       <c r="AM64" s="34"/>
-      <c r="AO64" s="37"/>
-      <c r="AV64" s="34"/>
+      <c r="AO64" s="34"/>
+      <c r="AQ64" s="37"/>
+      <c r="AV64"/>
       <c r="AX64" s="34"/>
       <c r="AZ64" s="34"/>
       <c r="BB64" s="34"/>
       <c r="BD64" s="34"/>
-      <c r="BE64" s="19"/>
-      <c r="BK64" s="34"/>
+      <c r="BF64" s="34"/>
+      <c r="BG64" s="19"/>
+      <c r="BK64"/>
       <c r="BM64" s="34"/>
       <c r="BO64" s="34"/>
       <c r="BQ64" s="34"/>
-      <c r="BS64" s="37"/>
+      <c r="BS64" s="34"/>
+      <c r="BU64" s="37"/>
       <c r="BX64"/>
-      <c r="BZ64" s="34"/>
       <c r="CB64" s="34"/>
       <c r="CD64" s="34"/>
       <c r="CF64" s="34"/>
       <c r="CH64" s="34"/>
-    </row>
-    <row r="65" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R65" s="34"/>
-      <c r="T65" s="34"/>
-      <c r="V65" s="34"/>
-      <c r="X65" s="34"/>
-      <c r="Z65" s="37"/>
-      <c r="AG65" s="34"/>
+      <c r="CJ64" s="34"/>
+    </row>
+    <row r="65" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S65" s="34"/>
+      <c r="U65" s="34"/>
+      <c r="W65" s="34"/>
+      <c r="Y65" s="34"/>
+      <c r="Z65"/>
+      <c r="AA65" s="37"/>
+      <c r="AG65"/>
       <c r="AI65" s="34"/>
       <c r="AK65" s="34"/>
       <c r="AM65" s="34"/>
-      <c r="AO65" s="37"/>
-      <c r="AV65" s="34"/>
+      <c r="AO65" s="34"/>
+      <c r="AQ65" s="37"/>
+      <c r="AV65"/>
       <c r="AX65" s="34"/>
       <c r="AZ65" s="34"/>
       <c r="BB65" s="34"/>
       <c r="BD65" s="34"/>
-      <c r="BE65" s="19"/>
-      <c r="BK65" s="34"/>
+      <c r="BF65" s="34"/>
+      <c r="BG65" s="19"/>
+      <c r="BK65"/>
       <c r="BM65" s="34"/>
       <c r="BO65" s="34"/>
       <c r="BQ65" s="34"/>
-      <c r="BS65" s="37"/>
+      <c r="BS65" s="34"/>
+      <c r="BU65" s="37"/>
       <c r="BX65"/>
-      <c r="BZ65" s="34"/>
       <c r="CB65" s="34"/>
       <c r="CD65" s="34"/>
       <c r="CF65" s="34"/>
       <c r="CH65" s="34"/>
-    </row>
-    <row r="66" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R66" s="34"/>
-      <c r="T66" s="34"/>
-      <c r="V66" s="34"/>
-      <c r="X66" s="34"/>
-      <c r="Z66" s="37"/>
-      <c r="AG66" s="34"/>
+      <c r="CJ65" s="34"/>
+    </row>
+    <row r="66" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S66" s="34"/>
+      <c r="U66" s="34"/>
+      <c r="W66" s="34"/>
+      <c r="Y66" s="34"/>
+      <c r="Z66"/>
+      <c r="AA66" s="37"/>
+      <c r="AG66"/>
       <c r="AI66" s="34"/>
       <c r="AK66" s="34"/>
       <c r="AM66" s="34"/>
-      <c r="AO66" s="37"/>
-      <c r="AV66" s="34"/>
+      <c r="AO66" s="34"/>
+      <c r="AQ66" s="37"/>
+      <c r="AV66"/>
       <c r="AX66" s="34"/>
       <c r="AZ66" s="34"/>
       <c r="BB66" s="34"/>
       <c r="BD66" s="34"/>
-      <c r="BE66" s="19"/>
-      <c r="BK66" s="34"/>
+      <c r="BF66" s="34"/>
+      <c r="BG66" s="19"/>
+      <c r="BK66"/>
       <c r="BM66" s="34"/>
       <c r="BO66" s="34"/>
       <c r="BQ66" s="34"/>
-      <c r="BS66" s="37"/>
+      <c r="BS66" s="34"/>
+      <c r="BU66" s="37"/>
       <c r="BX66"/>
-      <c r="BZ66" s="34"/>
       <c r="CB66" s="34"/>
       <c r="CD66" s="34"/>
       <c r="CF66" s="34"/>
       <c r="CH66" s="34"/>
-    </row>
-    <row r="67" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R67" s="34"/>
-      <c r="T67" s="34"/>
-      <c r="V67" s="34"/>
-      <c r="X67" s="34"/>
-      <c r="Z67" s="37"/>
-      <c r="AG67" s="34"/>
+      <c r="CJ66" s="34"/>
+    </row>
+    <row r="67" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S67" s="34"/>
+      <c r="U67" s="34"/>
+      <c r="W67" s="34"/>
+      <c r="Y67" s="34"/>
+      <c r="Z67"/>
+      <c r="AA67" s="37"/>
+      <c r="AG67"/>
       <c r="AI67" s="34"/>
       <c r="AK67" s="34"/>
       <c r="AM67" s="34"/>
-      <c r="AO67" s="37"/>
-      <c r="AV67" s="34"/>
+      <c r="AO67" s="34"/>
+      <c r="AQ67" s="37"/>
+      <c r="AV67"/>
       <c r="AX67" s="34"/>
       <c r="AZ67" s="34"/>
       <c r="BB67" s="34"/>
       <c r="BD67" s="34"/>
-      <c r="BE67" s="19"/>
-      <c r="BK67" s="34"/>
+      <c r="BF67" s="34"/>
+      <c r="BG67" s="19"/>
+      <c r="BK67"/>
       <c r="BM67" s="34"/>
       <c r="BO67" s="34"/>
       <c r="BQ67" s="34"/>
-      <c r="BS67" s="37"/>
+      <c r="BS67" s="34"/>
+      <c r="BU67" s="37"/>
       <c r="BX67"/>
-      <c r="BZ67" s="34"/>
       <c r="CB67" s="34"/>
       <c r="CD67" s="34"/>
       <c r="CF67" s="34"/>
       <c r="CH67" s="34"/>
-    </row>
-    <row r="68" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R68" s="34"/>
-      <c r="T68" s="34"/>
-      <c r="V68" s="34"/>
-      <c r="X68" s="34"/>
-      <c r="Z68" s="37"/>
-      <c r="AG68" s="34"/>
+      <c r="CJ67" s="34"/>
+    </row>
+    <row r="68" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S68" s="34"/>
+      <c r="U68" s="34"/>
+      <c r="W68" s="34"/>
+      <c r="Y68" s="34"/>
+      <c r="Z68"/>
+      <c r="AA68" s="37"/>
+      <c r="AG68"/>
       <c r="AI68" s="34"/>
       <c r="AK68" s="34"/>
       <c r="AM68" s="34"/>
-      <c r="AO68" s="37"/>
-      <c r="AV68" s="34"/>
+      <c r="AO68" s="34"/>
+      <c r="AQ68" s="37"/>
+      <c r="AV68"/>
       <c r="AX68" s="34"/>
       <c r="AZ68" s="34"/>
       <c r="BB68" s="34"/>
       <c r="BD68" s="34"/>
-      <c r="BE68" s="19"/>
-      <c r="BK68" s="34"/>
+      <c r="BF68" s="34"/>
+      <c r="BG68" s="19"/>
+      <c r="BK68"/>
       <c r="BM68" s="34"/>
       <c r="BO68" s="34"/>
       <c r="BQ68" s="34"/>
-      <c r="BS68" s="37"/>
+      <c r="BS68" s="34"/>
+      <c r="BU68" s="37"/>
       <c r="BX68"/>
-      <c r="BZ68" s="34"/>
       <c r="CB68" s="34"/>
       <c r="CD68" s="34"/>
       <c r="CF68" s="34"/>
       <c r="CH68" s="34"/>
-    </row>
-    <row r="69" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R69" s="34"/>
-      <c r="T69" s="34"/>
-      <c r="V69" s="34"/>
-      <c r="X69" s="34"/>
-      <c r="Z69" s="37"/>
-      <c r="AG69" s="34"/>
+      <c r="CJ68" s="34"/>
+    </row>
+    <row r="69" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S69" s="34"/>
+      <c r="U69" s="34"/>
+      <c r="W69" s="34"/>
+      <c r="Y69" s="34"/>
+      <c r="Z69"/>
+      <c r="AA69" s="37"/>
+      <c r="AG69"/>
       <c r="AI69" s="34"/>
       <c r="AK69" s="34"/>
       <c r="AM69" s="34"/>
-      <c r="AO69" s="37"/>
-      <c r="AV69" s="34"/>
+      <c r="AO69" s="34"/>
+      <c r="AQ69" s="37"/>
+      <c r="AV69"/>
       <c r="AX69" s="34"/>
       <c r="AZ69" s="34"/>
       <c r="BB69" s="34"/>
       <c r="BD69" s="34"/>
-      <c r="BE69" s="19"/>
-      <c r="BK69" s="34"/>
+      <c r="BF69" s="34"/>
+      <c r="BG69" s="19"/>
+      <c r="BK69"/>
       <c r="BM69" s="34"/>
       <c r="BO69" s="34"/>
       <c r="BQ69" s="34"/>
-      <c r="BS69" s="37"/>
+      <c r="BS69" s="34"/>
+      <c r="BU69" s="37"/>
       <c r="BX69"/>
-      <c r="BZ69" s="34"/>
       <c r="CB69" s="34"/>
       <c r="CD69" s="34"/>
       <c r="CF69" s="34"/>
       <c r="CH69" s="34"/>
-    </row>
-    <row r="70" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R70" s="34"/>
-      <c r="T70" s="34"/>
-      <c r="V70" s="34"/>
-      <c r="X70" s="34"/>
-      <c r="Z70" s="37"/>
-      <c r="AG70" s="34"/>
+      <c r="CJ69" s="34"/>
+    </row>
+    <row r="70" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S70" s="34"/>
+      <c r="U70" s="34"/>
+      <c r="W70" s="34"/>
+      <c r="Y70" s="34"/>
+      <c r="Z70"/>
+      <c r="AA70" s="37"/>
+      <c r="AG70"/>
       <c r="AI70" s="34"/>
       <c r="AK70" s="34"/>
       <c r="AM70" s="34"/>
-      <c r="AO70" s="37"/>
-      <c r="AV70" s="34"/>
+      <c r="AO70" s="34"/>
+      <c r="AQ70" s="37"/>
+      <c r="AV70"/>
       <c r="AX70" s="34"/>
       <c r="AZ70" s="34"/>
       <c r="BB70" s="34"/>
       <c r="BD70" s="34"/>
-      <c r="BE70" s="19"/>
-      <c r="BK70" s="34"/>
+      <c r="BF70" s="34"/>
+      <c r="BG70" s="19"/>
+      <c r="BK70"/>
       <c r="BM70" s="34"/>
       <c r="BO70" s="34"/>
       <c r="BQ70" s="34"/>
-      <c r="BS70" s="37"/>
+      <c r="BS70" s="34"/>
+      <c r="BU70" s="37"/>
       <c r="BX70"/>
-      <c r="BZ70" s="34"/>
       <c r="CB70" s="34"/>
       <c r="CD70" s="34"/>
       <c r="CF70" s="34"/>
       <c r="CH70" s="34"/>
-    </row>
-    <row r="71" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R71" s="34"/>
-      <c r="T71" s="34"/>
-      <c r="V71" s="34"/>
-      <c r="X71" s="34"/>
-      <c r="Z71" s="37"/>
-      <c r="AG71" s="34"/>
+      <c r="CJ70" s="34"/>
+    </row>
+    <row r="71" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S71" s="34"/>
+      <c r="U71" s="34"/>
+      <c r="W71" s="34"/>
+      <c r="Y71" s="34"/>
+      <c r="Z71"/>
+      <c r="AA71" s="37"/>
+      <c r="AG71"/>
       <c r="AI71" s="34"/>
       <c r="AK71" s="34"/>
       <c r="AM71" s="34"/>
-      <c r="AO71" s="37"/>
-      <c r="AV71" s="34"/>
+      <c r="AO71" s="34"/>
+      <c r="AQ71" s="37"/>
+      <c r="AV71"/>
       <c r="AX71" s="34"/>
       <c r="AZ71" s="34"/>
       <c r="BB71" s="34"/>
       <c r="BD71" s="34"/>
-      <c r="BE71" s="19"/>
-      <c r="BK71" s="34"/>
+      <c r="BF71" s="34"/>
+      <c r="BG71" s="19"/>
+      <c r="BK71"/>
       <c r="BM71" s="34"/>
       <c r="BO71" s="34"/>
       <c r="BQ71" s="34"/>
-      <c r="BS71" s="37"/>
+      <c r="BS71" s="34"/>
+      <c r="BU71" s="37"/>
       <c r="BX71"/>
-      <c r="BZ71" s="34"/>
       <c r="CB71" s="34"/>
       <c r="CD71" s="34"/>
       <c r="CF71" s="34"/>
       <c r="CH71" s="34"/>
-    </row>
-    <row r="72" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R72" s="34"/>
-      <c r="T72" s="34"/>
-      <c r="V72" s="34"/>
-      <c r="X72" s="34"/>
-      <c r="Z72" s="37"/>
-      <c r="AG72" s="34"/>
+      <c r="CJ71" s="34"/>
+    </row>
+    <row r="72" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S72" s="34"/>
+      <c r="U72" s="34"/>
+      <c r="W72" s="34"/>
+      <c r="Y72" s="34"/>
+      <c r="Z72"/>
+      <c r="AA72" s="37"/>
+      <c r="AG72"/>
       <c r="AI72" s="34"/>
       <c r="AK72" s="34"/>
       <c r="AM72" s="34"/>
-      <c r="AO72" s="37"/>
-      <c r="AV72" s="34"/>
+      <c r="AO72" s="34"/>
+      <c r="AQ72" s="37"/>
+      <c r="AV72"/>
       <c r="AX72" s="34"/>
       <c r="AZ72" s="34"/>
       <c r="BB72" s="34"/>
       <c r="BD72" s="34"/>
-      <c r="BE72" s="19"/>
-      <c r="BK72" s="34"/>
+      <c r="BF72" s="34"/>
+      <c r="BG72" s="19"/>
+      <c r="BK72"/>
       <c r="BM72" s="34"/>
       <c r="BO72" s="34"/>
       <c r="BQ72" s="34"/>
-      <c r="BS72" s="37"/>
+      <c r="BS72" s="34"/>
+      <c r="BU72" s="37"/>
       <c r="BX72"/>
-      <c r="BZ72" s="34"/>
       <c r="CB72" s="34"/>
       <c r="CD72" s="34"/>
       <c r="CF72" s="34"/>
       <c r="CH72" s="34"/>
-    </row>
-    <row r="73" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R73" s="34"/>
-      <c r="T73" s="34"/>
-      <c r="V73" s="34"/>
-      <c r="X73" s="34"/>
-      <c r="Z73" s="37"/>
-      <c r="AG73" s="34"/>
+      <c r="CJ72" s="34"/>
+    </row>
+    <row r="73" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S73" s="34"/>
+      <c r="U73" s="34"/>
+      <c r="W73" s="34"/>
+      <c r="Y73" s="34"/>
+      <c r="Z73"/>
+      <c r="AA73" s="37"/>
+      <c r="AG73"/>
       <c r="AI73" s="34"/>
       <c r="AK73" s="34"/>
       <c r="AM73" s="34"/>
-      <c r="AO73" s="37"/>
-      <c r="AV73" s="34"/>
+      <c r="AO73" s="34"/>
+      <c r="AQ73" s="37"/>
+      <c r="AV73"/>
       <c r="AX73" s="34"/>
       <c r="AZ73" s="34"/>
       <c r="BB73" s="34"/>
       <c r="BD73" s="34"/>
-      <c r="BE73" s="19"/>
-      <c r="BK73" s="34"/>
+      <c r="BF73" s="34"/>
+      <c r="BG73" s="19"/>
+      <c r="BK73"/>
       <c r="BM73" s="34"/>
       <c r="BO73" s="34"/>
       <c r="BQ73" s="34"/>
-      <c r="BS73" s="37"/>
+      <c r="BS73" s="34"/>
+      <c r="BU73" s="37"/>
       <c r="BX73"/>
-      <c r="BZ73" s="34"/>
       <c r="CB73" s="34"/>
       <c r="CD73" s="34"/>
       <c r="CF73" s="34"/>
       <c r="CH73" s="34"/>
-    </row>
-    <row r="74" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R74" s="34"/>
-      <c r="T74" s="34"/>
-      <c r="V74" s="34"/>
-      <c r="X74" s="34"/>
-      <c r="Z74" s="37"/>
-      <c r="AG74" s="34"/>
+      <c r="CJ73" s="34"/>
+    </row>
+    <row r="74" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S74" s="34"/>
+      <c r="U74" s="34"/>
+      <c r="W74" s="34"/>
+      <c r="Y74" s="34"/>
+      <c r="Z74"/>
+      <c r="AA74" s="37"/>
+      <c r="AG74"/>
       <c r="AI74" s="34"/>
       <c r="AK74" s="34"/>
       <c r="AM74" s="34"/>
-      <c r="AO74" s="37"/>
-      <c r="AV74" s="34"/>
+      <c r="AO74" s="34"/>
+      <c r="AQ74" s="37"/>
+      <c r="AV74"/>
       <c r="AX74" s="34"/>
       <c r="AZ74" s="34"/>
       <c r="BB74" s="34"/>
       <c r="BD74" s="34"/>
-      <c r="BE74" s="19"/>
-      <c r="BK74" s="34"/>
+      <c r="BF74" s="34"/>
+      <c r="BG74" s="19"/>
+      <c r="BK74"/>
       <c r="BM74" s="34"/>
       <c r="BO74" s="34"/>
       <c r="BQ74" s="34"/>
-      <c r="BS74" s="37"/>
+      <c r="BS74" s="34"/>
+      <c r="BU74" s="37"/>
       <c r="BX74"/>
-      <c r="BZ74" s="34"/>
       <c r="CB74" s="34"/>
       <c r="CD74" s="34"/>
       <c r="CF74" s="34"/>
       <c r="CH74" s="34"/>
-    </row>
-    <row r="75" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R75" s="34"/>
-      <c r="T75" s="34"/>
-      <c r="V75" s="34"/>
-      <c r="X75" s="34"/>
-      <c r="Z75" s="37"/>
-      <c r="AG75" s="34"/>
+      <c r="CJ74" s="34"/>
+    </row>
+    <row r="75" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S75" s="34"/>
+      <c r="U75" s="34"/>
+      <c r="W75" s="34"/>
+      <c r="Y75" s="34"/>
+      <c r="Z75"/>
+      <c r="AA75" s="37"/>
+      <c r="AG75"/>
       <c r="AI75" s="34"/>
       <c r="AK75" s="34"/>
       <c r="AM75" s="34"/>
-      <c r="AO75" s="37"/>
-      <c r="AV75" s="34"/>
+      <c r="AO75" s="34"/>
+      <c r="AQ75" s="37"/>
+      <c r="AV75"/>
       <c r="AX75" s="34"/>
       <c r="AZ75" s="34"/>
       <c r="BB75" s="34"/>
       <c r="BD75" s="34"/>
-      <c r="BE75" s="19"/>
-      <c r="BK75" s="34"/>
+      <c r="BF75" s="34"/>
+      <c r="BG75" s="19"/>
+      <c r="BK75"/>
       <c r="BM75" s="34"/>
       <c r="BO75" s="34"/>
       <c r="BQ75" s="34"/>
-      <c r="BS75" s="37"/>
+      <c r="BS75" s="34"/>
+      <c r="BU75" s="37"/>
       <c r="BX75"/>
-      <c r="BZ75" s="34"/>
       <c r="CB75" s="34"/>
       <c r="CD75" s="34"/>
       <c r="CF75" s="34"/>
       <c r="CH75" s="34"/>
-    </row>
-    <row r="76" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R76" s="34"/>
-      <c r="T76" s="34"/>
-      <c r="V76" s="34"/>
-      <c r="X76" s="34"/>
-      <c r="Z76" s="37"/>
-      <c r="AG76" s="34"/>
+      <c r="CJ75" s="34"/>
+    </row>
+    <row r="76" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S76" s="34"/>
+      <c r="U76" s="34"/>
+      <c r="W76" s="34"/>
+      <c r="Y76" s="34"/>
+      <c r="Z76"/>
+      <c r="AA76" s="37"/>
+      <c r="AG76"/>
       <c r="AI76" s="34"/>
       <c r="AK76" s="34"/>
       <c r="AM76" s="34"/>
-      <c r="AO76" s="37"/>
-      <c r="AV76" s="34"/>
+      <c r="AO76" s="34"/>
+      <c r="AQ76" s="37"/>
+      <c r="AV76"/>
       <c r="AX76" s="34"/>
       <c r="AZ76" s="34"/>
       <c r="BB76" s="34"/>
       <c r="BD76" s="34"/>
-      <c r="BE76" s="19"/>
-      <c r="BK76" s="34"/>
+      <c r="BF76" s="34"/>
+      <c r="BG76" s="19"/>
+      <c r="BK76"/>
       <c r="BM76" s="34"/>
       <c r="BO76" s="34"/>
       <c r="BQ76" s="34"/>
-      <c r="BS76" s="37"/>
+      <c r="BS76" s="34"/>
+      <c r="BU76" s="37"/>
       <c r="BX76"/>
-      <c r="BZ76" s="34"/>
       <c r="CB76" s="34"/>
       <c r="CD76" s="34"/>
       <c r="CF76" s="34"/>
       <c r="CH76" s="34"/>
-    </row>
-    <row r="77" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R77" s="34"/>
-      <c r="T77" s="34"/>
-      <c r="V77" s="34"/>
-      <c r="X77" s="34"/>
-      <c r="Z77" s="37"/>
-      <c r="AG77" s="34"/>
+      <c r="CJ76" s="34"/>
+    </row>
+    <row r="77" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S77" s="34"/>
+      <c r="U77" s="34"/>
+      <c r="W77" s="34"/>
+      <c r="Y77" s="34"/>
+      <c r="Z77"/>
+      <c r="AA77" s="37"/>
+      <c r="AG77"/>
       <c r="AI77" s="34"/>
       <c r="AK77" s="34"/>
       <c r="AM77" s="34"/>
-      <c r="AO77" s="37"/>
-      <c r="AV77" s="34"/>
+      <c r="AO77" s="34"/>
+      <c r="AQ77" s="37"/>
+      <c r="AV77"/>
       <c r="AX77" s="34"/>
       <c r="AZ77" s="34"/>
       <c r="BB77" s="34"/>
       <c r="BD77" s="34"/>
-      <c r="BE77" s="19"/>
-      <c r="BK77" s="34"/>
+      <c r="BF77" s="34"/>
+      <c r="BG77" s="19"/>
+      <c r="BK77"/>
       <c r="BM77" s="34"/>
       <c r="BO77" s="34"/>
       <c r="BQ77" s="34"/>
-      <c r="BS77" s="37"/>
+      <c r="BS77" s="34"/>
+      <c r="BU77" s="37"/>
       <c r="BX77"/>
-      <c r="BZ77" s="34"/>
       <c r="CB77" s="34"/>
       <c r="CD77" s="34"/>
       <c r="CF77" s="34"/>
       <c r="CH77" s="34"/>
-    </row>
-    <row r="78" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R78" s="34"/>
-      <c r="T78" s="34"/>
-      <c r="V78" s="34"/>
-      <c r="X78" s="34"/>
-      <c r="Z78" s="37"/>
-      <c r="AG78" s="34"/>
+      <c r="CJ77" s="34"/>
+    </row>
+    <row r="78" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S78" s="34"/>
+      <c r="U78" s="34"/>
+      <c r="W78" s="34"/>
+      <c r="Y78" s="34"/>
+      <c r="Z78"/>
+      <c r="AA78" s="37"/>
+      <c r="AG78"/>
       <c r="AI78" s="34"/>
       <c r="AK78" s="34"/>
       <c r="AM78" s="34"/>
-      <c r="AO78" s="37"/>
-      <c r="AV78" s="34"/>
+      <c r="AO78" s="34"/>
+      <c r="AQ78" s="37"/>
+      <c r="AV78"/>
       <c r="AX78" s="34"/>
       <c r="AZ78" s="34"/>
       <c r="BB78" s="34"/>
       <c r="BD78" s="34"/>
-      <c r="BE78" s="19"/>
-      <c r="BK78" s="34"/>
+      <c r="BF78" s="34"/>
+      <c r="BG78" s="19"/>
+      <c r="BK78"/>
       <c r="BM78" s="34"/>
       <c r="BO78" s="34"/>
       <c r="BQ78" s="34"/>
-      <c r="BS78" s="37"/>
+      <c r="BS78" s="34"/>
+      <c r="BU78" s="37"/>
       <c r="BX78"/>
-      <c r="BZ78" s="34"/>
       <c r="CB78" s="34"/>
       <c r="CD78" s="34"/>
       <c r="CF78" s="34"/>
       <c r="CH78" s="34"/>
-    </row>
-    <row r="79" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R79" s="34"/>
-      <c r="T79" s="34"/>
-      <c r="V79" s="34"/>
-      <c r="X79" s="34"/>
-      <c r="Z79" s="37"/>
-      <c r="AG79" s="34"/>
+      <c r="CJ78" s="34"/>
+    </row>
+    <row r="79" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S79" s="34"/>
+      <c r="U79" s="34"/>
+      <c r="W79" s="34"/>
+      <c r="Y79" s="34"/>
+      <c r="Z79"/>
+      <c r="AA79" s="37"/>
+      <c r="AG79"/>
       <c r="AI79" s="34"/>
       <c r="AK79" s="34"/>
       <c r="AM79" s="34"/>
-      <c r="AO79" s="37"/>
-      <c r="AV79" s="34"/>
+      <c r="AO79" s="34"/>
+      <c r="AQ79" s="37"/>
+      <c r="AV79"/>
       <c r="AX79" s="34"/>
       <c r="AZ79" s="34"/>
       <c r="BB79" s="34"/>
       <c r="BD79" s="34"/>
-      <c r="BE79" s="19"/>
-      <c r="BK79" s="34"/>
+      <c r="BF79" s="34"/>
+      <c r="BG79" s="19"/>
+      <c r="BK79"/>
       <c r="BM79" s="34"/>
       <c r="BO79" s="34"/>
       <c r="BQ79" s="34"/>
-      <c r="BS79" s="37"/>
+      <c r="BS79" s="34"/>
+      <c r="BU79" s="37"/>
       <c r="BX79"/>
-      <c r="BZ79" s="34"/>
       <c r="CB79" s="34"/>
       <c r="CD79" s="34"/>
       <c r="CF79" s="34"/>
       <c r="CH79" s="34"/>
-    </row>
-    <row r="80" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R80" s="34"/>
-      <c r="T80" s="34"/>
-      <c r="V80" s="34"/>
-      <c r="X80" s="34"/>
-      <c r="Z80" s="37"/>
-      <c r="AG80" s="34"/>
+      <c r="CJ79" s="34"/>
+    </row>
+    <row r="80" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S80" s="34"/>
+      <c r="U80" s="34"/>
+      <c r="W80" s="34"/>
+      <c r="Y80" s="34"/>
+      <c r="Z80"/>
+      <c r="AA80" s="37"/>
+      <c r="AG80"/>
       <c r="AI80" s="34"/>
       <c r="AK80" s="34"/>
       <c r="AM80" s="34"/>
-      <c r="AO80" s="37"/>
-      <c r="AV80" s="34"/>
+      <c r="AO80" s="34"/>
+      <c r="AQ80" s="37"/>
+      <c r="AV80"/>
       <c r="AX80" s="34"/>
       <c r="AZ80" s="34"/>
       <c r="BB80" s="34"/>
       <c r="BD80" s="34"/>
-      <c r="BE80" s="19"/>
-      <c r="BK80" s="34"/>
+      <c r="BF80" s="34"/>
+      <c r="BG80" s="19"/>
+      <c r="BK80"/>
       <c r="BM80" s="34"/>
       <c r="BO80" s="34"/>
       <c r="BQ80" s="34"/>
-      <c r="BS80" s="37"/>
+      <c r="BS80" s="34"/>
+      <c r="BU80" s="37"/>
       <c r="BX80"/>
-      <c r="BZ80" s="34"/>
       <c r="CB80" s="34"/>
       <c r="CD80" s="34"/>
       <c r="CF80" s="34"/>
       <c r="CH80" s="34"/>
-    </row>
-    <row r="81" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R81" s="34"/>
-      <c r="T81" s="34"/>
-      <c r="V81" s="34"/>
-      <c r="X81" s="34"/>
-      <c r="Z81" s="37"/>
-      <c r="AG81" s="34"/>
+      <c r="CJ80" s="34"/>
+    </row>
+    <row r="81" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S81" s="34"/>
+      <c r="U81" s="34"/>
+      <c r="W81" s="34"/>
+      <c r="Y81" s="34"/>
+      <c r="Z81"/>
+      <c r="AA81" s="37"/>
+      <c r="AG81"/>
       <c r="AI81" s="34"/>
       <c r="AK81" s="34"/>
       <c r="AM81" s="34"/>
-      <c r="AO81" s="37"/>
-      <c r="AV81" s="34"/>
+      <c r="AO81" s="34"/>
+      <c r="AQ81" s="37"/>
+      <c r="AV81"/>
       <c r="AX81" s="34"/>
       <c r="AZ81" s="34"/>
       <c r="BB81" s="34"/>
       <c r="BD81" s="34"/>
-      <c r="BE81" s="19"/>
-      <c r="BK81" s="34"/>
+      <c r="BF81" s="34"/>
+      <c r="BG81" s="19"/>
+      <c r="BK81"/>
       <c r="BM81" s="34"/>
       <c r="BO81" s="34"/>
       <c r="BQ81" s="34"/>
-      <c r="BS81" s="37"/>
+      <c r="BS81" s="34"/>
+      <c r="BU81" s="37"/>
       <c r="BX81"/>
-      <c r="BZ81" s="34"/>
       <c r="CB81" s="34"/>
       <c r="CD81" s="34"/>
       <c r="CF81" s="34"/>
       <c r="CH81" s="34"/>
-    </row>
-    <row r="82" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R82" s="34"/>
-      <c r="T82" s="34"/>
-      <c r="V82" s="34"/>
-      <c r="X82" s="34"/>
-      <c r="Z82" s="37"/>
-      <c r="AG82" s="34"/>
+      <c r="CJ81" s="34"/>
+    </row>
+    <row r="82" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S82" s="34"/>
+      <c r="U82" s="34"/>
+      <c r="W82" s="34"/>
+      <c r="Y82" s="34"/>
+      <c r="Z82"/>
+      <c r="AA82" s="37"/>
+      <c r="AG82"/>
       <c r="AI82" s="34"/>
       <c r="AK82" s="34"/>
       <c r="AM82" s="34"/>
-      <c r="AO82" s="37"/>
-      <c r="AV82" s="34"/>
+      <c r="AO82" s="34"/>
+      <c r="AQ82" s="37"/>
+      <c r="AV82"/>
       <c r="AX82" s="34"/>
       <c r="AZ82" s="34"/>
       <c r="BB82" s="34"/>
       <c r="BD82" s="34"/>
-      <c r="BE82" s="19"/>
-      <c r="BK82" s="34"/>
+      <c r="BF82" s="34"/>
+      <c r="BG82" s="19"/>
+      <c r="BK82"/>
       <c r="BM82" s="34"/>
       <c r="BO82" s="34"/>
       <c r="BQ82" s="34"/>
-      <c r="BS82" s="37"/>
+      <c r="BS82" s="34"/>
+      <c r="BU82" s="37"/>
       <c r="BX82"/>
-      <c r="BZ82" s="34"/>
       <c r="CB82" s="34"/>
       <c r="CD82" s="34"/>
       <c r="CF82" s="34"/>
       <c r="CH82" s="34"/>
-    </row>
-    <row r="83" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R83" s="34"/>
-      <c r="T83" s="34"/>
-      <c r="V83" s="34"/>
-      <c r="X83" s="34"/>
-      <c r="Z83" s="37"/>
-      <c r="AG83" s="34"/>
+      <c r="CJ82" s="34"/>
+    </row>
+    <row r="83" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S83" s="34"/>
+      <c r="U83" s="34"/>
+      <c r="W83" s="34"/>
+      <c r="Y83" s="34"/>
+      <c r="Z83"/>
+      <c r="AA83" s="37"/>
+      <c r="AG83"/>
       <c r="AI83" s="34"/>
       <c r="AK83" s="34"/>
       <c r="AM83" s="34"/>
-      <c r="AO83" s="37"/>
-      <c r="AV83" s="34"/>
+      <c r="AO83" s="34"/>
+      <c r="AQ83" s="37"/>
+      <c r="AV83"/>
       <c r="AX83" s="34"/>
       <c r="AZ83" s="34"/>
       <c r="BB83" s="34"/>
       <c r="BD83" s="34"/>
-      <c r="BE83" s="19"/>
-      <c r="BK83" s="34"/>
+      <c r="BF83" s="34"/>
+      <c r="BG83" s="19"/>
+      <c r="BK83"/>
       <c r="BM83" s="34"/>
       <c r="BO83" s="34"/>
       <c r="BQ83" s="34"/>
-      <c r="BS83" s="37"/>
+      <c r="BS83" s="34"/>
+      <c r="BU83" s="37"/>
       <c r="BX83"/>
-      <c r="BZ83" s="34"/>
       <c r="CB83" s="34"/>
       <c r="CD83" s="34"/>
       <c r="CF83" s="34"/>
       <c r="CH83" s="34"/>
-    </row>
-    <row r="84" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R84" s="34"/>
-      <c r="T84" s="34"/>
-      <c r="V84" s="34"/>
-      <c r="X84" s="34"/>
-      <c r="Z84" s="37"/>
-      <c r="AG84" s="34"/>
+      <c r="CJ83" s="34"/>
+    </row>
+    <row r="84" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S84" s="34"/>
+      <c r="U84" s="34"/>
+      <c r="W84" s="34"/>
+      <c r="Y84" s="34"/>
+      <c r="Z84"/>
+      <c r="AA84" s="37"/>
+      <c r="AG84"/>
       <c r="AI84" s="34"/>
       <c r="AK84" s="34"/>
       <c r="AM84" s="34"/>
-      <c r="AO84" s="37"/>
-      <c r="AV84" s="34"/>
+      <c r="AO84" s="34"/>
+      <c r="AQ84" s="37"/>
+      <c r="AV84"/>
       <c r="AX84" s="34"/>
       <c r="AZ84" s="34"/>
       <c r="BB84" s="34"/>
       <c r="BD84" s="34"/>
-      <c r="BE84" s="19"/>
-      <c r="BK84" s="34"/>
+      <c r="BF84" s="34"/>
+      <c r="BG84" s="19"/>
+      <c r="BK84"/>
       <c r="BM84" s="34"/>
       <c r="BO84" s="34"/>
       <c r="BQ84" s="34"/>
-      <c r="BS84" s="37"/>
+      <c r="BS84" s="34"/>
+      <c r="BU84" s="37"/>
       <c r="BX84"/>
-      <c r="BZ84" s="34"/>
       <c r="CB84" s="34"/>
       <c r="CD84" s="34"/>
       <c r="CF84" s="34"/>
       <c r="CH84" s="34"/>
-    </row>
-    <row r="85" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R85" s="34"/>
-      <c r="T85" s="34"/>
-      <c r="V85" s="34"/>
-      <c r="X85" s="34"/>
-      <c r="Z85" s="37"/>
-      <c r="AG85" s="34"/>
+      <c r="CJ84" s="34"/>
+    </row>
+    <row r="85" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S85" s="34"/>
+      <c r="U85" s="34"/>
+      <c r="W85" s="34"/>
+      <c r="Y85" s="34"/>
+      <c r="Z85"/>
+      <c r="AA85" s="37"/>
+      <c r="AG85"/>
       <c r="AI85" s="34"/>
       <c r="AK85" s="34"/>
       <c r="AM85" s="34"/>
-      <c r="AO85" s="37"/>
-      <c r="AV85" s="34"/>
+      <c r="AO85" s="34"/>
+      <c r="AQ85" s="37"/>
+      <c r="AV85"/>
       <c r="AX85" s="34"/>
       <c r="AZ85" s="34"/>
       <c r="BB85" s="34"/>
       <c r="BD85" s="34"/>
-      <c r="BE85" s="19"/>
-      <c r="BK85" s="34"/>
+      <c r="BF85" s="34"/>
+      <c r="BG85" s="19"/>
+      <c r="BK85"/>
       <c r="BM85" s="34"/>
       <c r="BO85" s="34"/>
       <c r="BQ85" s="34"/>
-      <c r="BS85" s="37"/>
+      <c r="BS85" s="34"/>
+      <c r="BU85" s="37"/>
       <c r="BX85"/>
-      <c r="BZ85" s="34"/>
       <c r="CB85" s="34"/>
       <c r="CD85" s="34"/>
       <c r="CF85" s="34"/>
       <c r="CH85" s="34"/>
-    </row>
-    <row r="86" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R86" s="34"/>
-      <c r="T86" s="34"/>
-      <c r="V86" s="34"/>
-      <c r="X86" s="34"/>
-      <c r="Z86" s="37"/>
-      <c r="AG86" s="34"/>
+      <c r="CJ85" s="34"/>
+    </row>
+    <row r="86" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S86" s="34"/>
+      <c r="U86" s="34"/>
+      <c r="W86" s="34"/>
+      <c r="Y86" s="34"/>
+      <c r="Z86"/>
+      <c r="AA86" s="37"/>
+      <c r="AG86"/>
       <c r="AI86" s="34"/>
       <c r="AK86" s="34"/>
       <c r="AM86" s="34"/>
-      <c r="AO86" s="37"/>
-      <c r="AV86" s="34"/>
+      <c r="AO86" s="34"/>
+      <c r="AQ86" s="37"/>
+      <c r="AV86"/>
       <c r="AX86" s="34"/>
       <c r="AZ86" s="34"/>
       <c r="BB86" s="34"/>
       <c r="BD86" s="34"/>
-      <c r="BE86" s="19"/>
-      <c r="BK86" s="34"/>
+      <c r="BF86" s="34"/>
+      <c r="BG86" s="19"/>
+      <c r="BK86"/>
       <c r="BM86" s="34"/>
       <c r="BO86" s="34"/>
       <c r="BQ86" s="34"/>
-      <c r="BS86" s="37"/>
+      <c r="BS86" s="34"/>
+      <c r="BU86" s="37"/>
       <c r="BX86"/>
-      <c r="BZ86" s="34"/>
       <c r="CB86" s="34"/>
       <c r="CD86" s="34"/>
       <c r="CF86" s="34"/>
       <c r="CH86" s="34"/>
-    </row>
-    <row r="87" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R87" s="34"/>
-      <c r="T87" s="34"/>
-      <c r="V87" s="34"/>
-      <c r="X87" s="34"/>
-      <c r="Z87" s="37"/>
-      <c r="AG87" s="34"/>
+      <c r="CJ86" s="34"/>
+    </row>
+    <row r="87" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S87" s="34"/>
+      <c r="U87" s="34"/>
+      <c r="W87" s="34"/>
+      <c r="Y87" s="34"/>
+      <c r="Z87"/>
+      <c r="AA87" s="37"/>
+      <c r="AG87"/>
       <c r="AI87" s="34"/>
       <c r="AK87" s="34"/>
       <c r="AM87" s="34"/>
-      <c r="AO87" s="37"/>
-      <c r="AV87" s="34"/>
+      <c r="AO87" s="34"/>
+      <c r="AQ87" s="37"/>
+      <c r="AV87"/>
       <c r="AX87" s="34"/>
       <c r="AZ87" s="34"/>
       <c r="BB87" s="34"/>
       <c r="BD87" s="34"/>
-      <c r="BE87" s="19"/>
-      <c r="BK87" s="34"/>
+      <c r="BF87" s="34"/>
+      <c r="BG87" s="19"/>
+      <c r="BK87"/>
       <c r="BM87" s="34"/>
       <c r="BO87" s="34"/>
       <c r="BQ87" s="34"/>
-      <c r="BS87" s="37"/>
+      <c r="BS87" s="34"/>
+      <c r="BU87" s="37"/>
       <c r="BX87"/>
-      <c r="BZ87" s="34"/>
       <c r="CB87" s="34"/>
       <c r="CD87" s="34"/>
       <c r="CF87" s="34"/>
       <c r="CH87" s="34"/>
-    </row>
-    <row r="88" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R88" s="34"/>
-      <c r="T88" s="34"/>
-      <c r="V88" s="34"/>
-      <c r="X88" s="34"/>
-      <c r="Z88" s="37"/>
-      <c r="AG88" s="34"/>
+      <c r="CJ87" s="34"/>
+    </row>
+    <row r="88" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S88" s="34"/>
+      <c r="U88" s="34"/>
+      <c r="W88" s="34"/>
+      <c r="Y88" s="34"/>
+      <c r="Z88"/>
+      <c r="AA88" s="37"/>
+      <c r="AG88"/>
       <c r="AI88" s="34"/>
       <c r="AK88" s="34"/>
       <c r="AM88" s="34"/>
-      <c r="AO88" s="37"/>
-      <c r="AV88" s="34"/>
+      <c r="AO88" s="34"/>
+      <c r="AQ88" s="37"/>
+      <c r="AV88"/>
       <c r="AX88" s="34"/>
       <c r="AZ88" s="34"/>
       <c r="BB88" s="34"/>
       <c r="BD88" s="34"/>
-      <c r="BE88" s="19"/>
-      <c r="BK88" s="34"/>
+      <c r="BF88" s="34"/>
+      <c r="BG88" s="19"/>
+      <c r="BK88"/>
       <c r="BM88" s="34"/>
       <c r="BO88" s="34"/>
       <c r="BQ88" s="34"/>
-      <c r="BS88" s="37"/>
+      <c r="BS88" s="34"/>
+      <c r="BU88" s="37"/>
       <c r="BX88"/>
-      <c r="BZ88" s="34"/>
       <c r="CB88" s="34"/>
       <c r="CD88" s="34"/>
       <c r="CF88" s="34"/>
       <c r="CH88" s="34"/>
-    </row>
-    <row r="89" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R89" s="34"/>
-      <c r="T89" s="34"/>
-      <c r="V89" s="34"/>
-      <c r="X89" s="34"/>
-      <c r="Z89" s="37"/>
-      <c r="AG89" s="34"/>
+      <c r="CJ88" s="34"/>
+    </row>
+    <row r="89" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S89" s="34"/>
+      <c r="U89" s="34"/>
+      <c r="W89" s="34"/>
+      <c r="Y89" s="34"/>
+      <c r="Z89"/>
+      <c r="AA89" s="37"/>
+      <c r="AG89"/>
       <c r="AI89" s="34"/>
       <c r="AK89" s="34"/>
       <c r="AM89" s="34"/>
-      <c r="AO89" s="37"/>
-      <c r="AV89" s="34"/>
+      <c r="AO89" s="34"/>
+      <c r="AQ89" s="37"/>
+      <c r="AV89"/>
       <c r="AX89" s="34"/>
       <c r="AZ89" s="34"/>
       <c r="BB89" s="34"/>
       <c r="BD89" s="34"/>
-      <c r="BE89" s="19"/>
-      <c r="BK89" s="34"/>
+      <c r="BF89" s="34"/>
+      <c r="BG89" s="19"/>
+      <c r="BK89"/>
       <c r="BM89" s="34"/>
       <c r="BO89" s="34"/>
       <c r="BQ89" s="34"/>
-      <c r="BS89" s="37"/>
+      <c r="BS89" s="34"/>
+      <c r="BU89" s="37"/>
       <c r="BX89"/>
-      <c r="BZ89" s="34"/>
       <c r="CB89" s="34"/>
       <c r="CD89" s="34"/>
       <c r="CF89" s="34"/>
       <c r="CH89" s="34"/>
-    </row>
-    <row r="90" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R90" s="34"/>
-      <c r="T90" s="34"/>
-      <c r="V90" s="34"/>
-      <c r="X90" s="34"/>
-      <c r="Z90" s="37"/>
-      <c r="AG90" s="34"/>
+      <c r="CJ89" s="34"/>
+    </row>
+    <row r="90" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S90" s="34"/>
+      <c r="U90" s="34"/>
+      <c r="W90" s="34"/>
+      <c r="Y90" s="34"/>
+      <c r="Z90"/>
+      <c r="AA90" s="37"/>
+      <c r="AG90"/>
       <c r="AI90" s="34"/>
       <c r="AK90" s="34"/>
       <c r="AM90" s="34"/>
-      <c r="AO90" s="37"/>
-      <c r="AV90" s="34"/>
+      <c r="AO90" s="34"/>
+      <c r="AQ90" s="37"/>
+      <c r="AV90"/>
       <c r="AX90" s="34"/>
       <c r="AZ90" s="34"/>
       <c r="BB90" s="34"/>
       <c r="BD90" s="34"/>
-      <c r="BE90" s="19"/>
-      <c r="BK90" s="34"/>
+      <c r="BF90" s="34"/>
+      <c r="BG90" s="19"/>
+      <c r="BK90"/>
       <c r="BM90" s="34"/>
       <c r="BO90" s="34"/>
       <c r="BQ90" s="34"/>
-      <c r="BS90" s="37"/>
+      <c r="BS90" s="34"/>
+      <c r="BU90" s="37"/>
       <c r="BX90"/>
-      <c r="BZ90" s="34"/>
       <c r="CB90" s="34"/>
       <c r="CD90" s="34"/>
       <c r="CF90" s="34"/>
       <c r="CH90" s="34"/>
-    </row>
-    <row r="91" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R91" s="34"/>
-      <c r="T91" s="34"/>
-      <c r="V91" s="34"/>
-      <c r="X91" s="34"/>
-      <c r="Z91" s="37"/>
-      <c r="AG91" s="34"/>
+      <c r="CJ90" s="34"/>
+    </row>
+    <row r="91" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S91" s="34"/>
+      <c r="U91" s="34"/>
+      <c r="W91" s="34"/>
+      <c r="Y91" s="34"/>
+      <c r="Z91"/>
+      <c r="AA91" s="37"/>
+      <c r="AG91"/>
       <c r="AI91" s="34"/>
       <c r="AK91" s="34"/>
       <c r="AM91" s="34"/>
-      <c r="AO91" s="37"/>
-      <c r="AV91" s="34"/>
+      <c r="AO91" s="34"/>
+      <c r="AQ91" s="37"/>
+      <c r="AV91"/>
       <c r="AX91" s="34"/>
       <c r="AZ91" s="34"/>
       <c r="BB91" s="34"/>
       <c r="BD91" s="34"/>
-      <c r="BE91" s="19"/>
-      <c r="BK91" s="34"/>
+      <c r="BF91" s="34"/>
+      <c r="BG91" s="19"/>
+      <c r="BK91"/>
       <c r="BM91" s="34"/>
       <c r="BO91" s="34"/>
       <c r="BQ91" s="34"/>
-      <c r="BS91" s="37"/>
+      <c r="BS91" s="34"/>
+      <c r="BU91" s="37"/>
       <c r="BX91"/>
-      <c r="BZ91" s="34"/>
       <c r="CB91" s="34"/>
       <c r="CD91" s="34"/>
       <c r="CF91" s="34"/>
       <c r="CH91" s="34"/>
-    </row>
-    <row r="92" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R92" s="34"/>
-      <c r="T92" s="34"/>
-      <c r="V92" s="34"/>
-      <c r="X92" s="34"/>
-      <c r="Z92" s="37"/>
-      <c r="AG92" s="34"/>
+      <c r="CJ91" s="34"/>
+    </row>
+    <row r="92" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S92" s="34"/>
+      <c r="U92" s="34"/>
+      <c r="W92" s="34"/>
+      <c r="Y92" s="34"/>
+      <c r="Z92"/>
+      <c r="AA92" s="37"/>
+      <c r="AG92"/>
       <c r="AI92" s="34"/>
       <c r="AK92" s="34"/>
       <c r="AM92" s="34"/>
-      <c r="AO92" s="37"/>
-      <c r="AV92" s="34"/>
+      <c r="AO92" s="34"/>
+      <c r="AQ92" s="37"/>
+      <c r="AV92"/>
       <c r="AX92" s="34"/>
       <c r="AZ92" s="34"/>
       <c r="BB92" s="34"/>
       <c r="BD92" s="34"/>
-      <c r="BE92" s="19"/>
-      <c r="BK92" s="34"/>
+      <c r="BF92" s="34"/>
+      <c r="BG92" s="19"/>
+      <c r="BK92"/>
       <c r="BM92" s="34"/>
       <c r="BO92" s="34"/>
       <c r="BQ92" s="34"/>
-      <c r="BS92" s="37"/>
+      <c r="BS92" s="34"/>
+      <c r="BU92" s="37"/>
       <c r="BX92"/>
-      <c r="BZ92" s="34"/>
       <c r="CB92" s="34"/>
       <c r="CD92" s="34"/>
       <c r="CF92" s="34"/>
       <c r="CH92" s="34"/>
-    </row>
-    <row r="93" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R93" s="34"/>
-      <c r="T93" s="34"/>
-      <c r="V93" s="34"/>
-      <c r="X93" s="34"/>
-      <c r="Z93" s="37"/>
-      <c r="AG93" s="34"/>
+      <c r="CJ92" s="34"/>
+    </row>
+    <row r="93" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S93" s="34"/>
+      <c r="U93" s="34"/>
+      <c r="W93" s="34"/>
+      <c r="Y93" s="34"/>
+      <c r="Z93"/>
+      <c r="AA93" s="37"/>
+      <c r="AG93"/>
       <c r="AI93" s="34"/>
       <c r="AK93" s="34"/>
       <c r="AM93" s="34"/>
-      <c r="AO93" s="37"/>
-      <c r="AV93" s="34"/>
+      <c r="AO93" s="34"/>
+      <c r="AQ93" s="37"/>
+      <c r="AV93"/>
       <c r="AX93" s="34"/>
       <c r="AZ93" s="34"/>
       <c r="BB93" s="34"/>
       <c r="BD93" s="34"/>
-      <c r="BE93" s="19"/>
-      <c r="BK93" s="34"/>
+      <c r="BF93" s="34"/>
+      <c r="BG93" s="19"/>
+      <c r="BK93"/>
       <c r="BM93" s="34"/>
       <c r="BO93" s="34"/>
       <c r="BQ93" s="34"/>
-      <c r="BS93" s="37"/>
+      <c r="BS93" s="34"/>
+      <c r="BU93" s="37"/>
       <c r="BX93"/>
-      <c r="BZ93" s="34"/>
       <c r="CB93" s="34"/>
       <c r="CD93" s="34"/>
       <c r="CF93" s="34"/>
       <c r="CH93" s="34"/>
-    </row>
-    <row r="94" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R94" s="34"/>
-      <c r="T94" s="34"/>
-      <c r="V94" s="34"/>
-      <c r="X94" s="34"/>
-      <c r="Z94" s="37"/>
-      <c r="AG94" s="34"/>
+      <c r="CJ93" s="34"/>
+    </row>
+    <row r="94" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S94" s="34"/>
+      <c r="U94" s="34"/>
+      <c r="W94" s="34"/>
+      <c r="Y94" s="34"/>
+      <c r="Z94"/>
+      <c r="AA94" s="37"/>
+      <c r="AG94"/>
       <c r="AI94" s="34"/>
       <c r="AK94" s="34"/>
       <c r="AM94" s="34"/>
-      <c r="AO94" s="37"/>
-      <c r="AV94" s="34"/>
+      <c r="AO94" s="34"/>
+      <c r="AQ94" s="37"/>
+      <c r="AV94"/>
       <c r="AX94" s="34"/>
       <c r="AZ94" s="34"/>
       <c r="BB94" s="34"/>
       <c r="BD94" s="34"/>
-      <c r="BE94" s="19"/>
-      <c r="BK94" s="34"/>
+      <c r="BF94" s="34"/>
+      <c r="BG94" s="19"/>
+      <c r="BK94"/>
       <c r="BM94" s="34"/>
       <c r="BO94" s="34"/>
       <c r="BQ94" s="34"/>
-      <c r="BS94" s="37"/>
+      <c r="BS94" s="34"/>
+      <c r="BU94" s="37"/>
       <c r="BX94"/>
-      <c r="BZ94" s="34"/>
       <c r="CB94" s="34"/>
       <c r="CD94" s="34"/>
       <c r="CF94" s="34"/>
       <c r="CH94" s="34"/>
-    </row>
-    <row r="95" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R95" s="34"/>
-      <c r="T95" s="34"/>
-      <c r="V95" s="34"/>
-      <c r="X95" s="34"/>
-      <c r="Z95" s="37"/>
-      <c r="AG95" s="34"/>
+      <c r="CJ94" s="34"/>
+    </row>
+    <row r="95" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S95" s="34"/>
+      <c r="U95" s="34"/>
+      <c r="W95" s="34"/>
+      <c r="Y95" s="34"/>
+      <c r="Z95"/>
+      <c r="AA95" s="37"/>
+      <c r="AG95"/>
       <c r="AI95" s="34"/>
       <c r="AK95" s="34"/>
       <c r="AM95" s="34"/>
-      <c r="AO95" s="37"/>
-      <c r="AV95" s="34"/>
+      <c r="AO95" s="34"/>
+      <c r="AQ95" s="37"/>
+      <c r="AV95"/>
       <c r="AX95" s="34"/>
       <c r="AZ95" s="34"/>
       <c r="BB95" s="34"/>
       <c r="BD95" s="34"/>
-      <c r="BE95" s="19"/>
-      <c r="BK95" s="34"/>
+      <c r="BF95" s="34"/>
+      <c r="BG95" s="19"/>
+      <c r="BK95"/>
       <c r="BM95" s="34"/>
       <c r="BO95" s="34"/>
       <c r="BQ95" s="34"/>
-      <c r="BS95" s="37"/>
+      <c r="BS95" s="34"/>
+      <c r="BU95" s="37"/>
       <c r="BX95"/>
-      <c r="BZ95" s="34"/>
       <c r="CB95" s="34"/>
       <c r="CD95" s="34"/>
       <c r="CF95" s="34"/>
       <c r="CH95" s="34"/>
-    </row>
-    <row r="96" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R96" s="34"/>
-      <c r="T96" s="34"/>
-      <c r="V96" s="34"/>
-      <c r="X96" s="34"/>
-      <c r="Z96" s="37"/>
-      <c r="AG96" s="34"/>
+      <c r="CJ95" s="34"/>
+    </row>
+    <row r="96" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S96" s="34"/>
+      <c r="U96" s="34"/>
+      <c r="W96" s="34"/>
+      <c r="Y96" s="34"/>
+      <c r="Z96"/>
+      <c r="AA96" s="37"/>
+      <c r="AG96"/>
       <c r="AI96" s="34"/>
       <c r="AK96" s="34"/>
       <c r="AM96" s="34"/>
-      <c r="AO96" s="37"/>
-      <c r="AV96" s="34"/>
+      <c r="AO96" s="34"/>
+      <c r="AQ96" s="37"/>
+      <c r="AV96"/>
       <c r="AX96" s="34"/>
       <c r="AZ96" s="34"/>
       <c r="BB96" s="34"/>
       <c r="BD96" s="34"/>
-      <c r="BE96" s="19"/>
-      <c r="BK96" s="34"/>
+      <c r="BF96" s="34"/>
+      <c r="BG96" s="19"/>
+      <c r="BK96"/>
       <c r="BM96" s="34"/>
       <c r="BO96" s="34"/>
       <c r="BQ96" s="34"/>
-      <c r="BS96" s="37"/>
+      <c r="BS96" s="34"/>
+      <c r="BU96" s="37"/>
       <c r="BX96"/>
-      <c r="BZ96" s="34"/>
       <c r="CB96" s="34"/>
       <c r="CD96" s="34"/>
       <c r="CF96" s="34"/>
       <c r="CH96" s="34"/>
-    </row>
-    <row r="97" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R97" s="34"/>
-      <c r="T97" s="34"/>
-      <c r="V97" s="34"/>
-      <c r="X97" s="34"/>
-      <c r="Z97" s="37"/>
-      <c r="AG97" s="34"/>
+      <c r="CJ96" s="34"/>
+    </row>
+    <row r="97" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S97" s="34"/>
+      <c r="U97" s="34"/>
+      <c r="W97" s="34"/>
+      <c r="Y97" s="34"/>
+      <c r="Z97"/>
+      <c r="AA97" s="37"/>
+      <c r="AG97"/>
       <c r="AI97" s="34"/>
       <c r="AK97" s="34"/>
       <c r="AM97" s="34"/>
-      <c r="AO97" s="37"/>
-      <c r="AV97" s="34"/>
+      <c r="AO97" s="34"/>
+      <c r="AQ97" s="37"/>
+      <c r="AV97"/>
       <c r="AX97" s="34"/>
       <c r="AZ97" s="34"/>
       <c r="BB97" s="34"/>
       <c r="BD97" s="34"/>
-      <c r="BE97" s="19"/>
-      <c r="BK97" s="34"/>
+      <c r="BF97" s="34"/>
+      <c r="BG97" s="19"/>
+      <c r="BK97"/>
       <c r="BM97" s="34"/>
       <c r="BO97" s="34"/>
       <c r="BQ97" s="34"/>
-      <c r="BS97" s="37"/>
+      <c r="BS97" s="34"/>
+      <c r="BU97" s="37"/>
       <c r="BX97"/>
-      <c r="BZ97" s="34"/>
       <c r="CB97" s="34"/>
       <c r="CD97" s="34"/>
       <c r="CF97" s="34"/>
       <c r="CH97" s="34"/>
-    </row>
-    <row r="98" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R98" s="34"/>
-      <c r="T98" s="34"/>
-      <c r="V98" s="34"/>
-      <c r="X98" s="34"/>
-      <c r="Z98" s="37"/>
-      <c r="AG98" s="34"/>
+      <c r="CJ97" s="34"/>
+    </row>
+    <row r="98" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S98" s="34"/>
+      <c r="U98" s="34"/>
+      <c r="W98" s="34"/>
+      <c r="Y98" s="34"/>
+      <c r="Z98"/>
+      <c r="AA98" s="37"/>
+      <c r="AG98"/>
       <c r="AI98" s="34"/>
       <c r="AK98" s="34"/>
       <c r="AM98" s="34"/>
-      <c r="AO98" s="37"/>
-      <c r="AV98" s="34"/>
+      <c r="AO98" s="34"/>
+      <c r="AQ98" s="37"/>
+      <c r="AV98"/>
       <c r="AX98" s="34"/>
       <c r="AZ98" s="34"/>
       <c r="BB98" s="34"/>
       <c r="BD98" s="34"/>
-      <c r="BE98" s="19"/>
-      <c r="BK98" s="34"/>
+      <c r="BF98" s="34"/>
+      <c r="BG98" s="19"/>
+      <c r="BK98"/>
       <c r="BM98" s="34"/>
       <c r="BO98" s="34"/>
       <c r="BQ98" s="34"/>
-      <c r="BS98" s="37"/>
+      <c r="BS98" s="34"/>
+      <c r="BU98" s="37"/>
       <c r="BX98"/>
-      <c r="BZ98" s="34"/>
       <c r="CB98" s="34"/>
       <c r="CD98" s="34"/>
       <c r="CF98" s="34"/>
       <c r="CH98" s="34"/>
-    </row>
-    <row r="99" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R99" s="34"/>
-      <c r="T99" s="34"/>
-      <c r="V99" s="34"/>
-      <c r="X99" s="34"/>
-      <c r="Z99" s="37"/>
-      <c r="AG99" s="34"/>
+      <c r="CJ98" s="34"/>
+    </row>
+    <row r="99" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S99" s="34"/>
+      <c r="U99" s="34"/>
+      <c r="W99" s="34"/>
+      <c r="Y99" s="34"/>
+      <c r="Z99"/>
+      <c r="AA99" s="37"/>
+      <c r="AG99"/>
       <c r="AI99" s="34"/>
       <c r="AK99" s="34"/>
       <c r="AM99" s="34"/>
-      <c r="AO99" s="37"/>
-      <c r="AV99" s="34"/>
+      <c r="AO99" s="34"/>
+      <c r="AQ99" s="37"/>
+      <c r="AV99"/>
       <c r="AX99" s="34"/>
       <c r="AZ99" s="34"/>
       <c r="BB99" s="34"/>
       <c r="BD99" s="34"/>
-      <c r="BE99" s="19"/>
-      <c r="BK99" s="34"/>
+      <c r="BF99" s="34"/>
+      <c r="BG99" s="19"/>
+      <c r="BK99"/>
       <c r="BM99" s="34"/>
       <c r="BO99" s="34"/>
       <c r="BQ99" s="34"/>
-      <c r="BS99" s="37"/>
+      <c r="BS99" s="34"/>
+      <c r="BU99" s="37"/>
       <c r="BX99"/>
-      <c r="BZ99" s="34"/>
       <c r="CB99" s="34"/>
       <c r="CD99" s="34"/>
       <c r="CF99" s="34"/>
       <c r="CH99" s="34"/>
-    </row>
-    <row r="100" spans="18:86" x14ac:dyDescent="0.3">
-      <c r="R100" s="34"/>
-      <c r="T100" s="34"/>
-      <c r="V100" s="34"/>
-      <c r="X100" s="34"/>
-      <c r="Z100" s="37"/>
-      <c r="AG100" s="34"/>
+      <c r="CJ99" s="34"/>
+    </row>
+    <row r="100" spans="19:88" x14ac:dyDescent="0.3">
+      <c r="S100" s="34"/>
+      <c r="U100" s="34"/>
+      <c r="W100" s="34"/>
+      <c r="Y100" s="34"/>
+      <c r="Z100"/>
+      <c r="AA100" s="37"/>
+      <c r="AG100"/>
       <c r="AI100" s="34"/>
       <c r="AK100" s="34"/>
       <c r="AM100" s="34"/>
-      <c r="AO100" s="37"/>
-      <c r="AV100" s="34"/>
+      <c r="AO100" s="34"/>
+      <c r="AQ100" s="37"/>
+      <c r="AV100"/>
       <c r="AX100" s="34"/>
       <c r="AZ100" s="34"/>
       <c r="BB100" s="34"/>
       <c r="BD100" s="34"/>
-      <c r="BE100" s="19"/>
-      <c r="BK100" s="34"/>
+      <c r="BF100" s="34"/>
+      <c r="BG100" s="19"/>
+      <c r="BK100"/>
       <c r="BM100" s="34"/>
       <c r="BO100" s="34"/>
       <c r="BQ100" s="34"/>
-      <c r="BS100" s="37"/>
+      <c r="BS100" s="34"/>
+      <c r="BU100" s="37"/>
       <c r="BX100"/>
-      <c r="BZ100" s="34"/>
       <c r="CB100" s="34"/>
       <c r="CD100" s="34"/>
       <c r="CF100" s="34"/>
       <c r="CH100" s="34"/>
+      <c r="CJ100" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -7063,25 +7491,25 @@
           <x14:formula1>
             <xm:f>options!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>BK100</xm:sqref>
+          <xm:sqref>BM100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="soil moisture" prompt="indicate if measurement is gravimetric (% g/g) or volumetric (% V/V)" xr:uid="{95BC60E9-AF61-486E-9DBD-C211EE4FBBF0}">
           <x14:formula1>
             <xm:f>options!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>R3:R99 T3:T99 AG3:AG99 BZ3:BZ99 AX3:AX99 AI3:AI99 BM3:BM99 AV3:AV99 BK3:BK99 CB3:CB99</xm:sqref>
+          <xm:sqref>S3:S99 U3:U99 AI3:AI99 CB3:CB99 AZ3:AZ99 AK3:AK99 BO3:BO99 AX3:AX99 BM3:BM99 CD3:CD99</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="measurement units" prompt="select mg N/ha. or kg N/ha." xr:uid="{7A34E804-1F1D-4C2A-861F-919BB0C44744}">
           <x14:formula1>
             <xm:f>options!$I$2:$I$3</xm:f>
           </x14:formula1>
-          <xm:sqref>V3:V100 AK3:AK100 BO3:BO100 BB3:BB100 AM3:AM100 AZ3:AZ100 CF3:CF100 BQ3:BQ100 X3:X100 CD3:CD100</xm:sqref>
+          <xm:sqref>W3:W100 AM3:AM100 BQ3:BQ100 BD3:BD100 AO3:AO100 BB3:BB100 CH3:CH100 BS3:BS100 Y3:Y100 CF3:CF100</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{67722B95-306B-41AB-811A-519E31905398}">
           <x14:formula1>
             <xm:f>options!$K$2:$K$10</xm:f>
           </x14:formula1>
-          <xm:sqref>Z3:Z100 AO3:AO100 BS3:BS100 BD3:BD100 CH3:CH100</xm:sqref>
+          <xm:sqref>AA3:AA100 AQ3:AQ100 BU3:BU100 BF3:BF100 CJ3:CJ100</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7117,54 +7545,54 @@
         <v>62</v>
       </c>
       <c r="E1" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B2" s="6">
         <v>24.55</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="34"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B3" s="6">
         <v>-48.12</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D3" s="19">
         <v>5</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B4" s="6">
         <v>8.093</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D4" s="19">
         <v>40</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -7992,7 +8420,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3">
         <v>105</v>
@@ -8001,16 +8429,16 @@
         <v>325</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H3">
         <v>2019</v>
@@ -8021,7 +8449,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="59">
         <v>46086</v>
@@ -8030,16 +8458,16 @@
         <v>46118</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4">
         <v>2019</v>
@@ -8050,7 +8478,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -8059,16 +8487,16 @@
         <v>236</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H5">
         <v>2020</v>
@@ -8079,7 +8507,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B6" s="59">
         <v>46146</v>
@@ -8088,16 +8516,16 @@
         <v>46297</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6">
         <v>2004</v>
@@ -8642,15 +9070,15 @@
         <v>142</v>
       </c>
       <c r="E1" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="42" t="s">
         <v>180</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B2">
         <v>2019</v>
@@ -8667,7 +9095,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3">
         <v>2019</v>
@@ -8684,7 +9112,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4">
         <v>2019</v>
@@ -8701,7 +9129,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5">
         <v>2019</v>
@@ -8718,7 +9146,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B6">
         <v>2019</v>
@@ -8735,7 +9163,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7">
         <v>2019</v>
@@ -8752,7 +9180,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8">
         <v>2019</v>
@@ -8769,7 +9197,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9">
         <v>2019</v>
@@ -8786,7 +9214,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B10">
         <v>2019</v>
@@ -8803,7 +9231,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B11">
         <v>2004</v>
@@ -8820,7 +9248,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12">
         <v>2004</v>
@@ -8837,7 +9265,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13">
         <v>2004</v>
@@ -8854,7 +9282,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14">
         <v>2004</v>
@@ -8871,7 +9299,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15">
         <v>2004</v>
@@ -8888,7 +9316,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16">
         <v>2004</v>
@@ -8905,7 +9333,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17">
         <v>2004</v>
@@ -8922,7 +9350,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18">
         <v>2004</v>
@@ -8939,7 +9367,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B19">
         <v>2004</v>
@@ -9028,10 +9456,10 @@
         <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G1" t="s">
         <v>114</v>
@@ -9040,24 +9468,24 @@
         <v>127</v>
       </c>
       <c r="K1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O1" t="s">
         <v>189</v>
-      </c>
-      <c r="M1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" t="s">
         <v>197</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>198</v>
-      </c>
-      <c r="E2" t="s">
-        <v>199</v>
       </c>
       <c r="G2" t="s">
         <v>116</v>
@@ -9066,24 +9494,24 @@
         <v>126</v>
       </c>
       <c r="K2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
         <v>201</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>202</v>
-      </c>
-      <c r="E3" t="s">
-        <v>203</v>
       </c>
       <c r="G3" t="s">
         <v>115</v>
@@ -9092,76 +9520,76 @@
         <v>125</v>
       </c>
       <c r="K3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" t="s">
         <v>205</v>
       </c>
-      <c r="C4" t="s">
+      <c r="K4" t="s">
         <v>206</v>
       </c>
-      <c r="K4" t="s">
-        <v>207</v>
-      </c>
       <c r="O4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
         <v>208</v>
       </c>
-      <c r="C5" t="s">
+      <c r="K5" t="s">
         <v>209</v>
-      </c>
-      <c r="K5" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K6" t="s">
         <v>211</v>
-      </c>
-      <c r="K6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
+        <v>212</v>
+      </c>
+      <c r="K7" t="s">
         <v>213</v>
-      </c>
-      <c r="K7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
+        <v>214</v>
+      </c>
+      <c r="K8" t="s">
         <v>215</v>
-      </c>
-      <c r="K8" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
         <v>217</v>
-      </c>
-      <c r="K9" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="F10" s="1"/>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
